--- a/books_table.xlsx
+++ b/books_table.xlsx
@@ -95,6 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8A89F"/>
+        <bgColor rgb="00E8A89F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8E8E8"/>
         <bgColor rgb="00E8E8E8"/>
       </patternFill>
@@ -127,12 +133,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8D4E8"/>
         <bgColor rgb="00E8E4D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8A89F"/>
-        <bgColor rgb="00E8A89F"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,8 +203,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -221,8 +221,8 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -833,8 +833,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>1</v>
+      <c r="D11" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -928,7 +928,7 @@
           <t>Костромина С. Н. - Учиться на пятерки по математике. Как?, 2008, АСТ, ПРАЙМ-ЕВРОЗНАК</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -948,7 +948,7 @@
           <t>Технологии Буракова - Экспресс-курсы по обучению счёту. Состав числа</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -968,7 +968,7 @@
           <t>Л.Р. Бережнова - Секреты творчества в табличном умножении, 2006, АРКТИ</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>С. С. Минаева - Математика. Устные упражнения. 5 класс. Учебное пособие для общеобразовательных организаций, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -1848,7 +1848,7 @@
           <t>А. В. Фарков - Тесты по геометрии: 7 класс: к учебнику А. В. Погорелова «Геометрия. 7–9», 2017, Экзамен</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -1928,7 +1928,7 @@
           <t>Т. М. Мищенко - Дидактические материалы и методические рекомендации для учителя по геометрии: 9 класс: к учебнику Л. С. Атанасяна и др. «Геометрия. 7–9 классы», 2017, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -1948,7 +1948,7 @@
           <t>Ю. А. Глазков, М. В. Егупова - Рабочая тетрадь по геометрии. 8 класс: к учебнику Л. С. Атанасяна и др. «Геометрия. 7–9 классы», 2017, Экзамен</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -2068,7 +2068,7 @@
           <t>Ю.А. Глазков, П.М. Камаев - Рабочая тетрадь по геометрии. 8 класс, 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -2088,7 +2088,7 @@
           <t>Ю. А. Глазков, М. В. Егупова - Рабочая тетрадь по геометрии: 7 класс, 2017, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -2688,7 +2688,7 @@
           <t>Р.Н. Бунеев, Е.В. Бунеева, А.А. Вахрушев, С.А. Козлова - Летняя тетрадь будущего третьеклассника, 2007, Баласс</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -2708,7 +2708,7 @@
           <t>Бунеев Р.Н., Бунеева Е.В., Вахрушев А.А., Козлова С.А. - Летняя тетрадь будущего второклассника, 2009, Баласс</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -2748,7 +2748,7 @@
           <t>Т.В. Шклярова - Как научить Вашего ребёнка решать задачи: 1-6 классы, Грамотей</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -2784,7 +2784,7 @@
           <t>Т.В. Шклярова - Как я учила мою девочку таблице умножения, Грамотей</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -2844,7 +2844,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 5 класса учреждений общего среднего образования с русским языком обучения. В 2 частях. Часть 1, 2013, «Адукацыя i выхаванне»</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -2864,7 +2864,7 @@
           <t>С.А. Козлова, А.Г. Рубин - Математика. 5 класс. Часть 1, 2015, Баласс</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -2884,7 +2884,7 @@
           <t>Ю.А. Глазков, И.К. Варшавский, М.Я. Гаиашвили - Комплексные числа. 9–11 классы, 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -2904,7 +2904,7 @@
           <t>Ю.П. Дудницын, В.Л. Кронгауз - Контрольные работы по алгебре: 8 класс, 2010, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -2924,7 +2924,7 @@
           <t>С.С. Минаева - Дроби и проценты. 5-7 классы, 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -2944,7 +2944,7 @@
           <t>А. В. Шаповалов, И. В. Ященко - Вертикальная математика для всех. Готовимся к задаче С6 ЕГЭ с 6 класса, 2014, МЦНМО</t>
         </is>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -2984,7 +2984,7 @@
           <t>С. Б. Суворова, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Математика, 5—6 : книга для учителя, 2006, Просвещение</t>
         </is>
       </c>
-      <c r="C119" s="12" t="inlineStr">
+      <c r="C119" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -3004,7 +3004,7 @@
           <t>И.Л. Бродский, О.С. Мешавкина - Вероятность и статистика. 10–11 классы. Планирование и практикум, 2009, АРКТИ</t>
         </is>
       </c>
-      <c r="C120" s="13" t="inlineStr">
+      <c r="C120" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -3024,7 +3024,7 @@
           <t>Т. Кирис - Школьный репетитор. Математика. 7–11 класс, 2008, Питер</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -3044,7 +3044,7 @@
           <t>Э. Г. Гельфман, В. А. Панчищина, О. В. Холодная, Н. Б. Лобаненко, И. Е. Малова, В. Н. Ксенева - Уроки математики в 5 классе: книга для учителя, 2006, Просвещение</t>
         </is>
       </c>
-      <c r="C122" s="12" t="inlineStr">
+      <c r="C122" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -3064,7 +3064,7 @@
           <t>И. И. Зубарева, А. Г. Мордкович - Программы. Математика. 5—6 классы. Алгебра. 7—9 классы. Алгебра и начала математического анализа. 10—11 классы, 2011, Мнемозина</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3084,7 +3084,7 @@
           <t>Алгебра. 7 класс, 2005, Просвещение</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3104,7 +3104,7 @@
           <t>Ершова А.П., Голобородько В.В., Ершова А.С. - Самостоятельные и контрольные работы по алгебре и геометрии для 7 класса, 2005, Илекса</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -3124,7 +3124,7 @@
           <t>А. Г. Мордкович - Алгебра. 7 класс. Часть 2. Задачник, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3144,7 +3144,7 @@
           <t>А. Г. Мордкович - Алгебра. 7 класс. Часть 1. Учебник, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="C127" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3164,7 +3164,7 @@
           <t>Ш. А. Алимов, Ю. М. Колягин, Ю. В. Сидоров, Н. Е. Федорова, М. И. Шабунин - Алгебра и начала анализа, 2007, Просвещение</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3184,7 +3184,7 @@
           <t>А. Н. Колмогоров, А. М. Абрамов, Ю. П. Дудницын, Б. М. Ивлев, С. И. Шварцбурд - Алгебра и начала математического анализа, 2008, Просвещение</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3204,7 +3204,7 @@
           <t>Б. М. Ивлев, С. М. Саакян, С. И. Шварцбурд - Алгебра и начала анализа. Дидактические материалы для 11 класса, 2007, Просвещение</t>
         </is>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3224,7 +3224,7 @@
           <t>Г. В. Дорофеев, Г. К. Муравин, Е. А. Седова - Математика. Сборник заданий для подготовки и проведения письменного экзамена по математике (курс А) и алгебре и началам анализа (курс В) за курс средней школы. 11 класс, 2008, Дрофа</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C131" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -3244,7 +3244,7 @@
           <t>Н.Я. Виленкин - Алгебра 9. Учебник для учащихся 9 класса с углубленным изучением математики, 2006, Просвещение</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3264,7 +3264,7 @@
           <t>Примерные программы по учебным предметам. Математика. 5–9 классы, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -3284,7 +3284,7 @@
           <t>И.В. Ященко, А.В. Семенова - Преподавание математики в 2009/2010 учебном году. Методическое письмо, 2009, МИОО</t>
         </is>
       </c>
-      <c r="C134" s="12" t="inlineStr">
+      <c r="C134" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -3304,7 +3304,7 @@
           <t>И.В. Ященко, А.В. Семенова - О преподавании математики в 2010/2011 учебном году, 2010, МИОО</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -3364,7 +3364,7 @@
           <t>Нелин Е. П., Долгова О. Е. - Алгебра и начала анализа: Двухуровневый учеб. для 11 кл. общеобразоват. учеб. заведений, 2006, Мир детства</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -3384,7 +3384,7 @@
           <t>Л.И. Звавич, Е.В. Потоскуев - Тесты по геометрии. 8 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -3564,7 +3564,7 @@
           <t>А. Р. Рязановский, Д. Г. Мухин - Геометрия. 8 класс. Контрольные измерительные материалы, 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -3609,7 +3609,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D150" s="14" t="n">
+      <c r="D150" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
           <t>Ю.А. Глазков, П.М. Камаев - Рабочая тетрадь по геометрии. 9 класс: к учебнику Л.С. Атанасяна и др. «Геометрия. 7–9 классы», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C151" s="10" t="inlineStr">
+      <c r="C151" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -3724,7 +3724,7 @@
           <t>Л.П. Попова - Контрольно-измерительные материалы. Математика. 6 класс, 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="C156" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -3744,7 +3744,7 @@
           <t>В.В. Выговская - Сборник практических задач по математике. 6 класс, 2012, ВАКО</t>
         </is>
       </c>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -3764,7 +3764,7 @@
           <t>В.Н. Рудницкая - Тесты по математике: 6 класс: к учебнику Н.Я. Виленкина и др. «Математика. 6 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C158" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -3784,7 +3784,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по математике. 6 класс: ко всем линиям учебников по математике, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C159" s="9" t="inlineStr">
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -3804,7 +3804,7 @@
           <t>И.Л. Гусева, С.А. Пушкин, Н.В. Рыбакова - Тестовые материалы для оценки качества обучения. Математика. 6 класс, 2012, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C160" s="9" t="inlineStr">
+      <c r="C160" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -3824,7 +3824,7 @@
           <t>И.В. Шестакова - Математика. 6 класс. Практикум. Готовимся к ГИА, 2014, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C161" s="10" t="inlineStr">
+      <c r="C161" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -3844,7 +3844,7 @@
           <t>Выговская В.В. - Поурочные разработки по математике: 6 класс. К учебному комплекту Н.Я. Виленкина и др., 2011, ВАКО</t>
         </is>
       </c>
-      <c r="C162" s="12" t="inlineStr">
+      <c r="C162" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -3864,7 +3864,7 @@
           <t>Ю. А. Глазков, В. И. Ахременкова, М. Я. Гаиашвили - Математика. 6 класс. Контрольные измерительные материалы, 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -4004,13 +4004,13 @@
           <t>Э.Н. Балаян - Геометрия. Задачи на готовых чертежах для подготовки к ЕГЭ. 10-11 классы, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D170" s="5" t="n">
-        <v>1</v>
+      <c r="D170" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4064,7 +4064,7 @@
           <t>Ю.А. Глазков, М.Я. Гаиашвили - Тесты по алгебре: 7 класс: к учебнику Ю.Н. Макарычева и др. «Алгебра. 7 класс», 2011, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C173" s="10" t="inlineStr">
+      <c r="C173" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4084,7 +4084,7 @@
           <t>Ю. П. Дудницын, В. Л. Кронгауз - Алгебра. Тематические тесты. 7 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C174" s="10" t="inlineStr">
+      <c r="C174" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4104,7 +4104,7 @@
           <t>Крайнева Л.Б. - Алгебра. 7 класс. Практикум. Готовимся к ГИА, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C175" s="10" t="inlineStr">
+      <c r="C175" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4124,7 +4124,7 @@
           <t>Л.И. Звавич, Н.В. Дьяконова - Дидактические материалы по алгебре. 7 класс: к учебнику Ю.Н. Макарычева и др. «Алгебра. 7 класс», 2013, «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C176" s="10" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4144,7 +4144,7 @@
           <t>И. Л. Гусева, С. А. Пушкин, Н. В. Рыбакова - Тестовые материалы для оценки качества обучения. Алгебра. 7 класс, 2013, «Интеллект-Центр»</t>
         </is>
       </c>
-      <c r="C177" s="10" t="inlineStr">
+      <c r="C177" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4164,7 +4164,7 @@
           <t>Лебединцева Е. А., Беленкова Е. Ю. - Алгебра 7 класс. Задания для обучения и развития учащихся, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C178" s="10" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4184,7 +4184,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Тесты по алгебре. 7 класс: к учебнику А.Г. Мордковича «Алгебра. 7 класс», 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C179" s="10" t="inlineStr">
+      <c r="C179" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4204,7 +4204,7 @@
           <t>М. А. Попов - Контрольные и самостоятельные работы по алгебре: 7 класс: к учебнику А. Г. Мордковича «Алгебра. 7 класс», 2017, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C180" s="10" t="inlineStr">
+      <c r="C180" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4404,7 +4404,7 @@
           <t>Г.Д. Карташева - Тестовые материалы для оценки качества обучения. Геометрия. 9 класс (к учебнику Атанасяна и др.), 2012, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C190" s="10" t="inlineStr">
+      <c r="C190" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4424,7 +4424,7 @@
           <t>Н. Б. Мельникова - Геометрия. 9 класс. Экспресс-диагностика, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C191" s="10" t="inlineStr">
+      <c r="C191" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4444,7 +4444,7 @@
           <t>Т.М. Мищенко - Тематические тесты по геометрии. 9 класс: учебное пособие к учебникам Л.С. Атанасяна и др., А.В. Погорелова, И.Ф. Шарыгина, 2011, АСТ: Астрель; ВКТ</t>
         </is>
       </c>
-      <c r="C192" s="10" t="inlineStr">
+      <c r="C192" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4484,7 +4484,7 @@
           <t>А. В. Фарков - Тесты по геометрии: 9 класс: к учебнику Л. С. Атанасяна и др. «Геометрия. 7–9 классы», 2016, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C194" s="10" t="inlineStr">
+      <c r="C194" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4504,7 +4504,7 @@
           <t>А. Л. Семенов, И. В. Ященко - Геометрия. Длины. Тематический контроль. 7-9 классы. Рабочая тетрадь, 2013, Издательство «Национальное образование»</t>
         </is>
       </c>
-      <c r="C195" s="10" t="inlineStr">
+      <c r="C195" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4524,7 +4524,7 @@
           <t>В. И. Рыжик - Геометрия. Диагностические тесты. 7-9 классы, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C196" s="10" t="inlineStr">
+      <c r="C196" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4544,7 +4544,7 @@
           <t>Э.Н. Балаян - Геометрия. Задачи на готовых чертежах для подготовки к ГИА и ЕГЭ. 7-9 классы, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C197" s="10" t="inlineStr">
+      <c r="C197" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4564,7 +4564,7 @@
           <t>Ю.А. Глазков, М.В. Егупова - Геометрия. 7-9 класс. Практикум по планиметрии. Готовимся к ГИА, 2014, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C198" s="10" t="inlineStr">
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4584,7 +4584,7 @@
           <t>В. Н. Литвиненко - Геометрия. Готовимся к ЕГЭ. 11 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C199" s="10" t="inlineStr">
+      <c r="C199" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4604,7 +4604,7 @@
           <t>Панарина В.И. - Геометрия. Диагностические тесты. 7 класс, 2012, Национальное образование</t>
         </is>
       </c>
-      <c r="C200" s="10" t="inlineStr">
+      <c r="C200" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4644,7 +4644,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухова - Геометрия. 7 класс. Рабочая тетрадь. Самостоятельные работы. Тематические тесты. Тесты для промежуточной аттестации. Справочник, 2013, Легион</t>
         </is>
       </c>
-      <c r="C202" s="10" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4664,7 +4664,7 @@
           <t>Л.И. Звавич, Е.В. Потоскуев - Тесты по геометрии. 9 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C203" s="10" t="inlineStr">
+      <c r="C203" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4684,7 +4684,7 @@
           <t>А. Р. Рязановский, Д. Г. Мухин - Геометрия. 9 класс. Контрольные измерительные материалы, 2016, Экзамен</t>
         </is>
       </c>
-      <c r="C204" s="10" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4704,7 +4704,7 @@
           <t>Ю.А. Глазков, Л.И. Божёнкова - Тесты по геометрии. 10 класс: к учебнику Л.С. Атанасяна и др. «Геометрия. 10–11 классы», 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C205" s="10" t="inlineStr">
+      <c r="C205" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -4824,7 +4824,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк - Алгебра. Дидактические материалы. 9 класс: с углубленным изучением математики, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C211" s="10" t="inlineStr">
+      <c r="C211" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4844,7 +4844,7 @@
           <t>Ершова А.П., Голобородько В.В., Крижановский А.Ф. - Тетрадь-конспект по алгебре для 9 класса, 2012, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C212" s="10" t="inlineStr">
+      <c r="C212" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4864,7 +4864,7 @@
           <t>Ю.А. Глазков, И.К. Варшавский, М.Я. Гаиашвили - Тесты по алгебре: 9 класс: к учебнику Ю.Н. Макарычева и др. «Алгебра. 9 класс», 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C213" s="10" t="inlineStr">
+      <c r="C213" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4884,7 +4884,7 @@
           <t>Ю.А. Глазков, И.К. Варшавский, М.Я. Гаиашвили - Самостоятельные и контрольные работы по алгебре. 9 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C214" s="10" t="inlineStr">
+      <c r="C214" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4904,7 +4904,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, С. Б. Суворова, И. С. Шлыкова - Изучение алгебры в 7—9 классах: пособие для учителей, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C215" s="10" t="inlineStr">
+      <c r="C215" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4924,7 +4924,7 @@
           <t>&lt;авторы&gt; - &lt;название&gt;, &lt;год&gt;, &lt;издательство&gt;</t>
         </is>
       </c>
-      <c r="C216" s="10" t="inlineStr">
+      <c r="C216" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4944,7 +4944,7 @@
           <t>М. К. Потапов, А.В. Шевкин - Алгебра. Дидактические материалы. 9 класс, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C217" s="10" t="inlineStr">
+      <c r="C217" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -4964,7 +4964,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Тесты по алгебре. 9 класс: к учебнику А.Г. Мордковича «Алгебра. 9 класс», 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C218" s="10" t="inlineStr">
+      <c r="C218" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5044,7 +5044,7 @@
           <t>Беленкова Е.Ю., Лебединцева Е.А. - Математика. 6 класс. Тетрадь 1. Задания для обучения и развития учащихся, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C222" s="9" t="inlineStr">
+      <c r="C222" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -5064,7 +5064,7 @@
           <t>М.А. Попов - Дидактические материалы по математике: 6 класс: к учебнику Н.Я. Виленкина и др. «Математика. 6 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C223" s="9" t="inlineStr">
+      <c r="C223" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -5084,7 +5084,7 @@
           <t>М. Б. Миндюк, В. Н. Рудницкая - Математика. Рабочая тетрадь для 6 класса. В 2-х частях. Часть I, 2014, Издательский Дом «ГЕНЖЕР»</t>
         </is>
       </c>
-      <c r="C224" s="9" t="inlineStr">
+      <c r="C224" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -5129,7 +5129,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D226" s="14" t="n">
+      <c r="D226" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
           <t>М.А. Попов - Контрольные и самостоятельные работы по алгебре: 9 класс: к учебнику А.Г. Мордковича «Алгебра. 9 класс», 2011, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C234" s="10" t="inlineStr">
+      <c r="C234" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5304,7 +5304,7 @@
           <t>Б.Г. Зив, В.А. Гольдич - Дидактические материалы по алгебре для 9 класса, 2013, Петроглиф</t>
         </is>
       </c>
-      <c r="C235" s="10" t="inlineStr">
+      <c r="C235" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5324,7 +5324,7 @@
           <t>С. Г. Журавлев, Л. А. Малышева, В. А. Свентковский - Контрольные и самостоятельные работы по алгебре и геометрии, 2016, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C236" s="8" t="inlineStr">
+      <c r="C236" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -5444,7 +5444,7 @@
           <t>Л. В. Кузнецова, С. Б. Суворова, Е. А. Бунимович, Т. В. Колесникова, Л. О. Рослова - Алгебра : сб. заданий для подготовки к итоговой аттестации в 9 кл., 2008, Просвещение</t>
         </is>
       </c>
-      <c r="C242" s="10" t="inlineStr">
+      <c r="C242" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -5464,7 +5464,7 @@
           <t>Л. В. Кузнецова, Е. А. Бунимович, Б. П. Пигарев, С. Б. Суворова - Алгебра. Сборник заданий для проведения письменного экзамена по алгебре за курс основной школы. 9 класс, 2008, Дрофа</t>
         </is>
       </c>
-      <c r="C243" s="10" t="inlineStr">
+      <c r="C243" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -5684,7 +5684,7 @@
           <t>Е. М. Ключникова, И. В. Комиссарова - Промежуточное тестирование. Алгебра. 7 класс, 2015, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C254" s="10" t="inlineStr">
+      <c r="C254" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -5704,7 +5704,7 @@
           <t>М. А. Попов - Дидактические материалы по алгебре: 7 класс: к учебнику А. Г. Мордковича «Алгебра. 7 класс», 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C255" s="10" t="inlineStr">
+      <c r="C255" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5724,7 +5724,7 @@
           <t>Н. А. Ким - Алгебра. 7 класс : технологические карты уроков по учебнику А. Г. Мордковича, 2016, Учитель</t>
         </is>
       </c>
-      <c r="C256" s="10" t="inlineStr">
+      <c r="C256" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5744,7 +5744,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Рабочая тетрадь по алгебре. 7 класс: к учебнику А.Г. Мордковича и др. «Алгебра. 7 класс. В 2-х частях», 2013, Экзамен</t>
         </is>
       </c>
-      <c r="C257" s="10" t="inlineStr">
+      <c r="C257" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5764,7 +5764,7 @@
           <t>А.Г. Мордкович - Алгебра. 7 класс, Мнемозина</t>
         </is>
       </c>
-      <c r="C258" s="10" t="inlineStr">
+      <c r="C258" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5784,7 +5784,7 @@
           <t>С. Г. Журавлев, С. А. Изотова, С. В. Киреева - Контрольные и самостоятельные работы по алгебре и геометрии, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C259" s="9" t="inlineStr">
+      <c r="C259" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -5944,7 +5944,7 @@
           <t>Б.Г. Зив, В.А. Гольдич - Дидактические материалы по алгебре для 8 класса, 2012, Петроглиф</t>
         </is>
       </c>
-      <c r="C267" s="10" t="inlineStr">
+      <c r="C267" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -5964,7 +5964,7 @@
           <t>Лысенко Ф. Ф., Ольховая Л. С., Агафонова И. М., Бубличенко О. А., Давыдов Б. Е., Дробязко Е. А., Ковалева Л. Н., Ланцова Л. В., Монастырская Г. А. - Алгебра. Тесты для промежуточной аттестации. 7-8 класс, 2009, Легион-М</t>
         </is>
       </c>
-      <c r="C268" s="10" t="inlineStr">
+      <c r="C268" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -5984,7 +5984,7 @@
           <t>В. В. Кочагин, М. Н. Кочагина - Алгебра. 8 класс. Тестовые задания к основным учебникам. Рабочая тетрадь, 2009, Эксмо</t>
         </is>
       </c>
-      <c r="C269" s="10" t="inlineStr">
+      <c r="C269" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6004,7 +6004,7 @@
           <t>Алгебра. 8 класс. Тематические тесты. Промежуточная аттестация, 2011, Легион-М</t>
         </is>
       </c>
-      <c r="C270" s="10" t="inlineStr">
+      <c r="C270" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -6024,7 +6024,7 @@
           <t>Ю.А. Глазков, М.Я. Гаиашвили - Алгебра. 8 класс. Тематические тестовые задания к итоговой аттестации, 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C271" s="10" t="inlineStr">
+      <c r="C271" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -6044,7 +6044,7 @@
           <t>Панарина В.И. - Алгебра. 8 класс. 208 диагностических вариантов, 2012, Национальное образование</t>
         </is>
       </c>
-      <c r="C272" s="10" t="inlineStr">
+      <c r="C272" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -6264,7 +6264,7 @@
           <t>А. В. Фарков - Тесты по геометрии: 9 класс: к учебнику А. В. Погорелова «Геометрия. 7–9», 2017, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C283" s="10" t="inlineStr">
+      <c r="C283" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -6404,7 +6404,7 @@
           <t>Г. В. Дорофеев, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева - Алгебра. 9 класс, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C290" s="10" t="inlineStr">
+      <c r="C290" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6424,7 +6424,7 @@
           <t>Г.С. Сурвилло, А.С. Симонов - Дидактические материалы по алгебре для 9 класса с углубленным изучением математики, 2006, Просвещение</t>
         </is>
       </c>
-      <c r="C291" s="10" t="inlineStr">
+      <c r="C291" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6469,7 +6469,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D293" s="14" t="n">
+      <c r="D293" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
           <t>Н.Я. Виленкин - Алгебра 9: Учебник для учащихся 9 класса с углубленным изучением математики, 2006, Просвещение</t>
         </is>
       </c>
-      <c r="C300" s="10" t="inlineStr">
+      <c r="C300" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D300" s="14" t="n">
+      <c r="D300" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
           <t>М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Дидактические материалы. 9 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C301" s="10" t="inlineStr">
+      <c r="C301" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6644,7 +6644,7 @@
           <t>Ю. М. Колягин, Ю. В. Сидоров, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 9 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C302" s="10" t="inlineStr">
+      <c r="C302" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6664,7 +6664,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, Л. Б. Крайнева - Алгебра. Дидактические материалы. 9 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C303" s="10" t="inlineStr">
+      <c r="C303" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6684,7 +6684,7 @@
           <t>Л. И. Звавич, Н. В. Дьяконова - Дидактические материалы по алгебре: 9 класс: к учебнику Ю. Н. Макарычева и др. «Алгебра. 9 класс», 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C304" s="10" t="inlineStr">
+      <c r="C304" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6704,7 +6704,7 @@
           <t>Ю. П. Дудницын, В. Л. Кронгауз - Алгебра. Тематические тесты. 9 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C305" s="10" t="inlineStr">
+      <c r="C305" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6724,7 +6724,7 @@
           <t>Т.Г. Роева, Н.Ф. Хроленко - Алгебра в таблицах. 11 класс, 2002, Країна мрій</t>
         </is>
       </c>
-      <c r="C306" s="10" t="inlineStr">
+      <c r="C306" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6824,7 +6824,7 @@
           <t>М. Я. Пратусевич, К. М. Столбов, В. Н. Соломин, А. Н. Головин - Алгебра и начала математического анализа. Методические рекомендации. 11 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C311" s="10" t="inlineStr">
+      <c r="C311" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6844,7 +6844,7 @@
           <t>М. Я. Пратусевич, К. М. Столбов, В. Н. Соломин, А. Н. Головин - Алгебра и начала математического анализа. Методические рекомендации. 10 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C312" s="10" t="inlineStr">
+      <c r="C312" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6864,7 +6864,7 @@
           <t>А.Н. Рурукин - Контрольно-измерительные материалы. Алгебра и начала анализа. 10 класс, 2017, ВАКО</t>
         </is>
       </c>
-      <c r="C313" s="10" t="inlineStr">
+      <c r="C313" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6884,7 +6884,7 @@
           <t>Е. П. Нелин - АЛГЕБРА В ТАБЛИЦАХ, 2011, Гимназия</t>
         </is>
       </c>
-      <c r="C314" s="10" t="inlineStr">
+      <c r="C314" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -6924,7 +6924,7 @@
           <t>Ю. Н. Тюрин, А. А. Макаров, И. Р. Высоцкий, И. В. Ященко - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И СТАТИСТИКА, 2008, Издательство МЦНМО, ОАО «Московские учебники»</t>
         </is>
       </c>
-      <c r="C316" s="13" t="inlineStr">
+      <c r="C316" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -6944,7 +6944,7 @@
           <t>Т. Н. Маслова, А. М. Суходский - Справочник школьника по математике. 5—11 классы, 2008, ООО «Издательство Оникс»: ООО «Издательство «Мир и Образование»</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
+      <c r="C317" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -6984,7 +6984,7 @@
           <t>Л.Э. Генденштейн, А.П. Ершова, А.С. Ершова - Наглядный справочник по алгебре и началам анализа с примерами для 7-11 классов, 1997, Илекса, Гимназия</t>
         </is>
       </c>
-      <c r="C319" s="10" t="inlineStr">
+      <c r="C319" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7004,7 +7004,7 @@
           <t>Ф. Ф. Лысенко, С. Ю. Кулабухова - Математика. Устные вычисления и быстрый счёт. Тренировочные упражнения за курс 7–11 классов, 2010, Легион-М</t>
         </is>
       </c>
-      <c r="C320" s="8" t="inlineStr">
+      <c r="C320" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -7024,7 +7024,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухов - Алгебра. 7-8 классы. Тренажер. Тематические тесты и итоговые работы, 2013, Легион</t>
         </is>
       </c>
-      <c r="C321" s="10" t="inlineStr">
+      <c r="C321" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7044,7 +7044,7 @@
           <t>Василий Кравчук, Мария Пидручная, Галина Янченко - Алгебра: учебник для 9 класса, 2009, Підручники і посібники</t>
         </is>
       </c>
-      <c r="C322" s="10" t="inlineStr">
+      <c r="C322" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7064,7 +7064,7 @@
           <t>М. В. Ткачёва - Алгебра. Тематические тесты. 9 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C323" s="10" t="inlineStr">
+      <c r="C323" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7084,12 +7084,12 @@
           <t>М. В. Ткачёва - Алгебра. Тематические тесты. 9 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C324" s="10" t="inlineStr">
+      <c r="C324" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D324" s="14" t="n">
+      <c r="D324" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
           <t>Л.В. Кузнецова, С.С. Минаева, Л.О. Рослова - Алгебра. Контрольные работы. 7-9 классы, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C325" s="10" t="inlineStr">
+      <c r="C325" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7124,7 +7124,7 @@
           <t>Л.П. Евстафьева, А.П. Карп - Алгебра. Дидактические материалы. 9 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C326" s="10" t="inlineStr">
+      <c r="C326" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7184,7 +7184,7 @@
           <t>Л. Б. Крайнева - Тестовые материалы для оценки качества обучения. Алгебра. 9 класс, 2012, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C329" s="10" t="inlineStr">
+      <c r="C329" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7204,7 +7204,7 @@
           <t>Г. Д. Карташева, Л. Б. Крайнева - Алгебра. 9 класс. Контрольные работы в новом формате, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C330" s="10" t="inlineStr">
+      <c r="C330" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7224,7 +7224,7 @@
           <t>Лебединцева Е.А., Беленкова Е.Ю. - Алгебра. 9 класс. Задания для обучения и развития учащихся, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C331" s="10" t="inlineStr">
+      <c r="C331" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7244,7 +7244,7 @@
           <t>Рурукин А.Н., Полякова С.А. - Поурочные разработки по алгебре: 9 класс, 2010, ВАКО</t>
         </is>
       </c>
-      <c r="C332" s="10" t="inlineStr">
+      <c r="C332" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7264,7 +7264,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили, В. И. Ахременкова - Контрольные измерительные материалы. Алгебра. 9 класс, 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C333" s="10" t="inlineStr">
+      <c r="C333" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7284,7 +7284,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Рабочая тетрадь. 9 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C334" s="10" t="inlineStr">
+      <c r="C334" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7304,7 +7304,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Рабочая тетрадь по алгебре: 9 класс: к учебнику А.Г. Мордковича «Алгебра. 9 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C335" s="10" t="inlineStr">
+      <c r="C335" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7324,7 +7324,7 @@
           <t>Рурукин А.Н., Масленникова И.А., Мишина Т.Г. - Поурочные разработки по алгебре: 9 класс: к УМК А.Г. Мордковича и др. (М.: Мнемозина), 2011, ВАКО</t>
         </is>
       </c>
-      <c r="C336" s="10" t="inlineStr">
+      <c r="C336" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7344,7 +7344,7 @@
           <t>Н. В. Шевелева, Т. А. Корешкова, В. В. Мирошин - МАТЕМАТИКА. АЛГЕБРА, ЭЛЕМЕНТЫ СТАТИСТИКИ И ТЕОРИИ ВЕРОЯТНОСТЕЙ. 9 класс, 2011, Национальное образование</t>
         </is>
       </c>
-      <c r="C337" s="8" t="inlineStr">
+      <c r="C337" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -7364,7 +7364,7 @@
           <t>И.Н.Сергеев - 1000 ВОПРОСОВ И ОТВЕТОВ. МАТЕМАТИКА: Учебное пособие для поступающих в ВУЗы, 2001, Книжный дом «Университет»</t>
         </is>
       </c>
-      <c r="C338" s="10" t="inlineStr">
+      <c r="C338" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7384,7 +7384,7 @@
           <t>А. А. Рывкин, Е. Б. Ваховский - Сборник задач по математике с решениями для поступающих в вузы, 2003, ОНИКС 21 век, Мир и Образование</t>
         </is>
       </c>
-      <c r="C339" s="10" t="inlineStr">
+      <c r="C339" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7404,7 +7404,7 @@
           <t>Под ред. Шабунина М. И. - Методическое пособие по математике для поступающих в вузы, 2006, Физматкнига</t>
         </is>
       </c>
-      <c r="C340" s="10" t="inlineStr">
+      <c r="C340" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7584,7 +7584,7 @@
           <t>Звавич Л. И., Рязановский А. Р., Семенов П. В. - Алгебра. 9 класс : задачник для учащихся общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C349" s="10" t="inlineStr">
+      <c r="C349" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7604,7 +7604,7 @@
           <t>А. Г. Мордкович, П. В. Семенов - Алгебра. 9 класс. Часть 1. Учебник, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C350" s="10" t="inlineStr">
+      <c r="C350" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7644,7 +7644,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 9 класс, 2014, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C352" s="10" t="inlineStr">
+      <c r="C352" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7664,7 +7664,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Математика. 6 кл., 2014, Дрофа</t>
         </is>
       </c>
-      <c r="C353" s="9" t="inlineStr">
+      <c r="C353" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -7684,7 +7684,7 @@
           <t>В. И. Жохов - Математический тренажёр. 5 класс : пособие для учителей и учащихся, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C354" s="12" t="inlineStr">
+      <c r="C354" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -7704,7 +7704,7 @@
           <t>Л. Н. Фадеева, А. В. Лебедев - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА, 2011, Рид Групп</t>
         </is>
       </c>
-      <c r="C355" s="13" t="inlineStr">
+      <c r="C355" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -7724,7 +7724,7 @@
           <t>А.Ф. Веремьёв - Решение экзаменационных задач по алгебре за 9 класс, 2008, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C356" s="10" t="inlineStr">
+      <c r="C356" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7744,7 +7744,7 @@
           <t>Н.В. Дорофеев, А.А. Сапожников, Е.С. Шубин - РЕШЕНИЕ ЭКЗАМЕНАЦИОННЫХ ЗАДАЧ ПО МАТЕМАТИКЕ ЗА 11 КЛАСС, Дрофа</t>
         </is>
       </c>
-      <c r="C357" s="10" t="inlineStr">
+      <c r="C357" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7764,7 +7764,7 @@
           <t>Веселаго И. А. - Алгебра для школьников и абитуриентов, 2007, ФИЗМАТЛИТ</t>
         </is>
       </c>
-      <c r="C358" s="10" t="inlineStr">
+      <c r="C358" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7884,7 +7884,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебраический тренажер, 2007, Илекса</t>
         </is>
       </c>
-      <c r="C364" s="10" t="inlineStr">
+      <c r="C364" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7904,7 +7904,7 @@
           <t>Моденов В. П. - Математика: Пособие для поступающих в вузы, 2002, Издательство Новая Волна</t>
         </is>
       </c>
-      <c r="C365" s="10" t="inlineStr">
+      <c r="C365" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7944,7 +7944,7 @@
           <t>М. Ю. Пантаев - Математический гербарий абитуриента: Алгебра во всем ее блеске и многообразии, 2017, ЛЕНАНД</t>
         </is>
       </c>
-      <c r="C367" s="10" t="inlineStr">
+      <c r="C367" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -7964,7 +7964,7 @@
           <t>Э. С. Беляева, А. С. Потапов, С. А. Титоренко - Уравнения и неравенства с параметром. Часть 1, 2009, Дрофа</t>
         </is>
       </c>
-      <c r="C368" s="10" t="inlineStr">
+      <c r="C368" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -7984,7 +7984,7 @@
           <t>А. А. Рывкин, А. З. Рывкин - Математика. Справочное пособие для школьников старших классов и поступающих в вузы, 2003, ОНИКС 21 век, Мир и Образование</t>
         </is>
       </c>
-      <c r="C369" s="10" t="inlineStr">
+      <c r="C369" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8004,7 +8004,7 @@
           <t>С. А. Барвенов - Математика. Секреты ЦТ: 10 + 1 проверенный способ угадать правильный ответ, 2015, Аверсэв</t>
         </is>
       </c>
-      <c r="C370" s="10" t="inlineStr">
+      <c r="C370" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8024,7 +8024,7 @@
           <t>М.И. Сканави - Полный сборник решений задач по математике для поступающих в вузы. Группа А, 2012, Мир и Образование, Астрель</t>
         </is>
       </c>
-      <c r="C371" s="10" t="inlineStr">
+      <c r="C371" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8064,7 +8064,7 @@
           <t>И. Г. Арефьева - Повторяем математику за курс средней школы. Решение смешанных тестов, Аверсэв</t>
         </is>
       </c>
-      <c r="C373" s="10" t="inlineStr">
+      <c r="C373" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8109,8 +8109,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D375" s="14" t="n">
-        <v>2</v>
+      <c r="D375" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8244,7 +8244,7 @@
           <t>Поурочные разработки по математике. 5 класс</t>
         </is>
       </c>
-      <c r="C382" s="12" t="inlineStr">
+      <c r="C382" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -8264,7 +8264,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Контрольные работы. 5 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C383" s="12" t="inlineStr">
+      <c r="C383" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -8284,7 +8284,7 @@
           <t>Л. Г. Петерсон, Л. А. Грушевская, М. А. Кубышева, М. В. Рогатова - Методические рекомендации к учебнику «Математика» 5 класс, 2015, Издательство «Ювента»</t>
         </is>
       </c>
-      <c r="C384" s="12" t="inlineStr">
+      <c r="C384" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -8304,7 +8304,7 @@
           <t>Н.В. Сафонова - Математика. Арифметика. Геометрия. Тетрадь-экзаменатор. 5 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C385" s="10" t="inlineStr">
+      <c r="C385" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8344,7 +8344,7 @@
           <t>С.А. Козлова, А.Г. Рубин - Математика. Учебник. 6 класс. Часть 1, 2013, Баласс</t>
         </is>
       </c>
-      <c r="C387" s="9" t="inlineStr">
+      <c r="C387" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -8364,7 +8364,7 @@
           <t>Математика в школе, 2018, Школьная Пресса</t>
         </is>
       </c>
-      <c r="C388" s="8" t="inlineStr">
+      <c r="C388" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8384,7 +8384,7 @@
           <t>Т.М. Виноградова - Математика. 5-6 классы. Алгоритмы решения задач, 2018, Эксмо</t>
         </is>
       </c>
-      <c r="C389" s="9" t="inlineStr">
+      <c r="C389" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -8404,7 +8404,7 @@
           <t>Анатолий Верчинский - Незабываемые числа. Как запомнить пароль, пин-код и день рождения любимой бабушки, 2018, Ridero</t>
         </is>
       </c>
-      <c r="C390" s="11" t="inlineStr">
+      <c r="C390" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -8464,13 +8464,13 @@
           <t>Э.Н. Балаян - Геометрия. Задачи на готовых чертежах для подготовки к ГИА и ЕГЭ. 7-9 классы, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C393" s="10" t="inlineStr">
+      <c r="C393" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D393" s="14" t="n">
-        <v>2</v>
+      <c r="D393" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8484,7 +8484,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Математика. Дидактические материалы. 6 класс, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C394" s="9" t="inlineStr">
+      <c r="C394" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -8504,7 +8504,7 @@
           <t>А. Г. Мордкович, Л. О. Денищева, Л. И. Звавич, Т. А. Корешкова, Т. Н. Мишустина, А. Р. Рязановский, П. В. Семенов - Алгебра и начала математического анализа. 10 класс. В 2 ч. Ч. 2. Задачник для учащихся общеобразовательных учреждений (профильный уровень), 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C395" s="10" t="inlineStr">
+      <c r="C395" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8524,7 +8524,7 @@
           <t>Мордкович А. Г., Семенов П. В. - Алгебра и начала математического анализа. 10 класс. В 2 ч. Ч. 1. Учебник для учащихся общеобразовательных учреждений (профильный уровень), 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C396" s="10" t="inlineStr">
+      <c r="C396" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8544,7 +8544,7 @@
           <t>В. С. Крамор - Задачи на составление уравнений и методы их решения, 2009, ООО «Издательство Оникс»: ООО «Издательство «Мир и Образование»</t>
         </is>
       </c>
-      <c r="C397" s="8" t="inlineStr">
+      <c r="C397" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8564,7 +8564,7 @@
           <t>Прокофьев А.А. - Задачи с параметрами, 2004, МИЭТ</t>
         </is>
       </c>
-      <c r="C398" s="8" t="inlineStr">
+      <c r="C398" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8604,7 +8604,7 @@
           <t>В. С. Крамор - ЗАДАЧИ С ПАРАМЕТРАМИ И МЕТОДЫ ИХ РЕШЕНИЯ, 2007, ОНИКС • Мир и Образование</t>
         </is>
       </c>
-      <c r="C400" s="8" t="inlineStr">
+      <c r="C400" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8624,7 +8624,7 @@
           <t>Козко А. И., Панфёров В. С., Сергеев И. Н., Чирский В. Г. - Задачи с параметрами, сложные и нестандартные задачи, 2016, МЦНМО</t>
         </is>
       </c>
-      <c r="C401" s="8" t="inlineStr">
+      <c r="C401" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8644,7 +8644,7 @@
           <t>В.В. Локоть - Задачи с параметрами. Применение свойств функций, преобразование неравенств, 2010, АРКТИ</t>
         </is>
       </c>
-      <c r="C402" s="8" t="inlineStr">
+      <c r="C402" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8664,7 +8664,7 @@
           <t>А. Х. Шахмейстер - Задачи с параметрами на экзаменах, 2009, МЦНМО, Петроглиф, Виктория плюс</t>
         </is>
       </c>
-      <c r="C403" s="10" t="inlineStr">
+      <c r="C403" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -8684,7 +8684,7 @@
           <t>В.В. Локоть - Задачи с параметрами. Иррациональные уравнения, неравенства, системы, задачи с модулем, 2010, АРКТИ</t>
         </is>
       </c>
-      <c r="C404" s="8" t="inlineStr">
+      <c r="C404" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8724,7 +8724,7 @@
           <t>М. С. Красс, Б. П. Чупрынов - Математика для экономистов, 2005, Питер</t>
         </is>
       </c>
-      <c r="C406" s="8" t="inlineStr">
+      <c r="C406" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8744,7 +8744,7 @@
           <t>Ухоботов В.И. - Математика для экономистов, 2002, Челябинский государственный университет</t>
         </is>
       </c>
-      <c r="C407" s="8" t="inlineStr">
+      <c r="C407" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8764,7 +8764,7 @@
           <t>А. Д. Мышкис - Математика для технических вузов: Специальные курсы, 2009, Лань</t>
         </is>
       </c>
-      <c r="C408" s="8" t="inlineStr">
+      <c r="C408" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8784,7 +8784,7 @@
           <t>Красс М. С., Чупрынов Б. П. - Математические методы и модели для магистрантов экономики, 2010, Питер</t>
         </is>
       </c>
-      <c r="C409" s="8" t="inlineStr">
+      <c r="C409" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8804,7 +8804,7 @@
           <t>Е. С. Кундышева - МАТЕМАТИКА: Учебник для экономистов, 2015, Издательско-торговая корпорация «Дашков и К°»</t>
         </is>
       </c>
-      <c r="C410" s="8" t="inlineStr">
+      <c r="C410" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -8844,7 +8844,7 @@
           <t>М. И. Башмаков - МАТЕМАТИКА. КНИГА ДЛЯ ПРЕПОДАВАТЕЛЯ, 2013, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C412" s="12" t="inlineStr">
+      <c r="C412" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -8884,7 +8884,7 @@
           <t>А.Г. Мерзляк, В.М. Поляков - Алгебра. 7 класс. Учебник для учащихся общеобразовательных организаций, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C414" s="10" t="inlineStr">
+      <c r="C414" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8904,7 +8904,7 @@
           <t>А.Г. Мерзляк, В.М. Поляков - Алгебра. 8 класс : учебник для учащихся общеобразовательных организаций, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C415" s="10" t="inlineStr">
+      <c r="C415" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8924,7 +8924,7 @@
           <t>А. Г. Мерзляк, В. М. Поляков - Алгебра. 9 класс. Углублённый уровень, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C416" s="10" t="inlineStr">
+      <c r="C416" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8944,7 +8944,7 @@
           <t>А. Г. Мерзляк, Д. А. Номировский, В. М. Поляков - Алгебра и начала математического анализа : 10 класс : учебное пособие : углублённый уровень, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C417" s="10" t="inlineStr">
+      <c r="C417" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -8964,7 +8964,7 @@
           <t>А.Г. Мерзляк, Д.А. Номировский, В.М. Поляков - Математика. Алгебра и начала математического анализа. 11 класс. Углублённый уровень. Учебное пособие, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C418" s="10" t="inlineStr">
+      <c r="C418" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -9064,7 +9064,7 @@
           <t>М. Б. Лагутин - Наглядная математическая статистика, 2009, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C423" s="13" t="inlineStr">
+      <c r="C423" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -9104,7 +9104,7 @@
           <t>Математический Словарь</t>
         </is>
       </c>
-      <c r="C425" s="8" t="inlineStr">
+      <c r="C425" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -9324,7 +9324,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - МАТЕМАТИКА 5 класс, 2018, «Гимназия»</t>
         </is>
       </c>
-      <c r="C436" s="9" t="inlineStr">
+      <c r="C436" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr"/>
-      <c r="C439" s="8" t="inlineStr">
+      <c r="C439" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -9400,7 +9400,7 @@
           <t>А. Г. Мерзляк, Д. А. Номировский, В. Б. Полонский, М. С. Якир - МАТЕМАТИКА. АЛГЕБРА И НАЧАЛА АНАЛИЗА И ГЕОМЕТРИЯ. УРОВЕНЬ СТАНДАРТА, 2018, «Гимназия»</t>
         </is>
       </c>
-      <c r="C440" s="8" t="inlineStr">
+      <c r="C440" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -9420,7 +9420,7 @@
           <t>Н. Я. Виленкин, В. И. Жохов, А. С. Чесноков, С. И. Шварцбурд - Математика. 5 класс. Учебник для учащихся общеобразовательных учреждений, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C441" s="9" t="inlineStr">
+      <c r="C441" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -9560,7 +9560,7 @@
           <t>А.П. Рябушко - Индивидуальные задания по высшей математике. В 4 ч. Ч. 4. Операционное исчисление. Элементы теории устойчивости. Теория вероятностей. Математическая статистика, 2007, Вышэйшая школа</t>
         </is>
       </c>
-      <c r="C448" s="13" t="inlineStr">
+      <c r="C448" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -9600,7 +9600,7 @@
           <t>А. Н. Ширяев - Задачи по теории вероятностей, 2006, МЦНМО</t>
         </is>
       </c>
-      <c r="C450" s="13" t="inlineStr">
+      <c r="C450" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -9620,7 +9620,7 @@
           <t>А. С. Шапкин, В. А. Шапкин - Задачи по высшей математике, теории вероятностей, математической статистике, математическому программированию с решениями, 2010, Издательско-торговая корпорация «Дашков и К°»</t>
         </is>
       </c>
-      <c r="C451" s="13" t="inlineStr">
+      <c r="C451" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -9640,7 +9640,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 6 класс. Рабочая тетрадь № 1, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C452" s="9" t="inlineStr">
+      <c r="C452" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -9660,7 +9660,7 @@
           <t>С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. Методические рекомендации. 7 класс, 2015, Просвещение</t>
         </is>
       </c>
-      <c r="C453" s="10" t="inlineStr">
+      <c r="C453" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -9680,7 +9680,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Алгебра. Контрольные работы. 7 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C454" s="10" t="inlineStr">
+      <c r="C454" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -9700,7 +9700,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 7 класс. Часть 1, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C455" s="10" t="inlineStr">
+      <c r="C455" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -9720,7 +9720,7 @@
           <t>Н. Б. Истомина, О. П. Горина - Тестовые задания по математике. 6 класс. Обыкновенные и десятичные дроби. Часть 1, 2014, Ассоциация XXI век</t>
         </is>
       </c>
-      <c r="C456" s="9" t="inlineStr">
+      <c r="C456" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -9740,7 +9740,7 @@
           <t>Т. М. Ерина - Рабочая тетрадь по математике. Часть 1. К учебнику С. М. Никольского и др. «Математика. 6 класс», 2017, Экзамен</t>
         </is>
       </c>
-      <c r="C457" s="9" t="inlineStr">
+      <c r="C457" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -9760,7 +9760,7 @@
           <t>Рурукин А.Н. - Поурочные разработки по алгебре: 7 класс: к учебнику Ю.Н. Макарычева и др., 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C458" s="12" t="inlineStr">
+      <c r="C458" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -9780,7 +9780,7 @@
           <t>И. Е. Феоктистов - Алгебра. 7 класс. Дидактические материалы. Методические рекомендации, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C459" s="10" t="inlineStr">
+      <c r="C459" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -9980,7 +9980,7 @@
           <t>Ш.А. АЛИМОВ, А.Р. ХАЛМУХАМЕДОВ, М.А. МИРЗААХМЕДОВ - АЛГЕБРА. УЧЕБНИК ДЛЯ 9 КЛАССОВ ОБЩЕОБРАЗОВАТЕЛЬНЫХ ШКОЛ, 2019, ИЗДАТЕЛЬСКО-ПОЛИГРАФИЧЕСКИЙ ТВОРЧЕСКИЙ ДОМ «O‘QITUVCHI»</t>
         </is>
       </c>
-      <c r="C469" s="10" t="inlineStr">
+      <c r="C469" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10020,7 +10020,7 @@
           <t>М. И. Шабунин - Математика. Пособие для поступающих в вузы, 2016, Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C471" s="10" t="inlineStr">
+      <c r="C471" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -10080,7 +10080,7 @@
           <t>Н. Б. Мельникова, Г. А. Захарова - Дидактические материалы по геометрии, 2019, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C474" s="8" t="inlineStr">
+      <c r="C474" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10120,7 +10120,7 @@
           <t>Э.Н. Балаян - ГЕОМЕТРИЯ. Решебник к книге Э.Н. Балаяна ГЕОМЕТРИЯ. Задачи на готовых чертежах для подготовки к ОГЭ и ЕГЭ (7-9 классы). 9 класс, 2019, Феникс</t>
         </is>
       </c>
-      <c r="C476" s="10" t="inlineStr">
+      <c r="C476" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -10140,7 +10140,7 @@
           <t>Э.Н. Балаян - ГЕОМЕТРИЯ. Решебник к книге Э.Н. Балаяна ГЕОМЕТРИЯ. Задачи на готовых чертежах для подготовки к ОГЭ и ЕГЭ (7-9 классы). 7 класс, 2019, Феникс</t>
         </is>
       </c>
-      <c r="C477" s="10" t="inlineStr">
+      <c r="C477" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -10180,7 +10180,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили - КИМ ВПР. Алгебра. 7 класс. Контрольные измерительные материалы : Всероссийская проверочная работа. ФГОС, 2020, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C479" s="10" t="inlineStr">
+      <c r="C479" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -10200,7 +10200,7 @@
           <t>Е. В. Буцко - Подготовка к Всероссийским проверочным работам. Математика. 7 класс, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C480" s="8" t="inlineStr">
+      <c r="C480" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10220,7 +10220,7 @@
           <t>Вольфсон Г. И., Виноградова О. А. - Математика. Всероссийская проверочная работа. 7 класс. Типовые задания, 2020, Экзамен</t>
         </is>
       </c>
-      <c r="C481" s="8" t="inlineStr">
+      <c r="C481" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10240,7 +10240,7 @@
           <t>Т. М. Ерина - Рабочая тетрадь по математике. 6 класс. Часть 1, 2020, Экзамен</t>
         </is>
       </c>
-      <c r="C482" s="9" t="inlineStr">
+      <c r="C482" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -10260,7 +10260,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Контрольные работы по математике. 5 класс, 2020, Экзамен</t>
         </is>
       </c>
-      <c r="C483" s="9" t="inlineStr">
+      <c r="C483" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -10280,7 +10280,7 @@
           <t>В. Н. Рудницкая - Тесты по математике: 5 класс : к учебнику Н. Я. Виленкина и др. «Математика. 5 класс. В 2-х частях», 2020, Экзамен</t>
         </is>
       </c>
-      <c r="C484" s="9" t="inlineStr">
+      <c r="C484" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -10300,12 +10300,12 @@
           <t>Ш.А. АЛИМОВ, А.Р. ХАЛМУХАМЕДОВ, М.А. МИРЗААХМЕДОВ - АЛГЕБРА. УЧЕБНИК ДЛЯ 9 КЛАССОВ ОБЩЕОБРАЗОВАТЕЛЬНЫХ ШКОЛ, 2019, ИЗДАТЕЛЬСКО-ПОЛИГРАФИЧЕСКИЙ ТВОРЧЕСКИЙ ДОМ «O‘QITUVCHI»</t>
         </is>
       </c>
-      <c r="C485" s="10" t="inlineStr">
+      <c r="C485" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D485" s="14" t="n">
+      <c r="D485" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
           <t>Д.Т. Письменный - Конспект лекций по высшей математике, 2009, Айрис-пресс</t>
         </is>
       </c>
-      <c r="C487" s="12" t="inlineStr">
+      <c r="C487" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -10360,7 +10360,7 @@
           <t>А. Д. Мышкис - Лекции по высшей математике, 2007, Лань</t>
         </is>
       </c>
-      <c r="C488" s="8" t="inlineStr">
+      <c r="C488" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10440,7 +10440,7 @@
           <t>В. С. Герасимчук, Г.С. Васильченко, В.И. Кравцов - Курс классической математики в примерах и задачах. Часть III, 2009, ФИЗМАТЛИТ</t>
         </is>
       </c>
-      <c r="C492" s="8" t="inlineStr">
+      <c r="C492" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10480,7 +10480,7 @@
           <t>Романко В. К. - Курс дифференциальных уравнений и вариационного исчисления, 2001, Лаборатория Базовых Знаний</t>
         </is>
       </c>
-      <c r="C494" s="8" t="inlineStr">
+      <c r="C494" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10500,7 +10500,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Дидактические материалы. 7 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C495" s="10" t="inlineStr">
+      <c r="C495" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10520,7 +10520,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Алгебра. 8 класс. Самостоятельные и контрольные работы, 2017, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C496" s="10" t="inlineStr">
+      <c r="C496" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10540,7 +10540,7 @@
           <t>И. Е. Феоктистов - Алгебра. 8 класс. Дидактические материалы. Методические рекомендации, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C497" s="10" t="inlineStr">
+      <c r="C497" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10585,8 +10585,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D499" s="5" t="n">
-        <v>1</v>
+      <c r="D499" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -10820,7 +10820,7 @@
           <t>В.А. Любецкий - ОСНОВНЫЕ ПОНЯТИЯ ШКОЛЬНОЙ МАТЕМАТИКИ, 1987, Просвещение</t>
         </is>
       </c>
-      <c r="C511" s="8" t="inlineStr">
+      <c r="C511" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10840,7 +10840,7 @@
           <t>А.Х. Шахмейстер - Построение и преобразования графиков. Параметры. Часть 1. Линейные функции и уравнения, 2014, МЦНМО, Петроглиф, Виктория плюс</t>
         </is>
       </c>
-      <c r="C512" s="10" t="inlineStr">
+      <c r="C512" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10860,7 +10860,7 @@
           <t>А.Х. Шахмейстер - Построение графиков функций элементарными методами, 2011, Петроглиф, Виктория плюс, МЦНМО</t>
         </is>
       </c>
-      <c r="C513" s="10" t="inlineStr">
+      <c r="C513" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10880,7 +10880,7 @@
           <t>В.В. Мирошин - Решение задач с параметрами. Теория и практика, 2009, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C514" s="10" t="inlineStr">
+      <c r="C514" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -10900,7 +10900,7 @@
           <t>В. К. Егерев, В. В. Зайцев, Б. А. Кордемский, Т. Н. Маслова, И. Ф. Орловская, Р. И. Позойский, Г. С. Ряховская, М. И. Сканави, А. М. Суходский, Н. М. Федорова - Сборник задач по математике с решениями. 8–11 классы, 2012, ООО «Издательство Оникс»: ООО «Издательство «Мир и Образование»: ООО «Издательство Астрель»</t>
         </is>
       </c>
-      <c r="C515" s="8" t="inlineStr">
+      <c r="C515" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -10920,7 +10920,7 @@
           <t>Я. С. Бродский - Статистика. Вероятность. Комбинаторика, 2008, ООО «Издательство Оникс»: ООО «Издательство «Мир и Образование»</t>
         </is>
       </c>
-      <c r="C516" s="13" t="inlineStr">
+      <c r="C516" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -10965,7 +10965,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D518" s="14" t="n">
+      <c r="D518" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D520" s="14" t="n">
+      <c r="D520" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
           <t>Брагин В.Г., Грабовский А.И. - Все предметы школьной программы в схемах и таблицах. Алгебра. Геометрия, 1998, Олимп, ООО «Издательство АСТ-ЛТД»</t>
         </is>
       </c>
-      <c r="C526" s="8" t="inlineStr">
+      <c r="C526" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -11165,8 +11165,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D528" s="5" t="n">
-        <v>1</v>
+      <c r="D528" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -11180,7 +11180,7 @@
           <t>И. Я. Танатар - Геометрические преобразования графиков функций, 2012, МЦНМО</t>
         </is>
       </c>
-      <c r="C529" s="10" t="inlineStr">
+      <c r="C529" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11240,7 +11240,7 @@
           <t>В. С. Крамор - Готовимся к экзамену по математике: Учебное пособие, 2008, ООО «Издательство Оникс»: ООО «Издательство «Мир и Образование»</t>
         </is>
       </c>
-      <c r="C532" s="10" t="inlineStr">
+      <c r="C532" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -11300,7 +11300,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра : учебник для 7 класса общеобразовательных учебных заведений, 2016, Гимназия</t>
         </is>
       </c>
-      <c r="C535" s="10" t="inlineStr">
+      <c r="C535" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11440,7 +11440,7 @@
           <t>Л. А. Александрова - Алгебра. 9 класс. Самостоятельные работы, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C542" s="10" t="inlineStr">
+      <c r="C542" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11460,7 +11460,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Методические рекомендации. 9 класс, 2015, Просвещение</t>
         </is>
       </c>
-      <c r="C543" s="10" t="inlineStr">
+      <c r="C543" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11500,12 +11500,12 @@
           <t>Л. В. Кузнецова, С. Б. Суворова, Е. А. Бунимович, Т. В. Колесникова, Л. О. Рослова - Алгебра : сб. заданий для подготовки к итоговой аттестации в 9 кл., 2008, Просвещение</t>
         </is>
       </c>
-      <c r="C545" s="10" t="inlineStr">
+      <c r="C545" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D545" s="14" t="n">
+      <c r="D545" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11520,12 +11520,12 @@
           <t>Л. В. Кузнецова, Е. А. Бунимович, Б. П. Пигарев, С. Б. Суворова - Алгебра. Сборник заданий для проведения письменного экзамена по алгебре за курс основной школы. 9 класс, 2008, Дрофа</t>
         </is>
       </c>
-      <c r="C546" s="10" t="inlineStr">
+      <c r="C546" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D546" s="14" t="n">
+      <c r="D546" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
           <t>Л. Г. Петерсон, Л. А. Грушевская, М. А. Кубышева, М. В. Рогатова - Методические рекомендации к учебнику «Математика» 6 класс, 2015, Издательство «Ювента»</t>
         </is>
       </c>
-      <c r="C550" s="12" t="inlineStr">
+      <c r="C550" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -11620,7 +11620,7 @@
           <t>В.Н. Рудницкая - Математика. 6 класс: Рабочая тетрадь № 1 для контрольных работ, 2013, Экзамен</t>
         </is>
       </c>
-      <c r="C551" s="9" t="inlineStr">
+      <c r="C551" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -11640,7 +11640,7 @@
           <t>В.Н. Рудницкая - Математика. 6 класс. Рабочая тетрадь № 1. Обыкновенные дроби, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C552" s="9" t="inlineStr">
+      <c r="C552" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -11660,7 +11660,7 @@
           <t>Ю.П. Дудницын, В.Л. Кронгауз - Контрольные работы по математике: 6 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C553" s="9" t="inlineStr">
+      <c r="C553" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -11700,7 +11700,7 @@
           <t>А.Г. Рубин, П.В. Чулков - Алгебра. 7 класс, 2015, Баласс</t>
         </is>
       </c>
-      <c r="C555" s="10" t="inlineStr">
+      <c r="C555" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11720,7 +11720,7 @@
           <t>Л. Г. Петерсон - Программа курса алгебры для 7–9 классов, 2016, Ювента</t>
         </is>
       </c>
-      <c r="C556" s="10" t="inlineStr">
+      <c r="C556" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11880,7 +11880,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, И. Е. Феоктистов - Алгебра. 9 класс : учебное пособие для общеобразовательных организаций : углублённый уровень, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C564" s="10" t="inlineStr">
+      <c r="C564" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11900,7 +11900,7 @@
           <t>В.В. Локоть - Готовимся к ЕГЭ. Математика. Задачи с параметрами и их решения. Тригонометрия: уравнения, неравенства, системы. 10 класс, 2008, АРКТИ</t>
         </is>
       </c>
-      <c r="C565" s="10" t="inlineStr">
+      <c r="C565" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -11920,7 +11920,7 @@
           <t>А. Д. Блинков - Классические средние в арифметике и геометрии, 2012, МЦНМО</t>
         </is>
       </c>
-      <c r="C566" s="8" t="inlineStr">
+      <c r="C566" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -11940,7 +11940,7 @@
           <t>А.Х. Шахмейстер - Иррациональные уравнения и неравенства, 2011, Петроглиф : Виктория плюс : МЦНМО</t>
         </is>
       </c>
-      <c r="C567" s="10" t="inlineStr">
+      <c r="C567" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -11960,7 +11960,7 @@
           <t>Райхмист Р. Б. - Задачник по математике для учащихся средней школы и поступающих в вузы (с решениями и ответами): Учеб. пособие, 2007, Московский Лицей</t>
         </is>
       </c>
-      <c r="C568" s="8" t="inlineStr">
+      <c r="C568" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -11980,7 +11980,7 @@
           <t>В. В. Ткачук - МАТЕМАТИКА — АБИТУРИЕНТУ. Все о вступительных экзаменах в ВУЗы, 2007, Издательство МЦНМО</t>
         </is>
       </c>
-      <c r="C569" s="10" t="inlineStr">
+      <c r="C569" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -12000,7 +12000,7 @@
           <t>В. А. Битнер - Краткий курс школьной математики, 2007, Питер</t>
         </is>
       </c>
-      <c r="C570" s="8" t="inlineStr">
+      <c r="C570" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -12340,7 +12340,7 @@
           <t>А. Г. Мерзляк, Д. А. Номировский, В. М. Поляков - Математика: алгебра и начала математического анализа, геометрия. Геометрия. 10 класс. Углублённый уровень, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C587" s="8" t="inlineStr">
+      <c r="C587" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -12705,7 +12705,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D605" s="14" t="n">
+      <c r="D605" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12720,7 +12720,7 @@
           <t>А. Г. Мордкович, Л. А. Александрова, Т. Н. Мишустина, Е. Е. Тульчинская - Алгебра. 8 класс. В 2 ч. Ч. 2. Задачник для учащихся общеобразовательных учреждений, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C606" s="10" t="inlineStr">
+      <c r="C606" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -12920,7 +12920,7 @@
           <t>Судавная Ольга - Краткий справочник по математике для абитуриентов и студентов. Формулы, алгоритмы, примеры, 2013, Питер</t>
         </is>
       </c>
-      <c r="C616" s="10" t="inlineStr">
+      <c r="C616" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -13040,7 +13040,7 @@
           <t>Дмитрий Письменный - Конспект лекций по теории вероятностей, математической статистике и случайным процессам, 2008, Айрис-пресс</t>
         </is>
       </c>
-      <c r="C622" s="13" t="inlineStr">
+      <c r="C622" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -13060,7 +13060,7 @@
           <t>С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. Методические рекомендации. 8 класс, 2015, Просвещение</t>
         </is>
       </c>
-      <c r="C623" s="10" t="inlineStr">
+      <c r="C623" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13080,7 +13080,7 @@
           <t>С. С. Минаева - Алгебра. Устные упражнения. 8 класс, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C624" s="10" t="inlineStr">
+      <c r="C624" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13100,7 +13100,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Алгебра. Контрольные работы. 8 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C625" s="10" t="inlineStr">
+      <c r="C625" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -13120,7 +13120,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 8, ГІМНАЗІЯ</t>
         </is>
       </c>
-      <c r="C626" s="10" t="inlineStr">
+      <c r="C626" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13140,7 +13140,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Рабочая тетрадь по алгебре. Часть 1. 8 класс: к учебнику А.Г. Мордковича «Алгебра. 8 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C627" s="10" t="inlineStr">
+      <c r="C627" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13160,7 +13160,7 @@
           <t>М. Л. Галицкий, А. М. Гольдман, Л. И. Звавич - Сборник задач по алгебре. 8-9 классы, 2019, Просвещение</t>
         </is>
       </c>
-      <c r="C628" s="10" t="inlineStr">
+      <c r="C628" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13180,7 +13180,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Алгебра. Контрольные работы. 9 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C629" s="10" t="inlineStr">
+      <c r="C629" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -13200,7 +13200,7 @@
           <t>С. С. Минаева, Л. О. Рослова - Алгебра. Рабочая тетрадь. 9 класс. Часть 1, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C630" s="10" t="inlineStr">
+      <c r="C630" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13440,7 +13440,7 @@
           <t>Н. Б. Мельникова - Контрольные работы по геометрии: 7 класс: к учебнику А. В. Погорелова «Геометрия. 7–9 классы», 2020, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C642" s="10" t="inlineStr">
+      <c r="C642" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -13480,7 +13480,7 @@
           <t>А. Г. Мордкович - Алгебра. 8 класс. В двух частях. Часть 1. Учебник, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C644" s="10" t="inlineStr">
+      <c r="C644" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13520,12 +13520,12 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 5 класс, 2013, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C646" s="9" t="inlineStr">
+      <c r="C646" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D646" s="14" t="n">
+      <c r="D646" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13560,12 +13560,12 @@
           <t>Ш.А. АЛИМОВ, А.Р. ХАЛМУХАМЕДОВ, М.А. МИРЗААХМЕДОВ - АЛГЕБРА. УЧЕБНИК ДЛЯ 9 КЛАССОВ ОБЩЕОБРАЗОВАТЕЛЬНЫХ ШКОЛ, 2019, ИЗДАТЕЛЬСКО-ПОЛИГРАФИЧЕСКИЙ ТВОРЧЕСКИЙ ДОМ «O‘QITUVCHI»</t>
         </is>
       </c>
-      <c r="C648" s="10" t="inlineStr">
+      <c r="C648" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D648" s="14" t="n">
+      <c r="D648" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
           <t>И. Г. Арефьева, О. Н. Пирютко - АЛГЕБРА. Учебное пособие для 9 класса учреждений общего среднего образования с русским языком обучения, 2019, Народная асвета</t>
         </is>
       </c>
-      <c r="C649" s="10" t="inlineStr">
+      <c r="C649" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13600,7 +13600,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Рабочая тетрадь по алгебре. 9 класс: к учебнику Ю. Н. Макарычева и др. «Алгебра. 9 класс», 2019, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C650" s="10" t="inlineStr">
+      <c r="C650" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13620,7 +13620,7 @@
           <t>Ш. А. Алимов, О. Р. Холмухамедов, М. А. Мирзаахмедов - Алгебра: учебник для 8 классов средних общеобразовательных школ, 2019, Издательско-полиграфический творческий дом "O‘qituvchi"</t>
         </is>
       </c>
-      <c r="C651" s="10" t="inlineStr">
+      <c r="C651" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13640,7 +13640,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Универсальные учебные действия. Рабочая тетрадь по алгебре: 7 класс: к учебнику Ю. Н. Макарычева и др. «Алгебра. 7 класс». ФГОС (к новому учебнику), 2019, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C652" s="10" t="inlineStr">
+      <c r="C652" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -13660,7 +13660,7 @@
           <t>Жохов В. И. - Математический тренажёр. 6 класс: пособие для учителей и учащихся, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C653" s="9" t="inlineStr">
+      <c r="C653" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -13680,7 +13680,7 @@
           <t>О. Н. Пирютко, О. А. Терешко, В. Д. Герасимов - Сборник задач по математике, 2019, Адукацыя і выхаванне</t>
         </is>
       </c>
-      <c r="C654" s="9" t="inlineStr">
+      <c r="C654" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -13700,7 +13700,7 @@
           <t>&lt;авторы&gt; - &lt;название&gt;, &lt;год&gt;, &lt;издательство&gt;</t>
         </is>
       </c>
-      <c r="C655" s="13" t="inlineStr">
+      <c r="C655" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -13840,7 +13840,7 @@
           <t>М. И. Башмаков - МАТЕМАТИКА. СБОРНИК ЗАДАЧ ПРОФИЛЬНОЙ НАПРАВЛЕННОСТИ, 2013, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C662" s="8" t="inlineStr">
+      <c r="C662" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -13860,7 +13860,7 @@
           <t>Л.П. СТОЙЛОВА - МАТЕМАТИКА, 2002, Академия</t>
         </is>
       </c>
-      <c r="C663" s="8" t="inlineStr">
+      <c r="C663" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -13880,7 +13880,7 @@
           <t>А. В. СПИВАК - ТЫСЯЧА И ОДНА ЗАДАЧА ПО МАТЕМАТИКЕ, 2002, ПРОСВЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C664" s="8" t="inlineStr">
+      <c r="C664" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -13920,7 +13920,7 @@
           <t>А. Лопатина, М. Скребцова - СКАЗОЧНАЯ МАТЕМАТИКА, 2009, Амрита-Русь</t>
         </is>
       </c>
-      <c r="C666" s="11" t="inlineStr">
+      <c r="C666" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -13940,7 +13940,7 @@
           <t>Экспресс-курсы по определению времени. Который час?, Технологии Буракова</t>
         </is>
       </c>
-      <c r="C667" s="8" t="inlineStr">
+      <c r="C667" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -13960,7 +13960,7 @@
           <t>Технологии Бурaкова - Экспресс-курсы по обучению счёту. Я считаю до 100</t>
         </is>
       </c>
-      <c r="C668" s="8" t="inlineStr">
+      <c r="C668" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -13980,7 +13980,7 @@
           <t>Экспресс-курсы по обучению счёту. Сложение и вычитание в пределах 10, Технологии Буракова</t>
         </is>
       </c>
-      <c r="C669" s="8" t="inlineStr">
+      <c r="C669" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14000,7 +14000,7 @@
           <t>Семенов А.Л., Ященко И.В., Рослова Л.О., Кузнецова Л.В., Суворова С.Б., Трепалин А.С., Захаров П.И., Смирнов В.А., Высоцкий И.Р. - ГИА: 3000 задач с ответами по математике. Все задания части 1 «Закрытый сегмент», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C670" s="10" t="inlineStr">
+      <c r="C670" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -14040,7 +14040,7 @@
           <t>И.Д. ПЕХЛЕЦКИЙ - МАТЕМАТИКА. Учебник, 2014, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C672" s="8" t="inlineStr">
+      <c r="C672" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14060,7 +14060,7 @@
           <t>В.П. Омельченко, Э.В. Курбатова - Математика, 2011, Феникс</t>
         </is>
       </c>
-      <c r="C673" s="8" t="inlineStr">
+      <c r="C673" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14080,7 +14080,7 @@
           <t>М. Я. Выгодский - Справочник по элементарной математике</t>
         </is>
       </c>
-      <c r="C674" s="8" t="inlineStr">
+      <c r="C674" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14100,7 +14100,7 @@
           <t>А. Г. Цыпкин, А. И. Пинский - Справочник по методам решения задач по математике для средней школы, 1989, Наука. Главная редакция физико-математической литературы</t>
         </is>
       </c>
-      <c r="C675" s="8" t="inlineStr">
+      <c r="C675" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14320,7 +14320,7 @@
           <t>Л.И. Майсеня - Справочник по математике. Основные понятия и формулы, 2012, Вышэйшая школа</t>
         </is>
       </c>
-      <c r="C686" s="8" t="inlineStr">
+      <c r="C686" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14400,7 +14400,7 @@
           <t>Севрюков П. Ф., Смоляков А. Н. - Уравнения и неравенства с модулями и методика их решения, 2005, Илекса, Народное образование, Сервисшкола</t>
         </is>
       </c>
-      <c r="C690" s="8" t="inlineStr">
+      <c r="C690" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14420,7 +14420,7 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 5 класс. Методическое пособие, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C691" s="12" t="inlineStr">
+      <c r="C691" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -14440,7 +14440,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Математика. 5 кл., 2014, Дрофа</t>
         </is>
       </c>
-      <c r="C692" s="9" t="inlineStr">
+      <c r="C692" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14460,7 +14460,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Математика. 5 класс. Рабочая тетрадь. Часть 1, 2019, Дрофа</t>
         </is>
       </c>
-      <c r="C693" s="9" t="inlineStr">
+      <c r="C693" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14480,7 +14480,7 @@
           <t>Найма Гахраманова, Фамиль Гусейнов - МАТЕМАТИКА 5, 2018, Radius</t>
         </is>
       </c>
-      <c r="C694" s="9" t="inlineStr">
+      <c r="C694" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14500,7 +14500,7 @@
           <t>В. Д. Герасимов, О. Н. Пирютко, А. П. Лобанов - Математика. Учебное пособие для 5 класса учреждений общего среднего образования с русским языком обучения. В 2 частях. Часть 1, 2017, Адукацыя і выхаванне</t>
         </is>
       </c>
-      <c r="C695" s="9" t="inlineStr">
+      <c r="C695" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14520,12 +14520,12 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 5 класса учреждений общего среднего образования с русским языком обучения. В 2 частях. Часть 1, 2013, «Адукацыя і выхаванне»</t>
         </is>
       </c>
-      <c r="C696" s="9" t="inlineStr">
+      <c r="C696" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D696" s="14" t="n">
+      <c r="D696" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
           <t>Т.А. Алдамуратова, К.С. Байшоланова, Е.С. Байшоланов - Математика. В двух частях. Часть 1. Учебник для 5 класса общеобразовательной школы, 2017, Атамұра</t>
         </is>
       </c>
-      <c r="C697" s="9" t="inlineStr">
+      <c r="C697" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14560,7 +14560,7 @@
           <t>Н. Я. Виленкин, О. С. Ивашев-Мусатов, С. И. Шварцбурд - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 11 класс : учебник для учащихся общеобразовательных организаций : углублённый уровень, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C698" s="8" t="inlineStr">
+      <c r="C698" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14580,7 +14580,7 @@
           <t>Е. В. Буцко, А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 10 класс. Базовый уровень. Методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C699" s="12" t="inlineStr">
+      <c r="C699" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -14600,7 +14600,7 @@
           <t>Е. В. Буцко, А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 11 класс. Базовый уровень. Методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C700" s="12" t="inlineStr">
+      <c r="C700" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -14620,7 +14620,7 @@
           <t>Е. В. Буцко, А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика : алгебра и начала математического анализа. Углублённый уровень : 10 класс : методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C701" s="12" t="inlineStr">
+      <c r="C701" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -14640,7 +14640,7 @@
           <t>Хорошавина С.Г. - Шпаргалка по математике, 2012, Феникс</t>
         </is>
       </c>
-      <c r="C702" s="8" t="inlineStr">
+      <c r="C702" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14660,7 +14660,7 @@
           <t>О. А. Филатов - Шпаргалки по алгебре и геометрии, 2011, Издательский Дом «Литера»</t>
         </is>
       </c>
-      <c r="C703" s="8" t="inlineStr">
+      <c r="C703" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14800,7 +14800,7 @@
           <t>Б. К. Хайдаров - МАТЕМАТИКА 5, 2015, YANGIYO'L POLIGRAF SERVIS</t>
         </is>
       </c>
-      <c r="C710" s="9" t="inlineStr">
+      <c r="C710" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -14820,12 +14820,12 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - МАТЕМАТИКА 5 класс, 2018, «Гимназия»</t>
         </is>
       </c>
-      <c r="C711" s="9" t="inlineStr">
+      <c r="C711" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D711" s="14" t="n">
+      <c r="D711" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Алгебра. 8 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C712" s="10" t="inlineStr">
+      <c r="C712" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -14860,7 +14860,7 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Математика. Алгебра и геометрия. Учебник для 8 класса общеобразовательных организаций, 2019, Русское слово</t>
         </is>
       </c>
-      <c r="C713" s="8" t="inlineStr">
+      <c r="C713" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -14880,12 +14880,12 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Математика. Алгебра и геометрия. Учебник для 8 класса общеобразовательных организаций, 2019, Русское слово</t>
         </is>
       </c>
-      <c r="C714" s="8" t="inlineStr">
+      <c r="C714" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D714" s="14" t="n">
+      <c r="D714" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
           <t>Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева и др. - Алгебра. 9 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C716" s="10" t="inlineStr">
+      <c r="C716" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -14940,7 +14940,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Алгебра. 9 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C717" s="10" t="inlineStr">
+      <c r="C717" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -14960,7 +14960,7 @@
           <t>Ю. П. Дудницын, Е. Е. Тульчинская - Алгебра, 7 класс. Контрольные работы: учебное пособие для общеобразовательных учреждений, 2006, Мнемозина</t>
         </is>
       </c>
-      <c r="C718" s="10" t="inlineStr">
+      <c r="C718" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -14980,7 +14980,7 @@
           <t>И. И. Зубарева, М. С. Мильштейн - Алгебра. 7 класс. Рабочая тетрадь № 1, 2012, Мнемозина</t>
         </is>
       </c>
-      <c r="C719" s="10" t="inlineStr">
+      <c r="C719" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15000,7 +15000,7 @@
           <t>Мордкович А.Г., Николаев Н.П. - Алгебра. 7 класс. В 2 ч. Ч. 1. Учебник для учащихся общеобразовательных учреждений, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C720" s="10" t="inlineStr">
+      <c r="C720" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15020,7 +15020,7 @@
           <t>Мордкович А. Г., Николаев Н. П. - Алгебра. 7 класс. В 2 ч. Ч. 2. Задачник для учащихся общеобразовательных учреждений, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C721" s="10" t="inlineStr">
+      <c r="C721" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15040,7 +15040,7 @@
           <t>А. Г. Мордкович - Алгебра. 7—9 классы. Контрольные работы для учащихся общеобразовательных учреждений : к учебникам А. Г. Мордковича, Н. П. Николаева, 2011, Мнемозина</t>
         </is>
       </c>
-      <c r="C722" s="10" t="inlineStr">
+      <c r="C722" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15060,7 +15060,7 @@
           <t>Г. К. Муравин, К. С. Муравин, О. В. Муравина - Алгебра. 7 класс, 2013, Дрофа</t>
         </is>
       </c>
-      <c r="C723" s="10" t="inlineStr">
+      <c r="C723" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15080,7 +15080,7 @@
           <t>Л. Г. Петерсон, Д. Л. Абраров, Е. В. Чуткова - Математика. Алгебра. Функции. Анализ данных. Учебник для 7 класса. Часть 1, 2011, Ювента</t>
         </is>
       </c>
-      <c r="C724" s="10" t="inlineStr">
+      <c r="C724" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15100,7 +15100,7 @@
           <t>Севда Исмаилова - МАТЕМАТИКА 7, 2018, ŞƏRQ-QƏRB</t>
         </is>
       </c>
-      <c r="C725" s="8" t="inlineStr">
+      <c r="C725" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -15116,7 +15116,7 @@
         </is>
       </c>
       <c r="B726" s="3" t="inlineStr"/>
-      <c r="C726" s="10" t="inlineStr">
+      <c r="C726" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15136,7 +15136,7 @@
           <t>А. Н. Шыныбеков, Д. А. Шыныбеков - Алгебра. Учебник для 7 класса общеобразовательной школы, 2017, Атамұра</t>
         </is>
       </c>
-      <c r="C727" s="10" t="inlineStr">
+      <c r="C727" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15156,7 +15156,7 @@
           <t>Ш. А. АЛИМОВ, А. Р. ХОЛМУХАМЕДОВ, М. А. МИРЗААХМЕДОВ - АЛГЕБРА: Учебник для 7 классов школ общего среднего образования, 2017, ИЗДАТЕЛЬСКО-ПОЛИГРАФИЧЕСКИЙ ТВОРЧЕСКИЙ ДОМ „O‘QITUVCHI“</t>
         </is>
       </c>
-      <c r="C728" s="10" t="inlineStr">
+      <c r="C728" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15181,8 +15181,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D729" s="14" t="n">
-        <v>2</v>
+      <c r="D729" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="730">
@@ -15216,7 +15216,7 @@
           <t>Т.М. Ерина - Рабочая тетрадь по математике. Часть 1. 5 класс. К учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 5 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C731" s="10" t="inlineStr">
+      <c r="C731" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -15276,7 +15276,7 @@
           <t>Ивченко Григорий Иванович, Медведев Юрий Иванович - Введение в математическую статистику, 2010, Издательство ЛКИ</t>
         </is>
       </c>
-      <c r="C734" s="13" t="inlineStr">
+      <c r="C734" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -15396,7 +15396,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухова - Математика. 5 класс. Тематические тесты. Промежуточная аттестация, 2012, Легион</t>
         </is>
       </c>
-      <c r="C740" s="10" t="inlineStr">
+      <c r="C740" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -15416,7 +15416,7 @@
           <t>Н. Я. Виленкин, В. И. Жохов, А. С. Чесноков, С. И. Шварцбурд - Математика. 6 класс : учебник для общеобразовательных учреждений, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C741" s="9" t="inlineStr">
+      <c r="C741" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15436,7 +15436,7 @@
           <t>В. И. Жохов, Л. Б. Крайнева - Математика. 6 класс. Контрольные работы для учащихся общеобразовательных учреждений, 2011, Мнемозина</t>
         </is>
       </c>
-      <c r="C742" s="9" t="inlineStr">
+      <c r="C742" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15456,7 +15456,7 @@
           <t>И. И. Зубарева - Математика. 6 класс. Рабочая тетрадь № 1, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C743" s="9" t="inlineStr">
+      <c r="C743" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15476,7 +15476,7 @@
           <t>И. И. Зубарева, И. П. Лепешонкова - Математика. 6 класс. Тетрадь для контрольных работ № 1, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C744" s="9" t="inlineStr">
+      <c r="C744" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15496,7 +15496,7 @@
           <t>Е. Е. Тульчинская - Математика. 6 класс. Блицопрос, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C745" s="9" t="inlineStr">
+      <c r="C745" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15516,7 +15516,7 @@
           <t>И. И. Зубарева, А. Г. Мордкович - Математика. 5-6 классы. Методическое пособие для учителя, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C746" s="12" t="inlineStr">
+      <c r="C746" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -15536,7 +15536,7 @@
           <t>Е.В. Ромашкова - ФУНКЦИИ И ГРАФИКИ В 8-11 КЛАССАХ, 2011, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C747" s="8" t="inlineStr">
+      <c r="C747" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -15556,12 +15556,12 @@
           <t>Е.В. Ромашкова - ФУНКЦИИ И ГРАФИКИ В 8-11 КЛАССАХ, 2011, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C748" s="8" t="inlineStr">
+      <c r="C748" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D748" s="14" t="n">
+      <c r="D748" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15576,12 +15576,12 @@
           <t>Е.В. Ромашкова - ФУНКЦИИ И ГРАФИКИ В 8-11 КЛАССАХ, 2011, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C749" s="8" t="inlineStr">
+      <c r="C749" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D749" s="14" t="n">
+      <c r="D749" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
           <t>В.М. БРАДИС - ЧЕТЫРЕХЗНАЧНЫЕ МАТЕМАТИЧЕСКИЕ ТАБЛИЦЫ, 2010, ДРОФА</t>
         </is>
       </c>
-      <c r="C750" s="8" t="inlineStr">
+      <c r="C750" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -15656,7 +15656,7 @@
           <t>В. С. БЕЛОНОСОВ, М. В. ФОКИН - ЗАДАЧИ ВСТУПИТЕЛЬНЫХ ЭКЗАМЕНОВ ПО МАТЕМАТИКЕ, 2005, СИБИРСКОЕ УНИВЕРСИТЕТСКОЕ ИЗДАТЕЛЬСТВО</t>
         </is>
       </c>
-      <c r="C753" s="10" t="inlineStr">
+      <c r="C753" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -15676,7 +15676,7 @@
           <t>А.С. Бортаковский, В.М. Закалюкин - Задачи повышенной сложности по математике для абитуриентов, 2006, Издательство МАИ</t>
         </is>
       </c>
-      <c r="C754" s="10" t="inlineStr">
+      <c r="C754" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -15696,7 +15696,7 @@
           <t>А.Х. Шахмейстер - Тригонометрия, 2014, Петроглиф, МЦНМО, ИД КДУ</t>
         </is>
       </c>
-      <c r="C755" s="10" t="inlineStr">
+      <c r="C755" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15756,7 +15756,7 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 7 класс. Методическое пособие, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C758" s="10" t="inlineStr">
+      <c r="C758" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15776,7 +15776,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Рабочая тетрадь. 7 класс. Часть 1, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C759" s="10" t="inlineStr">
+      <c r="C759" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15796,12 +15796,12 @@
           <t>А. П. Ершова, В. В. Голобородько, А. С. Ершова - САМОСТОЯТЕЛЬНЫЕ И КОНТРОЛЬНЫЕ РАБОТЫ ПО АЛГЕБРЕ И ГЕОМЕТРИИ ДЛЯ 8 КЛАССА, 2004, «ИЛЕКСА», «ГИМНАЗИЯ»</t>
         </is>
       </c>
-      <c r="C760" s="9" t="inlineStr">
+      <c r="C760" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D760" s="14" t="n">
+      <c r="D760" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15816,12 +15816,12 @@
           <t>А. П. Ершова, В. В. Голобородько, А. С. Ершова - САМОСТОЯТЕЛЬНЫЕ И КОНТРОЛЬНЫЕ РАБОТЫ ПО АЛГЕБРЕ И ГЕОМЕТРИИ ДЛЯ 8 КЛАССА, 2004, «ИЛЕКСА», «ГИМНАЗИЯ»</t>
         </is>
       </c>
-      <c r="C761" s="9" t="inlineStr">
+      <c r="C761" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D761" s="14" t="n">
+      <c r="D761" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15836,7 +15836,7 @@
           <t>Сферы. Математика. Арифметика. Геометрия. 5 класс. Задачник, Просвещение</t>
         </is>
       </c>
-      <c r="C762" s="9" t="inlineStr">
+      <c r="C762" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15856,7 +15856,7 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Текущий и итоговый контроль по курсу «Математика». 6 класс: контрольно-измерительные материалы, 2015, Русское слово</t>
         </is>
       </c>
-      <c r="C763" s="10" t="inlineStr">
+      <c r="C763" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -15876,7 +15876,7 @@
           <t>Е. В. Буцко, А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика. 6 класс. Методическое пособие, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C764" s="12" t="inlineStr">
+      <c r="C764" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -15896,7 +15896,7 @@
           <t>СЕВДА ИСМАЙЫЛОВА, АРЗУ ГУСЕЙНОВА - МАТЕМАТИКА 6. УЧЕБНИК, 2018, ŞƏRQ-QƏRB</t>
         </is>
       </c>
-      <c r="C765" s="9" t="inlineStr">
+      <c r="C765" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15916,7 +15916,7 @@
           <t>В. Д. Герасимов, О. Н. Пирютко - Математика. Учебное пособие для 6 класса учреждений общего среднего образования с русским языком обучения, 2018, Адукацыя і выхаванне</t>
         </is>
       </c>
-      <c r="C766" s="9" t="inlineStr">
+      <c r="C766" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15936,7 +15936,7 @@
           <t>Т.А. Алдамұратова, К.С. Байшоланова, Е.С. Байшоланов - Математика. Учебник для 6 класса общеобразовательной школы. Часть 1, 2018, Атамұра</t>
         </is>
       </c>
-      <c r="C767" s="9" t="inlineStr">
+      <c r="C767" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15956,7 +15956,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика, 2014, Гимназия</t>
         </is>
       </c>
-      <c r="C768" s="9" t="inlineStr">
+      <c r="C768" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -15976,7 +15976,7 @@
           <t>Ш. А. Алимов, Ю. М. Колягин, Ю. В. Сидоров, М. В. Ткачева, Н. Е. Федорова, М. И. Шабунин - Алгебра. 7 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C769" s="10" t="inlineStr">
+      <c r="C769" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -15996,7 +15996,7 @@
           <t>Г. В. Дорофеев, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. 7 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C770" s="10" t="inlineStr">
+      <c r="C770" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -16076,7 +16076,7 @@
           <t>В. И. Ахременкова - Математика. 5 класс. Рабочая тетрадь для контрольных работ: к учебнику Г. В. Дорофеева, Л. Г. Петерсон «Математика. 5 класс», 2020, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C774" s="10" t="inlineStr">
+      <c r="C774" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -16096,7 +16096,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Тематические тесты. 5 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C775" s="10" t="inlineStr">
+      <c r="C775" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -16116,7 +16116,7 @@
           <t>И. И. Зубарева, А. Г. Мордкович - Математика. 5 класс, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C776" s="9" t="inlineStr">
+      <c r="C776" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16136,7 +16136,7 @@
           <t>И. И. Зубарева - Математика. 5 класс. Рабочая тетрадь № 1, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C777" s="9" t="inlineStr">
+      <c r="C777" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16156,7 +16156,7 @@
           <t>Тульчинская Е. Е. - Математика. Тесты. 5–6 классы, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C778" s="10" t="inlineStr">
+      <c r="C778" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -16196,7 +16196,7 @@
           <t>Э.Н. Балаян - ГЕОМЕТРИЯ. Лучшие задачи на готовых чертежах для подготовки к ГИА и ЕГЭ. 7-11 классы, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C780" s="10" t="inlineStr">
+      <c r="C780" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -16236,7 +16236,7 @@
           <t>Ю.М. Данилов, Л.Н. Журбенко, Г.А. Никонова, Н.В. Никонова, С.Н. Нуриева - МАТЕМАТИКА: Учебное пособие, 2009, ИНФРА-М</t>
         </is>
       </c>
-      <c r="C782" s="8" t="inlineStr">
+      <c r="C782" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -16256,7 +16256,7 @@
           <t>С.Г. Григорьев, С.В. Иволгина - Математика, 2015, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C783" s="8" t="inlineStr">
+      <c r="C783" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -16276,12 +16276,12 @@
           <t>Н.В. Богомолов, П.И. Самойленко - МАТЕМАТИКА, 2010, Дрофа</t>
         </is>
       </c>
-      <c r="C784" s="8" t="inlineStr">
+      <c r="C784" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D784" s="14" t="n">
+      <c r="D784" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16376,7 +16376,7 @@
           <t>И.И. Баврин - Сборник задач и занимательных упражнений по математике, 5-9 классы, 2013, ВЛАДОС</t>
         </is>
       </c>
-      <c r="C789" s="11" t="inlineStr">
+      <c r="C789" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -16521,7 +16521,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D796" s="14" t="n">
+      <c r="D796" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
           <t>Ершова А.П., Голобородько В.В., Крижановский А.Ф. - Тетрадь-конспект по геометрии для 10 класса, 2012, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C799" s="12" t="inlineStr">
+      <c r="C799" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -16596,7 +16596,7 @@
           <t>Ершова А.П., Голобородько В.В., Крижановский А.Ф. - Тетрадь-конспект по геометрии: 11 класс (по учебнику Л.С. Атанасяна и др.), 2014, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C800" s="12" t="inlineStr">
+      <c r="C800" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -16636,7 +16636,7 @@
           <t>Г. И. Просветов - МАТЕМАТИКА ДЛЯ ГУМАНИТАРИЕВ: ЗАДАЧИ И РЕШЕНИЯ, 2008, Альфа-Пресс</t>
         </is>
       </c>
-      <c r="C802" s="8" t="inlineStr">
+      <c r="C802" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -16656,7 +16656,7 @@
           <t>Бабайцев В.А., Браилов А.В., Солодовников А.С. - Математика в экономике. Теория вероятностей: Курс лекций, 2002, Финансовая академия</t>
         </is>
       </c>
-      <c r="C803" s="13" t="inlineStr">
+      <c r="C803" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -16676,7 +16676,7 @@
           <t>Т. М. Ерина - Рабочая тетрадь по математике. 5 класс. Часть 1. К учебнику С. М. Никольского и др. «Математика. 5 класс», 2018, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C804" s="9" t="inlineStr">
+      <c r="C804" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16696,7 +16696,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 5 класс. Рабочая тетрадь № 1, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C805" s="9" t="inlineStr">
+      <c r="C805" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16716,7 +16716,7 @@
           <t>Беленкова Е.Ю., Лебединцева Е.А. - МАТЕМАТИКА. 6 класс. Тетрадь 1. Задания для обучения и развития учащихся, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C806" s="9" t="inlineStr">
+      <c r="C806" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16736,7 +16736,7 @@
           <t>Т.М. Ерина - Рабочая тетрадь по математике. Часть 1. 6 класс. К учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 6 класс», 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C807" s="9" t="inlineStr">
+      <c r="C807" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -16756,7 +16756,7 @@
           <t>В.М. Финкельштейн - ЧТО ДЕЛАТЬ, КОГДА РЕШИТЬ ЗАДАЧУ НЕ УДАЕТСЯ, 2008, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C808" s="8" t="inlineStr">
+      <c r="C808" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17056,7 +17056,7 @@
           <t>О.В. Узорова, Е.А. Нефёдова - Полный курс математики: все типы заданий, все виды задач, примеров, уравнений, неравенств, все контрольные работы, все виды тестов: 4-й класс, 2016, Издательство АСТ : Астрель</t>
         </is>
       </c>
-      <c r="C823" s="8" t="inlineStr">
+      <c r="C823" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17076,7 +17076,7 @@
           <t>Кэрен Брайант-Моул - ПРОСТЫЕ И ДЕСЯТИЧНЫЕ ДРОБИ</t>
         </is>
       </c>
-      <c r="C824" s="8" t="inlineStr">
+      <c r="C824" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17096,7 +17096,7 @@
           <t>Андрей Багманов, Александра Солдатова - Экзамен по математике без репетитора. Практикум абитуриента, 2004, БХВ-Петербург</t>
         </is>
       </c>
-      <c r="C825" s="10" t="inlineStr">
+      <c r="C825" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -17116,7 +17116,7 @@
           <t>С. Г. Гиндикин - РАССКАЗЫ О ФИЗИКАХ И МАТЕМАТИКАХ, 2006, Издательство МЦНМО</t>
         </is>
       </c>
-      <c r="C826" s="11" t="inlineStr">
+      <c r="C826" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -17156,7 +17156,7 @@
           <t>Н. Б. Алфутова, Ю. Е. Егоров, А. В. Устинов - 18 × 18. Вступительные задачи ФМШ при МГУ, 2017, МЦНМО</t>
         </is>
       </c>
-      <c r="C828" s="8" t="inlineStr">
+      <c r="C828" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17216,7 +17216,7 @@
           <t>М. Я. Кельберт, Ю. М. Сухов - Вероятность и статистика в примерах и задачах. Том I. Основные понятия теории вероятностей и математической статистики, 2007, Издательство МЦНМО</t>
         </is>
       </c>
-      <c r="C831" s="13" t="inlineStr">
+      <c r="C831" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17236,7 +17236,7 @@
           <t>А. Н. Ширяев, И. Г. Эрлих, П. А. Яськов - Вероятность в теоремах и задачах (с доказательствами и решениями) Книга 1, 2014, МЦНМО</t>
         </is>
       </c>
-      <c r="C832" s="13" t="inlineStr">
+      <c r="C832" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17276,7 +17276,7 @@
           <t>С. Н. Старков - Справочник по математическим формулам и графикам функций для студентов, 2009, Питер</t>
         </is>
       </c>
-      <c r="C834" s="8" t="inlineStr">
+      <c r="C834" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17316,7 +17316,7 @@
           <t>Александрова Л. А. - Алгебра. 9 класс. Контрольные работы для учащихся общеобразовательных учреждений, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C836" s="10" t="inlineStr">
+      <c r="C836" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17336,7 +17336,7 @@
           <t>Ю. П. Дудницын, Е. Е. Тульчинская - Алгебра. 9 класс. Контрольные работы для общеобразовательных учреждений, 2005, Мнемозина</t>
         </is>
       </c>
-      <c r="C837" s="10" t="inlineStr">
+      <c r="C837" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17356,7 +17356,7 @@
           <t>Е. Е. Тульчинская - Алгебра. 9 класс. Блицопрос, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C838" s="10" t="inlineStr">
+      <c r="C838" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17376,7 +17376,7 @@
           <t>А. Г. Мордкович, П. В. Семенов - Алгебра. 9 класс. Методическое пособие для учителя, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C839" s="10" t="inlineStr">
+      <c r="C839" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17396,7 +17396,7 @@
           <t>Л. А. Александрова - Алгебра. 9 класс. Тематические проверочные работы в новой форме, 2012, Мнемозина</t>
         </is>
       </c>
-      <c r="C840" s="10" t="inlineStr">
+      <c r="C840" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17416,7 +17416,7 @@
           <t>А. Г. Мордкович, Е. Е. Тульчинская - Алгебра. 7—9 классы. Тесты для учащихся общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C841" s="10" t="inlineStr">
+      <c r="C841" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17436,7 +17436,7 @@
           <t>А. Г. Мордкович, П. В. Семенов - События. Вероятности. Статистическая обработка данных. Дополнительные параграфы к курсу алгебры 7–9 классов общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C842" s="13" t="inlineStr">
+      <c r="C842" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17456,7 +17456,7 @@
           <t>МАТЕМАТИКА 9</t>
         </is>
       </c>
-      <c r="C843" s="8" t="inlineStr">
+      <c r="C843" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17496,7 +17496,7 @@
           <t>Математика : 5—6 классы : базовый уровень : методическое пособие к предметной линии учебников по математике Н. Я. Виленкина, В. И. Жохова, А. С. Чеснокова и др., 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C845" s="12" t="inlineStr">
+      <c r="C845" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -17516,7 +17516,7 @@
           <t>Математика. 5 класс. Базовый уровень. Учебник. Часть 1, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C846" s="9" t="inlineStr">
+      <c r="C846" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -17536,7 +17536,7 @@
           <t>М. В. Ткачёва - Математика. 5 класс. Базовый уровень. Рабочая тетрадь. Часть 1, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C847" s="9" t="inlineStr">
+      <c r="C847" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -17556,7 +17556,7 @@
           <t>Л. Б. Крайнева - Математика : 5-й класс : базовый уровень : контрольные работы : учебное пособие, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C848" s="9" t="inlineStr">
+      <c r="C848" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -17576,7 +17576,7 @@
           <t>Математика. Алгебра. 7–9 классы. Базовый уровень. Методическое пособие к предметной линии учебников по алгебре Ю. Н. Макарычева, Н. Г. Миндюк, К. И. Нешкова и др., 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C849" s="10" t="inlineStr">
+      <c r="C849" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17636,7 +17636,7 @@
           <t>Г.У. Мынбаева, И.Г. Дмитриев, В.З. Борисов, А.С. Саввин - ТЕОРИЯ ВЕРОЯТНОСТЕЙ В ПРИМЕРАХ И ЗАДАЧАХ, 2005, Вузовская книга</t>
         </is>
       </c>
-      <c r="C852" s="13" t="inlineStr">
+      <c r="C852" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17656,7 +17656,7 @@
           <t>Е. С. Кочетков, С. О. Смерчинская - ТЕОРИЯ ВЕРОЯТНОСТЕЙ в задачах и упражнениях, 2008, ФОРУМ</t>
         </is>
       </c>
-      <c r="C853" s="13" t="inlineStr">
+      <c r="C853" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17676,7 +17676,7 @@
           <t>В.В. Афанасьев - Теория вероятностей, 2007, ВЛАДОС</t>
         </is>
       </c>
-      <c r="C854" s="13" t="inlineStr">
+      <c r="C854" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17696,7 +17696,7 @@
           <t>М. С. Спирина, П. А. Спирин - Теория вероятностей и математическая статистика, 2011, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C855" s="13" t="inlineStr">
+      <c r="C855" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17716,7 +17716,7 @@
           <t>Р. И. Ивановский - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА. ОСНОВЫ, ПРИКЛАДНЫЕ АСПЕКТЫ С ПРИМЕРАМИ И ЗАДАЧАМИ В СРЕДЕ Mathcad, 2008, БХВ-Петербург</t>
         </is>
       </c>
-      <c r="C856" s="13" t="inlineStr">
+      <c r="C856" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17736,7 +17736,7 @@
           <t>Е.Н. Гусева - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА, 2011, ФЛИНТА</t>
         </is>
       </c>
-      <c r="C857" s="13" t="inlineStr">
+      <c r="C857" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17756,7 +17756,7 @@
           <t>Л. Л. Гладков, Г. А. Гладкова - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА, 2013, РИПО</t>
         </is>
       </c>
-      <c r="C858" s="13" t="inlineStr">
+      <c r="C858" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -17776,7 +17776,7 @@
           <t>В.В. Колесов, М.Н. Романов - Элементарное введение в высшую математику, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C859" s="8" t="inlineStr">
+      <c r="C859" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -17796,13 +17796,13 @@
           <t>Мордкович А.Г., Николаев Н.П. - Алгебра. 7 класс. В 2 ч. Ч. 1. Учебник для учащихся общеобразовательных учреждений, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C860" s="10" t="inlineStr">
+      <c r="C860" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D860" s="14" t="n">
-        <v>2</v>
+      <c r="D860" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="861">
@@ -17816,7 +17816,7 @@
           <t>А. С. Истер - Алгебра. Учебник для 9 класса общеобразовательных учебных заведений, 2017, Генеза</t>
         </is>
       </c>
-      <c r="C861" s="10" t="inlineStr">
+      <c r="C861" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17836,7 +17836,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 7 класс, 2015, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C862" s="10" t="inlineStr">
+      <c r="C862" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17856,7 +17856,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Алгебра. Дидактические материалы. 7 класс, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C863" s="10" t="inlineStr">
+      <c r="C863" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17876,12 +17876,12 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 7 класс. Методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C864" s="10" t="inlineStr">
+      <c r="C864" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D864" s="14" t="n">
+      <c r="D864" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17896,7 +17896,7 @@
           <t>Л. А. Александрова - Алгебра. 7 класс. Контрольные работы для учащихся общеобразовательных организаций, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C865" s="10" t="inlineStr">
+      <c r="C865" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17916,7 +17916,7 @@
           <t>Л. А. Александрова - Алгебра. 7 класс. Самостоятельные работы для учащихся общеобразовательных организаций : к учебнику А. Г. Мордковича, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C866" s="10" t="inlineStr">
+      <c r="C866" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17936,7 +17936,7 @@
           <t>Александрова Л. А. - Алгебра. 7 класс. Тематические проверочные работы в новой форме для учащихся общеобразовательных учреждений, 2012, Мнемозина</t>
         </is>
       </c>
-      <c r="C867" s="10" t="inlineStr">
+      <c r="C867" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17956,7 +17956,7 @@
           <t>Мордкович А. Г. - Алгебра. 7 класс : методическое пособие для учителя, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C868" s="10" t="inlineStr">
+      <c r="C868" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17976,7 +17976,7 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. Алгебра и начала математического анализа. Углубленный уровень. 11 класс. Методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C869" s="10" t="inlineStr">
+      <c r="C869" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -17996,7 +17996,7 @@
           <t>Александрова Л. А. - Алгебра и начала математического анализа. 10 класс. Самостоятельные работы для учащихся общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C870" s="10" t="inlineStr">
+      <c r="C870" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18016,7 +18016,7 @@
           <t>Александрова Л. А. - Алгебра и начала математического анализа. 11 класс. Самостоятельные работы для учащихся общеобразовательных учреждений, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C871" s="10" t="inlineStr">
+      <c r="C871" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18121,8 +18121,8 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D876" s="14" t="n">
-        <v>2</v>
+      <c r="D876" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="877">
@@ -18136,13 +18136,13 @@
           <t>А. Г. Мордкович, Н. П. Николаев - Алгебра. 8 класс. В двух частях. Часть 1. Учебник, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C877" s="10" t="inlineStr">
+      <c r="C877" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D877" s="14" t="n">
-        <v>2</v>
+      <c r="D877" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="878">
@@ -18156,7 +18156,7 @@
           <t>Мордкович А. Г., Николаев Н. П. - Алгебра. 9 кл., 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C878" s="10" t="inlineStr">
+      <c r="C878" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18181,7 +18181,7 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D879" s="14" t="n">
+      <c r="D879" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
           <t>И. Г. Арефьева, О. Н. Пирютко - Алгебра. Учебное пособие для 7 класса учреждений общего среднего образования с русским языком обучения, 2017, Народная асвета</t>
         </is>
       </c>
-      <c r="C881" s="10" t="inlineStr">
+      <c r="C881" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18316,7 +18316,7 @@
           <t>Е. Е. Тульчинская - Алгебра. 7 класс. Блицопрос, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C886" s="10" t="inlineStr">
+      <c r="C886" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18336,7 +18336,7 @@
           <t>Власова А.П., Евсеева Н.В., Латанова Н.И. - Уравнения в целых числах, 2010</t>
         </is>
       </c>
-      <c r="C887" s="10" t="inlineStr">
+      <c r="C887" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18376,7 +18376,7 @@
           <t>С. Б. Гашков - Современная элементарная алгебра в задачах и упражнениях, 2006, МЦНМО</t>
         </is>
       </c>
-      <c r="C889" s="10" t="inlineStr">
+      <c r="C889" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18396,7 +18396,7 @@
           <t>Вербицкий В. И. - Математика, 2013, Эксмо</t>
         </is>
       </c>
-      <c r="C890" s="8" t="inlineStr">
+      <c r="C890" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -18416,7 +18416,7 @@
           <t>Шахмейстер А.Х. - Уравнения, 2011, Издательство МЦНМО, Петроглиф, Виктория плюс</t>
         </is>
       </c>
-      <c r="C891" s="10" t="inlineStr">
+      <c r="C891" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18436,12 +18436,12 @@
           <t>Шахмейстер А.Х. - Уравнения, 2011, Издательство МЦНМО, Петроглиф, Виктория плюс</t>
         </is>
       </c>
-      <c r="C892" s="10" t="inlineStr">
+      <c r="C892" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D892" s="14" t="n">
+      <c r="D892" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18456,12 +18456,12 @@
           <t>Шахмейстер А.Х. - Уравнения, 2011, Издательство МЦНМО : Петроглиф : Виктория плюс</t>
         </is>
       </c>
-      <c r="C893" s="10" t="inlineStr">
+      <c r="C893" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D893" s="14" t="n">
+      <c r="D893" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18476,7 +18476,7 @@
           <t>Евг. В. Юрченко, Ел. В. Юрченко - Уравнения с параметром и нестандартные задачи. 7–9 класс. Живая методика математики — 2, 2017, МЦНМО</t>
         </is>
       </c>
-      <c r="C894" s="10" t="inlineStr">
+      <c r="C894" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -18776,7 +18776,7 @@
           <t>М.С. Красс, Б.П. Чупрынов - МАТЕМАТИКА В ЭКОНОМИКЕ. МАТЕМАТИЧЕСКИЕ МЕТОДЫ И МОДЕЛИ, 2007, Финансы и статистика</t>
         </is>
       </c>
-      <c r="C909" s="13" t="inlineStr">
+      <c r="C909" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -18796,7 +18796,7 @@
           <t>В.И. Малыхин - Математика в экономике, 2000, ИНФРА-М</t>
         </is>
       </c>
-      <c r="C910" s="8" t="inlineStr">
+      <c r="C910" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -18816,7 +18816,7 @@
           <t>Л.Н. Журбенко, Г.А. Никонова, Н.В. Никонова, С.Н. Нуриева, О.М. Дегтярева - МАТЕМАТИКА В ПРИМЕРАХ И ЗАДАЧАХ, 2009, ИНФРА-М</t>
         </is>
       </c>
-      <c r="C911" s="8" t="inlineStr">
+      <c r="C911" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -18836,7 +18836,7 @@
           <t>Евг. В. Юрченко, Ел. В. Юрченко - Уравнения с параметром и нестандартные задачи. 7–9 класс. Живая методика математики — 2, 2017, МЦНМО</t>
         </is>
       </c>
-      <c r="C912" s="8" t="inlineStr">
+      <c r="C912" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -18861,8 +18861,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D913" s="14" t="n">
-        <v>2</v>
+      <c r="D913" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="914">
@@ -18921,7 +18921,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D916" s="14" t="n">
+      <c r="D916" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18941,8 +18941,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D917" s="14" t="n">
-        <v>3</v>
+      <c r="D917" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="918">
@@ -18976,7 +18976,7 @@
           <t>Кэрен Брайант-Моул - ЗАНИМАТЕЛЬНАЯ МАТЕМАТИКА. ТАБЛИЦЫ И ГРАФИКИ</t>
         </is>
       </c>
-      <c r="C919" s="11" t="inlineStr">
+      <c r="C919" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -19076,7 +19076,7 @@
           <t>Г. И. Фалин, А. И. Фалин - Алгебра на вступительных экзаменах по математике в МГУ, 2020, МАКС Пресс</t>
         </is>
       </c>
-      <c r="C924" s="10" t="inlineStr">
+      <c r="C924" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -19096,7 +19096,7 @@
           <t>Г. В. Дорофеев, И. Ф. Шарыгин, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Математика. 6 класс. Учебник для общеобразовательных организаций, 2019, Просвещение</t>
         </is>
       </c>
-      <c r="C925" s="9" t="inlineStr">
+      <c r="C925" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -19116,7 +19116,7 @@
           <t>Л. И. Звавич, Л. В. Кузнецова, С. Б. Суворова - Алгебра. Дидактические материалы. 7 класс, 2019, Просвещение</t>
         </is>
       </c>
-      <c r="C926" s="10" t="inlineStr">
+      <c r="C926" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19136,7 +19136,7 @@
           <t>М.Л.Краснов, А.И.Киселев, Г.И.Макаренко - Функции комплексного переменного: Задачи и примеры с подробными решениями, 2003, Едиториал УРСС</t>
         </is>
       </c>
-      <c r="C927" s="8" t="inlineStr">
+      <c r="C927" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19156,7 +19156,7 @@
           <t>А.В. Пантелеев, А.С. Бортаковский - Теория управления в примерах и задачах, 2003, Высшая школа</t>
         </is>
       </c>
-      <c r="C928" s="8" t="inlineStr">
+      <c r="C928" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19176,7 +19176,7 @@
           <t>А.А. Гусак, Е.А. Бричикова - Теория вероятностей. Справочное пособие к решению задач, 2003, ТетраСистемс</t>
         </is>
       </c>
-      <c r="C929" s="13" t="inlineStr">
+      <c r="C929" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -19196,7 +19196,7 @@
           <t>А.И.Кибзун, Е.Р.Горяинова, А.В.Наумов, А.Н.Сиротин - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА. БАЗОВЫЙ КУРС С ПРИМЕРАМИ И ЗАДАЧАМИ, 2002, ФИЗМАТЛИТ</t>
         </is>
       </c>
-      <c r="C930" s="13" t="inlineStr">
+      <c r="C930" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -19301,7 +19301,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D935" s="14" t="n">
+      <c r="D935" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19341,7 +19341,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D937" s="14" t="n">
+      <c r="D937" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19381,7 +19381,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D939" s="14" t="n">
+      <c r="D939" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19436,7 +19436,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Рабочая тетрадь по алгебре. 8 класс : к учебнику Ю. Н. Макарычева и др. «Алгебра. 8 класс», 2020, Экзамен</t>
         </is>
       </c>
-      <c r="C942" s="10" t="inlineStr">
+      <c r="C942" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19456,7 +19456,7 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 8 класс. Методическое пособие, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C943" s="10" t="inlineStr">
+      <c r="C943" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19476,12 +19476,12 @@
           <t>А. Г. Мордкович, Л. А. Александрова, Т. Н. Мишустина, Е. Е. Тульчинская - Алгебра. 8 класс. В 2 ч. Ч. 2. Задачник для учащихся общеобразовательных учреждений, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C944" s="10" t="inlineStr">
+      <c r="C944" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D944" s="14" t="n">
+      <c r="D944" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
           <t>И. И. Зубарева, М. С. Мильштейн - Алгебра. 8 класс. Рабочая тетрадь № 1, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C945" s="10" t="inlineStr">
+      <c r="C945" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19516,7 +19516,7 @@
           <t>Л. А. Александрова - Алгебра. 8 класс. Контрольные работы для учащихся общеобразовательных организаций, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C946" s="10" t="inlineStr">
+      <c r="C946" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19536,7 +19536,7 @@
           <t>Ю. П. Дудницын, Е. Е. Тульчинская - Алгебра. 8 класс. Контрольные работы для общеобразовательных учреждений, 2005, Мнемозина</t>
         </is>
       </c>
-      <c r="C947" s="10" t="inlineStr">
+      <c r="C947" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19556,7 +19556,7 @@
           <t>Е. Е. Тульчинская - Алгебра. 8 класс. Блицопрос, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C948" s="10" t="inlineStr">
+      <c r="C948" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19576,7 +19576,7 @@
           <t>А. Г. Мордкович - Алгебра. 8 класс. Методическое пособие для учителя, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C949" s="10" t="inlineStr">
+      <c r="C949" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -19636,7 +19636,7 @@
           <t>М. А. Волчкевич - Уроки геометрии в задачах. 7–8 классы, 2016, МЦНМО</t>
         </is>
       </c>
-      <c r="C952" s="8" t="inlineStr">
+      <c r="C952" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19681,7 +19681,7 @@
           <t>High School Olympiads</t>
         </is>
       </c>
-      <c r="D954" s="14" t="n">
+      <c r="D954" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
           <t>High School Olympiads</t>
         </is>
       </c>
-      <c r="D955" s="14" t="n">
+      <c r="D955" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19861,7 +19861,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D963" s="14" t="n">
+      <c r="D963" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D966" s="14" t="n">
+      <c r="D966" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19936,7 +19936,7 @@
           <t>В. Ф. Бутузов, В. В. Прасолов - Математика: алгебра и начала математического анализа, геометрия. Геометрия. 10-11 классы, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C967" s="8" t="inlineStr">
+      <c r="C967" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19956,7 +19956,7 @@
           <t>А. В. Погорелов - Математика: алгебра и начала математического анализа, геометрия. Геометрия. 10–11 классы. Базовый и углублённый уровни, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C968" s="8" t="inlineStr">
+      <c r="C968" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19976,7 +19976,7 @@
           <t>И. Ф. Шарыгин - Математика: алгебра и начала математического анализа, геометрия. Геометрия. 10-11 классы. Базовый уровень. Учебник, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C969" s="8" t="inlineStr">
+      <c r="C969" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -19996,7 +19996,7 @@
           <t>Г. М. Генералов - Математическое моделирование. 10–11 классы, 2021, Просвещение</t>
         </is>
       </c>
-      <c r="C970" s="8" t="inlineStr">
+      <c r="C970" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -20016,7 +20016,7 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Математика: алгебра и начала математического анализа, геометрия, 2018, Русское слово</t>
         </is>
       </c>
-      <c r="C971" s="8" t="inlineStr">
+      <c r="C971" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -20036,12 +20036,12 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Математика: алгебра и начала математического анализа, геометрия, 2018, Русское слово</t>
         </is>
       </c>
-      <c r="C972" s="8" t="inlineStr">
+      <c r="C972" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D972" s="14" t="n">
+      <c r="D972" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20056,13 +20056,13 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов и др. - Математика. Алгебра и начала математического анализа, геометрия, 2018, Русское слово</t>
         </is>
       </c>
-      <c r="C973" s="8" t="inlineStr">
+      <c r="C973" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D973" s="14" t="n">
-        <v>3</v>
+      <c r="D973" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="974">
@@ -20116,7 +20116,7 @@
           <t>Н. Н. Удалова - Математика. Наглядный справочник для подготовки к ОГЭ и ЕГЭ, 2019, Эксмо</t>
         </is>
       </c>
-      <c r="C976" s="10" t="inlineStr">
+      <c r="C976" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20181,7 +20181,7 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D979" s="14" t="n">
+      <c r="D979" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20196,7 +20196,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Алгебра. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C980" s="10" t="inlineStr">
+      <c r="C980" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -20236,7 +20236,7 @@
           <t>В.П. ГРИГОРЬЕВ, Ю.А. ДУБИНСКИЙ - ЭЛЕМЕНТЫ ВЫСШЕЙ МАТЕМАТИКИ, 2014, Издательский центр «Академия»</t>
         </is>
       </c>
-      <c r="C982" s="8" t="inlineStr">
+      <c r="C982" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -20256,13 +20256,13 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 8 класс, 2019, Издательский центр «Вентана-Граф»</t>
         </is>
       </c>
-      <c r="C983" s="10" t="inlineStr">
+      <c r="C983" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D983" s="14" t="n">
-        <v>2</v>
+      <c r="D983" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="984">
@@ -20296,7 +20296,7 @@
           <t>Н.М. Пылаева, Т.В. Ахутина - Школа умножения. Методика развития внимания у детей 7–9 лет</t>
         </is>
       </c>
-      <c r="C985" s="11" t="inlineStr">
+      <c r="C985" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -20316,7 +20316,7 @@
           <t>Л.И. Слонимский, И.С. Слонимская - Математика в таблицах и схемах. Для подготовки к ОГЭ, 2020, Издательство АСТ</t>
         </is>
       </c>
-      <c r="C986" s="10" t="inlineStr">
+      <c r="C986" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20361,7 +20361,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D988" s="14" t="n">
+      <c r="D988" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20376,7 +20376,7 @@
           <t>И. И. Зубарева, М. С. Мильштейн, М. Н. Шанцева - Математика. 5 класс. Самостоятельные работы, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C989" s="9" t="inlineStr">
+      <c r="C989" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -20396,7 +20396,7 @@
           <t>И. И. Зубарева, И. П. Лепешонкова - Математика. 5 класс. Тетрадь для контрольных работ № 1, 2012, Мнемозина</t>
         </is>
       </c>
-      <c r="C990" s="9" t="inlineStr">
+      <c r="C990" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -20416,7 +20416,7 @@
           <t>Е. Е. Тульчинская - Математика. Блицопрос. 5 класс, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C991" s="9" t="inlineStr">
+      <c r="C991" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -20436,7 +20436,7 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Текущий и итоговый контроль по курсу «Математика». 5 класс: контрольно-измерительные материалы, 2014, Русское слово</t>
         </is>
       </c>
-      <c r="C992" s="10" t="inlineStr">
+      <c r="C992" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20456,12 +20456,12 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 5 класс, 2014, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C993" s="9" t="inlineStr">
+      <c r="C993" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D993" s="14" t="n">
+      <c r="D993" s="8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20476,12 +20476,12 @@
           <t>А.Х. Шахмейстер - Тригонометрия, 2014, Петроглиф, МЦНМО, ИД КДУ</t>
         </is>
       </c>
-      <c r="C994" s="10" t="inlineStr">
+      <c r="C994" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D994" s="14" t="n">
+      <c r="D994" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
           <t>О.В. Шульцева - Домашняя работа по алгебре за 8 класс к учебнику «Алгебра. 8 класс: учеб. для общеобразоват. учреждений / [С.М. Никольский, М.К. Потапов, Н.Н. Решетников, А.В. Шевкин]. — 8-е изд. — М. : Просвещение, 2011», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C996" s="10" t="inlineStr">
+      <c r="C996" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20576,7 +20576,7 @@
           <t>М.Г. Нефёдова - Математика. Контрольные и диагностические работы, 2013, Астрель</t>
         </is>
       </c>
-      <c r="C999" s="10" t="inlineStr">
+      <c r="C999" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20636,7 +20636,7 @@
           <t>Е.П.Бененсон, Л.С.Итина - МАТЕМАТИКА. ТЕТРАДЬ № 1 для 3-го класса</t>
         </is>
       </c>
-      <c r="C1002" s="8" t="inlineStr">
+      <c r="C1002" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -20676,7 +20676,7 @@
           <t>Э.Н. Балаян - Геометрия. Решебник к книге Э.Н. Балаяна «Геометрия. Задачи на готовых чертежах для подготовки к ОГЭ и ЕГЭ (7-9 классы)». 8 класс, 2019, Феникс</t>
         </is>
       </c>
-      <c r="C1004" s="10" t="inlineStr">
+      <c r="C1004" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -20696,7 +20696,7 @@
           <t>Александрова Л. А. - Алгебра и начала математического анализа. 10 класс. Самостоятельные работы для учащихся общеобразовательных организаций (базовый и углублённый уровни), 2015, Мнемозина</t>
         </is>
       </c>
-      <c r="C1005" s="10" t="inlineStr">
+      <c r="C1005" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -20716,7 +20716,7 @@
           <t>Учим таблицу умножения. Для начальной школы, 2014, АСТ</t>
         </is>
       </c>
-      <c r="C1006" s="8" t="inlineStr">
+      <c r="C1006" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -20876,7 +20876,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Алгебра и начала математического анализа. 10 класс. Базовый уровень, 2019, Дрофа</t>
         </is>
       </c>
-      <c r="C1014" s="10" t="inlineStr">
+      <c r="C1014" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -20896,7 +20896,7 @@
           <t>А. Г. Мордкович, Н. П. Николаев - Алгебра. 7 класс. Учебник для общеобразовательных организаций (углублённый уровень). Часть 1, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C1015" s="10" t="inlineStr">
+      <c r="C1015" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -20916,7 +20916,7 @@
           <t>А. Г. Мордкович, Н. П. Николаев - Алгебра. 8 класс. Учебник для общеобразовательных организаций (углублённый уровень). Часть 1, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C1016" s="10" t="inlineStr">
+      <c r="C1016" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -20936,7 +20936,7 @@
           <t>А. Г. Мордкович, Н. П. Николаев, П. В. Семенов - Алгебра. 9 класс. Учебник для общеобразовательных организаций (углублённый уровень). Часть 1, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C1017" s="10" t="inlineStr">
+      <c r="C1017" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21016,7 +21016,7 @@
           <t>И. Р. Высоцкий, И. В. Ященко - Математика. Вероятность и статистика. 7–9 классы. Базовый уровень. Учебник. Часть 1, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C1021" s="13" t="inlineStr">
+      <c r="C1021" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -21036,13 +21036,13 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 8, Гімнaзія</t>
         </is>
       </c>
-      <c r="C1022" s="10" t="inlineStr">
+      <c r="C1022" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1022" s="14" t="n">
-        <v>3</v>
+      <c r="D1022" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1023">
@@ -21056,13 +21056,13 @@
           <t>Александрова Л. А. - Алгебра и начала математического анализа. 10 класс. Самостоятельные работы для учащихся общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C1023" s="10" t="inlineStr">
+      <c r="C1023" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1023" s="14" t="n">
-        <v>2</v>
+      <c r="D1023" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1024">
@@ -21101,7 +21101,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1025" s="14" t="n">
+      <c r="D1025" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
           <t>Григорьева Г. И. - Алгебра и начала анализа. 10 класс: поурочные планы по учебнику Ш. А. Алимова и др. I полугодие, 2008, Учитель</t>
         </is>
       </c>
-      <c r="C1026" s="10" t="inlineStr">
+      <c r="C1026" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21156,7 +21156,7 @@
           <t>Математика. Вероятность и статистика. 7–9 классы. Базовый уровень. Методическое пособие к предметной линии учебников по вероятности и статистике И. Р. Высоцкого, И. В. Ященко под редакцией И. В. Ященко, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C1028" s="13" t="inlineStr">
+      <c r="C1028" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -21216,7 +21216,7 @@
           <t>Ю. Н. Гладкий, В. В. Николина - География. 10 класс, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C1031" s="8" t="inlineStr">
+      <c r="C1031" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -21256,7 +21256,7 @@
           <t>А. Г. Мордкович, П. В. Семенов - Алгебра и начала математического анализа. 10 класс (профильный уровень): методическое пособие для учителя, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C1033" s="10" t="inlineStr">
+      <c r="C1033" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21276,7 +21276,7 @@
           <t>Н. Е. Фёдорова, М. В. Ткачёва - Алгебра и начала математического анализа. Методические рекомендации. 10-11 классы, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1034" s="10" t="inlineStr">
+      <c r="C1034" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21316,7 +21316,7 @@
           <t>А.В. Фарков - Тесты по геометрии. 7 класс: к учебнику Л.С. Атанасяна и др. «Геометрия. 7–9», 2009, Экзамен</t>
         </is>
       </c>
-      <c r="C1036" s="10" t="inlineStr">
+      <c r="C1036" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21336,7 +21336,7 @@
           <t>Л.И. Звавич, Е.В. Потоскуев - Тесты по геометрии. 7 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1037" s="10" t="inlineStr">
+      <c r="C1037" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21356,7 +21356,7 @@
           <t>А. Р. Рязановский, Д. Г. Мухин - Геометрия. 7 класс. Контрольные измерительные материалы, 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1038" s="10" t="inlineStr">
+      <c r="C1038" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21376,7 +21376,7 @@
           <t>М. И. Шабунин, М. В. Ткачёва, Н. Е. Фёдорова - Алгебра и начала математического анализа. Дидактические материалы, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1039" s="10" t="inlineStr">
+      <c r="C1039" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21396,7 +21396,7 @@
           <t>П. В. Чулков, Т. С. Струков - Алгебра. Тематические тесты. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1040" s="10" t="inlineStr">
+      <c r="C1040" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21416,7 +21416,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Методические рекомендации. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1041" s="10" t="inlineStr">
+      <c r="C1041" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21436,7 +21436,7 @@
           <t>Ю.М. Колягин, М.В. Ткачёва, Н.Е. Фёдорова, М.И. Шабунин - Алгебра. Методические рекомендации. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1042" s="10" t="inlineStr">
+      <c r="C1042" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21456,7 +21456,7 @@
           <t>Н. И. Шкиль, З. И. Слепкань, Е. С. Дубинчук - Алгебра и начала анализа, 2003, Зодиак-ЭКО</t>
         </is>
       </c>
-      <c r="C1043" s="10" t="inlineStr">
+      <c r="C1043" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21476,7 +21476,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра : учеб. пособие для 10-го кл. учреждений, обеспечивающих получение общ. сред. образования, с рус. яз. обучения с 12-летним сроком обучения (базовый и повышенный уровни), 2006, Нар. асвета</t>
         </is>
       </c>
-      <c r="C1044" s="10" t="inlineStr">
+      <c r="C1044" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -21496,7 +21496,7 @@
           <t>Т. М. Мищенко - Дидактические материалы и методические рекомендации для учителя по геометрии: 7 класс: к учебнику Л. С. Атанасяна и др. «Геометрия. 7–9 классы», 2016, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1045" s="10" t="inlineStr">
+      <c r="C1045" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21536,7 +21536,7 @@
           <t>Н.Б. Мельникова, Г.А. Захарова - Дидактические материалы по геометрии: 8 класс: к учебнику Л.С. Атанасяна и др. «Геометрия. 7–9 классы», 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1047" s="10" t="inlineStr">
+      <c r="C1047" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21556,7 +21556,7 @@
           <t>Т. М. Мищенко - Дидактические материалы и методические рекомендации для учителя по геометрии: 8 класс: к учебнику Л. С. Атанасяна и др. «Геометрия. 7–9 классы», 2016, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1048" s="10" t="inlineStr">
+      <c r="C1048" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -21896,7 +21896,7 @@
           <t>Ю.А. Глазков, П.М. Камаев - Рабочая тетрадь по геометрии. 7 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1065" s="8" t="inlineStr">
+      <c r="C1065" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -21936,7 +21936,7 @@
           <t>Н.Б. Мельникова - Контрольные работы по геометрии, 2012, Экзамен</t>
         </is>
       </c>
-      <c r="C1067" s="8" t="inlineStr">
+      <c r="C1067" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -22056,7 +22056,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Дидактические материалы. 6 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1073" s="9" t="inlineStr">
+      <c r="C1073" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -22076,7 +22076,7 @@
           <t>Е. А. Бунимович, Л. В. Кузнецова, Л. О. Рослова, С. С. Минаева, С. Б. Суворова - Математика. Рабочая тетрадь. 6 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1074" s="9" t="inlineStr">
+      <c r="C1074" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -22096,7 +22096,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Рабочая тетрадь по математике. 6 класс. Часть 1. К учебнику Н. Я. Виленкина и др. «Математика. 6 класс», 2017, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1075" s="9" t="inlineStr">
+      <c r="C1075" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -22116,7 +22116,7 @@
           <t>Т. М. Ерина - Тесты по математике: 5 класс : к учебнику А. Г. Мерзляка и др. «Математика. 5 класс», 2017, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1076" s="9" t="inlineStr">
+      <c r="C1076" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -22136,12 +22136,12 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Тематические тесты. 5 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1077" s="9" t="inlineStr">
+      <c r="C1077" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1077" s="14" t="n">
+      <c r="D1077" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
           <t>Т. М. Ерина, М. Ю. Ерина - Универсальные учебные действия. Рабочая тетрадь по математике. 5 класс. Часть 1. К учебнику Н. Я. Виленкина и др., 2017, Экзамен</t>
         </is>
       </c>
-      <c r="C1078" s="9" t="inlineStr">
+      <c r="C1078" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -22276,7 +22276,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра: учебное пособие для 10 класса учреждений общего среднего образования с русским языком обучения, 2013, Народная асвета</t>
         </is>
       </c>
-      <c r="C1084" s="10" t="inlineStr">
+      <c r="C1084" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -22336,7 +22336,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, Е. М. Рабинович, М. С. Якир - Алгебра. 9 класс. Самостоятельные и контрольные работы, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1087" s="10" t="inlineStr">
+      <c r="C1087" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -22356,7 +22356,7 @@
           <t>И. Е. Феоктистов - Алгебра. 9 класс. Дидактические материалы, 2018, Мнемозина</t>
         </is>
       </c>
-      <c r="C1088" s="10" t="inlineStr">
+      <c r="C1088" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -22421,7 +22421,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1091" s="14" t="n">
+      <c r="D1091" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22921,8 +22921,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1116" s="5" t="n">
-        <v>1</v>
+      <c r="D1116" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1117">
@@ -23056,7 +23056,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра и начала математического анализа. Дидактические материалы. 10 класс : базовый и профил. уровни, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1123" s="10" t="inlineStr">
+      <c r="C1123" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -23076,7 +23076,7 @@
           <t>В. И. Рыжик, Т. Х. Черкасова - Дидактические материалы по алгебре и математическому анализу с ответами и решениями для 10–11 классов. Учебное пособие для профильной школы, 2008, СМИО Пресс</t>
         </is>
       </c>
-      <c r="C1124" s="8" t="inlineStr">
+      <c r="C1124" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -23096,7 +23096,7 @@
           <t>Семенко Е.А., Крупецкий С.Л., Ларкин Г.Н. - Тематический сборник заданий для подготовки к ЕГЭ по математике, 2012, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1125" s="10" t="inlineStr">
+      <c r="C1125" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -23116,7 +23116,7 @@
           <t>А.П. Ершова, В.В. Голобородько - Самостоятельные и контрольные работы по алгебре и началам анализа для 10–11 классов, 2013, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1126" s="8" t="inlineStr">
+      <c r="C1126" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -23136,7 +23136,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухов (ред.) - Математика. 10-й класс. Тесты для промежуточной аттестации и текущего контроля, 2011, Легион-М</t>
         </is>
       </c>
-      <c r="C1127" s="8" t="inlineStr">
+      <c r="C1127" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -23156,7 +23156,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухова - Математика. 10-й класс. Тесты для промежуточной аттестации и текущего контроля: учебно-методическое пособие, 2011, Легион-М</t>
         </is>
       </c>
-      <c r="C1128" s="8" t="inlineStr">
+      <c r="C1128" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -23441,7 +23441,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1142" s="14" t="n">
+      <c r="D1142" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23676,7 +23676,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили - ГЕОМЕТРИЯ. ИТОГОВАЯ АТТЕСТАЦИЯ. ТИПОВЫЕ ТЕСТОВЫЕ ЗАДАНИЯ. 8 класс, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1154" s="10" t="inlineStr">
+      <c r="C1154" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -23861,7 +23861,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1163" s="14" t="n">
+      <c r="D1163" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23956,7 +23956,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Алгебра. Тематические тесты. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1168" s="10" t="inlineStr">
+      <c r="C1168" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -23976,7 +23976,7 @@
           <t>С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. Методические рекомендации. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1169" s="10" t="inlineStr">
+      <c r="C1169" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -23996,7 +23996,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Методические рекомендации. 8 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1170" s="10" t="inlineStr">
+      <c r="C1170" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24016,7 +24016,7 @@
           <t>В.В. Черноруцкий - Контрольно-измерительные материалы. Алгебра. 8 класс, 2017, ВАКО</t>
         </is>
       </c>
-      <c r="C1171" s="10" t="inlineStr">
+      <c r="C1171" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24036,7 +24036,7 @@
           <t>Алгебра. Методические рекомендации. 8 класс: учебное пособие для общеобразовательных организаций, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1172" s="10" t="inlineStr">
+      <c r="C1172" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24056,7 +24056,7 @@
           <t>Л. П. Евстафьева, А. П. Карп - Алгебра. Дидактические материалы. 8 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1173" s="10" t="inlineStr">
+      <c r="C1173" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24076,7 +24076,7 @@
           <t>С. С. Минаева, Л. О. Рослова - Алгебра. Рабочая тетрадь. 8 класс. Часть 1, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1174" s="10" t="inlineStr">
+      <c r="C1174" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24096,7 +24096,7 @@
           <t>Макарычев Ю.Н., Миндюк Н.Г. и др. - Алгебра. 8 класс, Просвещение</t>
         </is>
       </c>
-      <c r="C1175" s="10" t="inlineStr">
+      <c r="C1175" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24141,7 +24141,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1177" s="14" t="n">
+      <c r="D1177" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24156,7 +24156,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили - ГЕОМЕТРИЯ. ИТОГОВАЯ АТТЕСТАЦИЯ. ТИПОВЫЕ ТЕСТОВЫЕ ЗАДАНИЯ. 7 класс, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1178" s="10" t="inlineStr">
+      <c r="C1178" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -24176,7 +24176,7 @@
           <t>Ю. В. Садовничий - Промежуточное тестирование. Геометрия. 7 класс. ФГОС, 2015, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1179" s="10" t="inlineStr">
+      <c r="C1179" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -24396,7 +24396,7 @@
           <t>А. Р. Рязановский, Д. Г. Мухин - Математика. Всероссийская проверочная работа. 7 класс. Практикум, 2018, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1190" s="10" t="inlineStr">
+      <c r="C1190" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -24416,7 +24416,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, И. Е. Феоктистов - Алгебра. 7 класс : учеб. пособие для общеобразоват. организаций : углубл. уровень, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C1191" s="10" t="inlineStr">
+      <c r="C1191" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24436,7 +24436,7 @@
           <t>С. С. Минаева - Алгебра. Устные упражнения. 7 класс, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C1192" s="10" t="inlineStr">
+      <c r="C1192" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24541,8 +24541,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1197" s="14" t="n">
-        <v>2</v>
+      <c r="D1197" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
@@ -24556,7 +24556,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Алгебра. 7 класс. Самостоятельные и контрольные работы, 2017, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1198" s="10" t="inlineStr">
+      <c r="C1198" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24576,7 +24576,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Дидактические материалы. 8 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1199" s="10" t="inlineStr">
+      <c r="C1199" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24596,7 +24596,7 @@
           <t>Л.И. Мартышова - Контрольно-измерительные материалы. Алгебра. 7 класс, 2017, ВАКО</t>
         </is>
       </c>
-      <c r="C1200" s="10" t="inlineStr">
+      <c r="C1200" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24616,7 +24616,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Методические рекомендации. 7 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1201" s="10" t="inlineStr">
+      <c r="C1201" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24636,7 +24636,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Методические рекомендации. 7 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1202" s="10" t="inlineStr">
+      <c r="C1202" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -24656,12 +24656,12 @@
           <t>Т. М. Ерина - Рабочая тетрадь по математике. 6 класс. Часть 1. К учебнику С. М. Никольского и др. «Математика. 6 класс», 2017, Экзамен</t>
         </is>
       </c>
-      <c r="C1203" s="9" t="inlineStr">
+      <c r="C1203" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1203" s="14" t="n">
+      <c r="D1203" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
           <t>Т. М. Ерина - Тесты по математике: 6 класс : к учебнику А. Г. Мерзляка и др. «Математика. 6 класс», 2017, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1204" s="9" t="inlineStr">
+      <c r="C1204" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -24696,7 +24696,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Контрольные работы. 6 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1205" s="9" t="inlineStr">
+      <c r="C1205" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -24776,7 +24776,7 @@
           <t>Проверочная работа по МАТЕМАТИКЕ. 6 КЛАСС. Образец, 2018, Федеральная служба по надзору в сфере образования и науки Российской Федерации</t>
         </is>
       </c>
-      <c r="C1209" s="10" t="inlineStr">
+      <c r="C1209" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -24796,7 +24796,7 @@
           <t>С. С. Минаева - Математика. Устные упражнения. 6 класс, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C1210" s="9" t="inlineStr">
+      <c r="C1210" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -24816,7 +24816,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Тематические тесты. 6 класс, 2018, Просвещение</t>
         </is>
       </c>
-      <c r="C1211" s="9" t="inlineStr">
+      <c r="C1211" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -25036,7 +25036,7 @@
           <t>Б.Г. Зив, В.А. Гольдич - Дидактические материалы по алгебре и началам анализа для 10-11 классов, 2013, Петроглиф</t>
         </is>
       </c>
-      <c r="C1222" s="10" t="inlineStr">
+      <c r="C1222" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25096,7 +25096,7 @@
           <t>А. Н. Роганин, В. А. Дергачев - Алгебра и геометрия в таблицах и схемах: лучше, чем учебник, 2006, Феникс</t>
         </is>
       </c>
-      <c r="C1225" s="8" t="inlineStr">
+      <c r="C1225" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -25241,8 +25241,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1232" s="14" t="n">
-        <v>2</v>
+      <c r="D1232" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1233">
@@ -25296,7 +25296,7 @@
           <t>&lt;авторы&gt; - &lt;название&gt;, &lt;год&gt;, &lt;издательство&gt;</t>
         </is>
       </c>
-      <c r="C1235" s="8" t="inlineStr">
+      <c r="C1235" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -25416,7 +25416,7 @@
           <t>Ю. П. Дудницын, А. В. Семенов - Алгебра и начала математического анализа. 11 класс. Контрольные работы в новом формате, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1241" s="10" t="inlineStr">
+      <c r="C1241" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -25436,7 +25436,7 @@
           <t>Ю. П. Дудницын, А. В. Семенов - Алгебра и начала математического анализа. 10 класс. Контрольные работы в новом формате, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1242" s="10" t="inlineStr">
+      <c r="C1242" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -25456,7 +25456,7 @@
           <t>М. В. Ткачёва - Алгебра и начала математического анализа. Тематические тесты. 10 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1243" s="10" t="inlineStr">
+      <c r="C1243" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25476,7 +25476,7 @@
           <t>Л.Б. Крайнева - Тестовые материалы для оценки качества обучения. Алгебра и начала анализа. 10–11 класс, 2013, «Интеллект-Центр»</t>
         </is>
       </c>
-      <c r="C1244" s="10" t="inlineStr">
+      <c r="C1244" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25496,7 +25496,7 @@
           <t>А.Н. Рурукин, Е.В. Бровкова, Г.В. Лупенко, Т.А. Пыжова - Поурочные разработки по алгебре и началам анализа: 11 класс, 2009, ВАКО</t>
         </is>
       </c>
-      <c r="C1245" s="10" t="inlineStr">
+      <c r="C1245" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25516,7 +25516,7 @@
           <t>Г.К. Муравин - Алгебра и начала математического анализа. 10 класс, 2013, Дрофа</t>
         </is>
       </c>
-      <c r="C1246" s="10" t="inlineStr">
+      <c r="C1246" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25536,7 +25536,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра и начала математического анализа. Книга для учителя. 11 класс : базовый и профильный уровни, 2009, Просвещение</t>
         </is>
       </c>
-      <c r="C1247" s="10" t="inlineStr">
+      <c r="C1247" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25556,7 +25556,7 @@
           <t>Ю. В. Шепелева - Алгебра и начала математического анализа. Тематические тесты. 11 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1248" s="10" t="inlineStr">
+      <c r="C1248" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25576,7 +25576,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра и начала математического анализа. Дидактические материалы. 11 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1249" s="10" t="inlineStr">
+      <c r="C1249" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25636,7 +25636,7 @@
           <t>Л. Г. Петерсон, Е. А. Суворина - Каллиграфия цифр. Прописи по математике. 1 часть, 2016, Ювента</t>
         </is>
       </c>
-      <c r="C1252" s="8" t="inlineStr">
+      <c r="C1252" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -25756,7 +25756,7 @@
           <t>Л. И. Звавич, А. Р. Рязановский - Алгебра. 8 класс. Задачник для учащихся общеобразовательных учреждений, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C1258" s="10" t="inlineStr">
+      <c r="C1258" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25776,7 +25776,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, И. Е. Феоктистов - Алгебра. 8 класс, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C1259" s="10" t="inlineStr">
+      <c r="C1259" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25796,7 +25796,7 @@
           <t>Л. И. Звавич, А. Р. Рязановский - Алгебра. 8 класс. Задачник, 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C1260" s="10" t="inlineStr">
+      <c r="C1260" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25816,7 +25816,7 @@
           <t>Алгебра: Учебник для 8 класса общеобразовательных учреждений, 2006, Просвещение, Московские учебники</t>
         </is>
       </c>
-      <c r="C1261" s="10" t="inlineStr">
+      <c r="C1261" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -25836,13 +25836,13 @@
           <t>Лысенко Ф. Ф., Ольховая Л. С., Агафонова И. М., Бубличенко О. А., Давыдов Б. Е., Дробязко Е. А., Ковалева Л. Н., Ланцова Л. В., Монастырская Г. А. - Алгебра. Тесты для промежуточной аттестации. 7-8 класс, 2009, Легион-М</t>
         </is>
       </c>
-      <c r="C1262" s="10" t="inlineStr">
+      <c r="C1262" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D1262" s="14" t="n">
-        <v>2</v>
+      <c r="D1262" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1263">
@@ -25968,7 +25968,7 @@
           <t>Э.Н. Балаян - Репетитор по геометрии для подготовки к ГИА и ЕГЭ: 7-11 классы, 2012, Феникс</t>
         </is>
       </c>
-      <c r="C1269" s="10" t="inlineStr">
+      <c r="C1269" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -26048,7 +26048,7 @@
           <t>В. И. Глизбург - Алгебра и начала анализа. Контрольные работы для 11 класса общеобразовательных учреждений (профильный уровень), 2008, Мнемозина</t>
         </is>
       </c>
-      <c r="C1273" s="10" t="inlineStr">
+      <c r="C1273" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26068,7 +26068,7 @@
           <t>А. Г. Мордкович, П. В. Семенов - Алгебра и начала математического анализа. 11 класс (профильный уровень). Методическое пособие для учителя, 2010, Мнемозина</t>
         </is>
       </c>
-      <c r="C1274" s="10" t="inlineStr">
+      <c r="C1274" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26133,8 +26133,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1277" s="14" t="n">
-        <v>2</v>
+      <c r="D1277" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1278">
@@ -26153,8 +26153,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1278" s="14" t="n">
-        <v>3</v>
+      <c r="D1278" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1279">
@@ -26173,8 +26173,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1279" s="14" t="n">
-        <v>2</v>
+      <c r="D1279" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1280">
@@ -26193,8 +26193,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1280" s="14" t="n">
-        <v>3</v>
+      <c r="D1280" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1281">
@@ -26308,7 +26308,7 @@
           <t>И. Р. Высоцкий, И. В. Ященко - Математика. Вероятность и статистика. 10–11 классы. Базовый и углублённый уровни : учебное пособие, 2025, Просвещение</t>
         </is>
       </c>
-      <c r="C1286" s="13" t="inlineStr">
+      <c r="C1286" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -26333,8 +26333,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1287" s="14" t="n">
-        <v>2</v>
+      <c r="D1287" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1288">
@@ -26348,7 +26348,7 @@
           <t>Л. Г. Петерсон, Н. Х. Агаханов, А. Ю. Петрович, О. К. Подлипский, М. В. Рогатова, Б. В. Трушин - Алгебра. 8 класс. Учебник. Часть 1, 2019, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1288" s="10" t="inlineStr">
+      <c r="C1288" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26368,7 +26368,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Математика. Алгебра. 9 класс. Базовый уровень. Учебник, 2023, Просвещение</t>
         </is>
       </c>
-      <c r="C1289" s="10" t="inlineStr">
+      <c r="C1289" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26388,7 +26388,7 @@
           <t>В. И. Глизбург - Алгебра и начала математического анализа. 10 класс. Контрольные работы, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C1290" s="10" t="inlineStr">
+      <c r="C1290" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26408,7 +26408,7 @@
           <t>А. Г. Мордкович, Л. О. Денищева, Л. И. Звавич, Т. А. Корешкова, Т. Н. Мишустина, А. Р. Рязановский, П. В. Семенов - Алгебра и начала математического анализа. 11 класс. В 2 ч. Ч. 2. Задачник, 2014, Мнемозина</t>
         </is>
       </c>
-      <c r="C1291" s="10" t="inlineStr">
+      <c r="C1291" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26448,7 +26448,7 @@
           <t>А. Г. Мордкович, И. М. Смирнова - МАТЕМАТИКА. 10 КЛАСС, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C1293" s="8" t="inlineStr">
+      <c r="C1293" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -26644,7 +26644,7 @@
           <t>С.А. Субханкулова - Задачи с параметрами, 2010, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1303" s="10" t="inlineStr">
+      <c r="C1303" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -26664,12 +26664,12 @@
           <t>С.А. Субханкулова - ЗАДАЧИ С ПАРАМЕТРАМИ, 2010, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1304" s="10" t="inlineStr">
+      <c r="C1304" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1304" s="14" t="n">
+      <c r="D1304" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26709,7 +26709,7 @@
           <t>High School Olympiads</t>
         </is>
       </c>
-      <c r="D1306" s="14" t="n">
+      <c r="D1306" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
           <t>High School Olympiads</t>
         </is>
       </c>
-      <c r="D1307" s="14" t="n">
+      <c r="D1307" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26764,7 +26764,7 @@
           <t>Математика. 5 класс. Контрольно-измерительные материалы, ВАКО</t>
         </is>
       </c>
-      <c r="C1309" s="9" t="inlineStr">
+      <c r="C1309" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -26784,7 +26784,7 @@
           <t>М.Я. Гаиашвили - Самостоятельные и контрольные работы по математике. 5 класс, 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C1310" s="9" t="inlineStr">
+      <c r="C1310" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -26804,7 +26804,7 @@
           <t>В.Н. Рудницкая - Математика. 5 класс: Рабочая тетрадь № 1 для контрольных работ: к учебнику Н.Я. Виленкина и др. «Математика. 5 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1311" s="9" t="inlineStr">
+      <c r="C1311" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -26824,7 +26824,7 @@
           <t>В.Н. Рудницкая - Математика. 5 класс. Рабочая тетрадь № 1. Натуральные числа, 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C1312" s="9" t="inlineStr">
+      <c r="C1312" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -26844,7 +26844,7 @@
           <t>В.Л. Александрова - Математика. 5 класс. Практикум. Готовимся к ГИА, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1313" s="10" t="inlineStr">
+      <c r="C1313" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -26864,7 +26864,7 @@
           <t>Поурочные разработки к учебнику Н.Я. Виленкина</t>
         </is>
       </c>
-      <c r="C1314" s="12" t="inlineStr">
+      <c r="C1314" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -26884,7 +26884,7 @@
           <t>В.Л. Александрова - Математика. 5 класс. Контрольные работы в НОВОМ формате, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1315" s="9" t="inlineStr">
+      <c r="C1315" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -26904,7 +26904,7 @@
           <t>Ю. А. Глазков, В. И. Ахременкова, М. Я. Гаиашвили - Математика. 5 класс. Контрольные измерительные материалы, 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C1316" s="9" t="inlineStr">
+      <c r="C1316" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -27109,7 +27109,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1326" s="14" t="n">
+      <c r="D1326" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27124,7 +27124,7 @@
           <t>А.Х. Шахмейстер - Логарифмы, 2016, Петроглиф : Виктория плюс : Издательство МЦНМО</t>
         </is>
       </c>
-      <c r="C1327" s="10" t="inlineStr">
+      <c r="C1327" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27144,7 +27144,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика. 6 класс. Базовый уровень</t>
         </is>
       </c>
-      <c r="C1328" s="9" t="inlineStr">
+      <c r="C1328" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -27244,7 +27244,7 @@
           <t>Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева [и др.] - Алгебра. 7 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1333" s="10" t="inlineStr">
+      <c r="C1333" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27309,8 +27309,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1336" s="14" t="n">
-        <v>2</v>
+      <c r="D1336" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1337">
@@ -27404,7 +27404,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра. Учебное пособие для 8 класса общеобразовательных учреждений с русским языком обучения, 2010, Народная асвета</t>
         </is>
       </c>
-      <c r="C1341" s="10" t="inlineStr">
+      <c r="C1341" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27424,7 +27424,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 8 класса учреждений общего среднего образования с русским языком обучения, 2015, Народная асвета</t>
         </is>
       </c>
-      <c r="C1342" s="8" t="inlineStr">
+      <c r="C1342" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -27444,7 +27444,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Математика. Дидактические материалы. 6 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1343" s="9" t="inlineStr">
+      <c r="C1343" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -27464,7 +27464,7 @@
           <t>М. А. МИРЗААХМЕДОВ, А. А. РАХИМКОРИЕВ, Ш. Н.ИСМАИЛОВ, М. А. ТОХТАХОДЖАЕВА - МАТЕМАТИКА 6. Учебник для 6 классов школ общего среднего образования, 2017, ИЗДАТЕЛЬСКО-ПОЛИГРАФИЧЕСКИЙ ТВОРЧЕСКИЙ ДОМ „O'QITUVCHI“</t>
         </is>
       </c>
-      <c r="C1344" s="9" t="inlineStr">
+      <c r="C1344" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -27484,13 +27484,13 @@
           <t>М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Дидактические материалы. 9 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C1345" s="10" t="inlineStr">
+      <c r="C1345" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1345" s="14" t="n">
-        <v>2</v>
+      <c r="D1345" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1346">
@@ -27504,7 +27504,7 @@
           <t>Александрова Л. А. - Алгебра. 8 класс. Тематические проверочные работы в новой форме для учащихся общеобразовательных учреждений, 2012, Мнемозина</t>
         </is>
       </c>
-      <c r="C1346" s="10" t="inlineStr">
+      <c r="C1346" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27524,7 +27524,7 @@
           <t>Найма Гахраманова, Магомед Керимов, Ильгам Гусейнов - МАТЕМАТИКА 8, 2018, Radius</t>
         </is>
       </c>
-      <c r="C1347" s="8" t="inlineStr">
+      <c r="C1347" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -27544,7 +27544,7 @@
           <t>И. Г. Арефьева, О. Н. Пирютко - Алгебра: учебное пособие для 8 класса учреждений общего среднего образования с русским языком обучения, 2018, Народная асвета</t>
         </is>
       </c>
-      <c r="C1348" s="10" t="inlineStr">
+      <c r="C1348" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27564,7 +27564,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Алгебра. 7 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1349" s="10" t="inlineStr">
+      <c r="C1349" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27584,7 +27584,7 @@
           <t>А. Г. Мордкович, П. В. Семенов, Л. А. Александрова, Е. Л. Мардахаева - Алгебра. 7 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1350" s="10" t="inlineStr">
+      <c r="C1350" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27624,7 +27624,7 @@
           <t>Е. П. Нелин, О. Е. Долгова - Алгебра, 11 класс: учебник для общеобразовательных учебных заведений: академический уровень, профильный уровень, 2011, Гимназия</t>
         </is>
       </c>
-      <c r="C1352" s="10" t="inlineStr">
+      <c r="C1352" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27644,7 +27644,7 @@
           <t>О. А. Иванов, Т. Ю. Иванова, К. М. Столбов - Алгебра в 9 классе. Функции и последовательности, 2018, СМИО Пресс</t>
         </is>
       </c>
-      <c r="C1353" s="10" t="inlineStr">
+      <c r="C1353" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27664,7 +27664,7 @@
           <t>Наталья Павловна Моторо, Наталья Васильевна Новожилова, Марина Михайловна Шалашова - Сборник математических задач «Основы финансовой грамотности». Том 2. Для обучающихся 5–9 классов, 2019, Банк России</t>
         </is>
       </c>
-      <c r="C1354" s="8" t="inlineStr">
+      <c r="C1354" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -27684,7 +27684,7 @@
           <t>Наталья Павловна Моторо, Наталья Васильевна Новожилова, Марина Михайловна Шалашова - Сборник математических задач «Основы финансовой грамотности». Том 3, 2019, Банк России</t>
         </is>
       </c>
-      <c r="C1355" s="8" t="inlineStr">
+      <c r="C1355" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -27704,7 +27704,7 @@
           <t>Наталья Павловна Моторо, Наталья Васильевна Новожилова, Марина Михайловна Шалашова - Методические рекомендации к сборнику математических задач «Основы финансовой грамотности». Том 3. 10-11 классы, 2019, Банк России</t>
         </is>
       </c>
-      <c r="C1356" s="12" t="inlineStr">
+      <c r="C1356" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -27729,8 +27729,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1357" s="14" t="n">
-        <v>2</v>
+      <c r="D1357" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1358">
@@ -27744,13 +27744,13 @@
           <t>Э.Н. Балаян - Геометрия. Задачи на готовых чертежах для подготовки к ЕГЭ. 10-11 классы, 2013, Феникс</t>
         </is>
       </c>
-      <c r="C1358" s="10" t="inlineStr">
+      <c r="C1358" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D1358" s="14" t="n">
-        <v>2</v>
+      <c r="D1358" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1359">
@@ -27844,7 +27844,7 @@
           <t>А. Н. Шыныбеков, Д. А. Шыныбеков, Р. Н. Жумабаев - Алгебра. Учебник для 8 класса общеобразовательной школы, 2018, Атамұра</t>
         </is>
       </c>
-      <c r="C1363" s="10" t="inlineStr">
+      <c r="C1363" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27864,12 +27864,12 @@
           <t>Ш. А. Алимов, О. Р. Холмухамедов, М. А. Мирзаахмедов - Алгебра: Учебник для 8 классов средних общеобразовательных школ, 2019, Издательско-полиграфический творческий дом “O‘QITUVCHI”</t>
         </is>
       </c>
-      <c r="C1364" s="10" t="inlineStr">
+      <c r="C1364" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1364" s="14" t="n">
+      <c r="D1364" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27884,7 +27884,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, Е. М. Рабинович, М. С. Якир - Сборник задач и контрольных работ по алгебре для 8 класса, 2010, Гимназия</t>
         </is>
       </c>
-      <c r="C1365" s="10" t="inlineStr">
+      <c r="C1365" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -27904,7 +27904,7 @@
           <t>ВПР. Математика. 8 класс. Образец. Проверочная работа по МАТЕМАТИКЕ, 2021, Федеральная служба по надзору в сфере образования и науки</t>
         </is>
       </c>
-      <c r="C1366" s="10" t="inlineStr">
+      <c r="C1366" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -27924,7 +27924,7 @@
           <t>Е. Г. Коннова, Д. И. Ханин - Математика. 8 класс. Ступени к ВПР и ОГЭ. Тематический тренинг, 2019, Легион</t>
         </is>
       </c>
-      <c r="C1367" s="10" t="inlineStr">
+      <c r="C1367" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -27944,7 +27944,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 11 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1368" s="8" t="inlineStr">
+      <c r="C1368" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -27984,7 +27984,7 @@
           <t>А.В. Шевкин - ТЕКСТОВЫЕ ЗАДАЧИ по математике 5–6, 2011, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1370" s="9" t="inlineStr">
+      <c r="C1370" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -28024,7 +28024,7 @@
           <t>И.Я. Депман, Н.Я. Виленкин - ЗА СТРАНИЦАМИ УЧЕБНИКА МАТЕМАТИКИ</t>
         </is>
       </c>
-      <c r="C1372" s="11" t="inlineStr">
+      <c r="C1372" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -28164,7 +28164,7 @@
           <t>П. В. Чулков - Алгебра. Тематические тесты. 7 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1379" s="10" t="inlineStr">
+      <c r="C1379" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28184,7 +28184,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Алгебра. Методические рекомендации. 7 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1380" s="10" t="inlineStr">
+      <c r="C1380" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28204,7 +28204,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по алгебре. 7 класс: к учебнику С.М. Никольского и др. «Алгебра. 7 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1381" s="10" t="inlineStr">
+      <c r="C1381" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28224,7 +28224,7 @@
           <t>С.Г. Журавлев, Ю.В. Перепелкина - Рабочая тетрадь по алгебре: 7 класс: к учебнику С.М. Никольского и др. «Алгебра. 7 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1382" s="10" t="inlineStr">
+      <c r="C1382" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -28244,13 +28244,13 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Алгебра. 7 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1383" s="10" t="inlineStr">
+      <c r="C1383" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1383" s="14" t="n">
-        <v>2</v>
+      <c r="D1383" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1384">
@@ -28264,7 +28264,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Алгебра. 7 класс. Рабочая тетрадь к учебнику Г. К. Муравина, К. С. Муравина, О. В. Муравиной «Алгебра. 7 класс». В 2 ч. Ч. 1, 2011, Дрофа</t>
         </is>
       </c>
-      <c r="C1384" s="10" t="inlineStr">
+      <c r="C1384" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28284,7 +28284,7 @@
           <t>А.Н. Рурукин - Самостоятельные и контрольные работы по алгебре. 7 класс, 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C1385" s="10" t="inlineStr">
+      <c r="C1385" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28324,7 +28324,7 @@
           <t>И. Р. Высоцкий, И. В. Ященко - Математика. Вероятность и статистика. 7–9 классы. Углублённый уровень. Учебное пособие. В 2 ч. Ч. 1, 2025, Просвещение</t>
         </is>
       </c>
-      <c r="C1387" s="13" t="inlineStr">
+      <c r="C1387" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -28344,7 +28344,7 @@
           <t>Г. В. Дорофеев, Л. Г. Петерсон - МАТЕМАТИКА. 6 класс. Учебник (в 3 частях). Часть 1, 2019, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1388" s="9" t="inlineStr">
+      <c r="C1388" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -28384,7 +28384,7 @@
           <t>Е. А. Таможняя, С. Г. Толкунова - География. География России. Хозяйство. Регионы. 9 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1390" s="8" t="inlineStr">
+      <c r="C1390" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -28404,7 +28404,7 @@
           <t>А. Г. Мерзляк, Д. А. Номировский, В. Б. Полонский, М. С. Якир - Алгебра и начала математического анализа. 10 класс. Базовый уровень, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1391" s="10" t="inlineStr">
+      <c r="C1391" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -28424,7 +28424,7 @@
           <t>И. В. Ященко, М. А. Волчкевич, О. А. Ворончагина, И. Р. Высоцкий, Р. К. Гордин, П. В. Семёнов, О. Н. Косухин, Д. А. Фёдоровых, А. И. Суздальцев, А. Р. Рязановский, В. А. Смирнов, А. С. Трепалин, А. В. Хачатурян, С. А. Шестаков, Д. Э. Шноль - ЕГЭ. Математика. Профильный уровень. 14 вариантов. Типовые варианты экзаменационных заданий от разработчиков ЕГЭ, 2022, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1392" s="10" t="inlineStr">
+      <c r="C1392" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -28444,12 +28444,12 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 5 класс, 2019, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1393" s="9" t="inlineStr">
+      <c r="C1393" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1393" s="14" t="n">
+      <c r="D1393" s="8" t="n">
         <v>5</v>
       </c>
     </row>
@@ -28504,7 +28504,7 @@
           <t>Ю. В. Липовцев, О. Н. Третьякова - Основы высшей математики для инженеров, 2009, Вузовская книга</t>
         </is>
       </c>
-      <c r="C1396" s="8" t="inlineStr">
+      <c r="C1396" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -28604,7 +28604,7 @@
           <t>Т.М. Ерина - Рабочая тетрадь по математике: 6 класс: к учебнику Н.Я. Виленкина и др. «Математика: 6 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1401" s="10" t="inlineStr">
+      <c r="C1401" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -28624,7 +28624,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. В. Суворова - Математика. Арифметика. Геометрия. Тетрадь-экзаменатор. 6 класс, 2015, Просвещение</t>
         </is>
       </c>
-      <c r="C1402" s="10" t="inlineStr">
+      <c r="C1402" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -28684,7 +28684,7 @@
           <t>Г. П. Бевз, В. Г. Бевз - Математика. 6 класс, 2006, Генеза</t>
         </is>
       </c>
-      <c r="C1405" s="9" t="inlineStr">
+      <c r="C1405" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -28704,7 +28704,7 @@
           <t>С. Б. Суворова, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Математика. Методические рекомендации. 6 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1406" s="12" t="inlineStr">
+      <c r="C1406" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -28724,7 +28724,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, Н. В. Сафонова - Математика. Контрольные работы. 5–6 классы, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1407" s="9" t="inlineStr">
+      <c r="C1407" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -28744,7 +28744,7 @@
           <t>Галина Янченко, Василий Кравчук - МАТЕМАТИКА: Учебник для 6 класса, 2006, Издательство «Підручники і посібники»</t>
         </is>
       </c>
-      <c r="C1408" s="9" t="inlineStr">
+      <c r="C1408" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -28769,7 +28769,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1409" s="14" t="n">
+      <c r="D1409" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28804,7 +28804,7 @@
           <t>Наталья Павловна Моторо, Наталья Васильевна Новожилова, Инна Викторовна Филатова, Марина Михайловна Шалашова - Методические рекомендации к сборнику математических задач «Основы финансовой грамотности» : в 3 т. Т. 2 : для обучающихся 5–9 классов, 2019, Банк России</t>
         </is>
       </c>
-      <c r="C1411" s="12" t="inlineStr">
+      <c r="C1411" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -28824,7 +28824,7 @@
           <t>И. К. Сиротина - МАТЕМАТИКА. ПОСОБИЕ ДЛЯ ПОДГОТОВКИ К ЦЕНТРАЛИЗОВАННОМУ ТЕСТИРОВАНИЮ И ЭКЗАМЕНУ, 2010, ТетраСистемс</t>
         </is>
       </c>
-      <c r="C1412" s="10" t="inlineStr">
+      <c r="C1412" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -28884,12 +28884,12 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 9 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1415" s="10" t="inlineStr">
+      <c r="C1415" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1415" s="14" t="n">
+      <c r="D1415" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28984,7 +28984,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, И. Е. Феоктистов - Алгебра. 8 класс : учебник для общеобразовательных организаций : углублённый уровень, 2019, Просвещение</t>
         </is>
       </c>
-      <c r="C1420" s="10" t="inlineStr">
+      <c r="C1420" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29024,7 +29024,7 @@
           <t>Г. С. Ковалёва, Л. О. Рослова, К. А. Краснянская, О. А. Рыдзе, Е. С. Квитко - Математическая грамотность. Сборник эталонных заданий. Выпуск 1. Часть 1, 2020, Просвещение</t>
         </is>
       </c>
-      <c r="C1422" s="8" t="inlineStr">
+      <c r="C1422" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29044,7 +29044,7 @@
           <t>Л. Г. Петерсон, Н. Х. Агаханов, А. Ю. Петрович, О. К. Подлипский, М. В. Рогатова, Б. В. Трушин - Алгебра. 9 класс : учебник (в 2 частях). Ч. 1, 2019, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1423" s="10" t="inlineStr">
+      <c r="C1423" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29084,7 +29084,7 @@
           <t>Г.К. Безрукова, Н.Б. Мельникова, Н.В. Шевелева - ГИА-2010. Экзамен в новой форме. Геометрия. 9 класс. Тренировочные варианты экзаменационных работ для проведения государственной итоговой аттестации в новой форме, 2010, АСТ: Астрель</t>
         </is>
       </c>
-      <c r="C1425" s="10" t="inlineStr">
+      <c r="C1425" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -29104,7 +29104,7 @@
           <t>Г. П. Бевз, В. Г. Бевз - Алгебра: Учебник для 7 класса общеобразовательных учебных заведений, 2007, Зодиак-ЕКО</t>
         </is>
       </c>
-      <c r="C1426" s="10" t="inlineStr">
+      <c r="C1426" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29124,12 +29124,12 @@
           <t>Г. В. Дорофеев, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. 7 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1427" s="10" t="inlineStr">
+      <c r="C1427" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1427" s="14" t="n">
+      <c r="D1427" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29144,7 +29144,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. 7 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1428" s="10" t="inlineStr">
+      <c r="C1428" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29164,7 +29164,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра. Учебное пособие для 7 класса учреждений общего среднего образования с русским языком обучения, 2014, Народная асвета</t>
         </is>
       </c>
-      <c r="C1429" s="10" t="inlineStr">
+      <c r="C1429" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29184,7 +29184,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 7 класса учреждений общего среднего образования с русским языком обучения, 2014, Народная асвета</t>
         </is>
       </c>
-      <c r="C1430" s="9" t="inlineStr">
+      <c r="C1430" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -29204,7 +29204,7 @@
           <t>Ш.А.Алимов, Ю.М.Колягин, Ю.В.Сидоров, М.В.Ткачёва, Н.Е.Фёдорова, М.И.Шабунин - Алгебра. 8 класс, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C1431" s="10" t="inlineStr">
+      <c r="C1431" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29224,7 +29224,7 @@
           <t>Н. Я. Виленкин, А. Н. Виленкин, Г. С. Сурвилло, Ю. А. Дробышев, И. В. Дробышева, А. И. Кудрявцев - Алгебра. 8 класс : учеб. для общеобразоват. учреждений и шк. с углубл. изучением математики, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C1432" s="10" t="inlineStr">
+      <c r="C1432" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29249,7 +29249,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1433" s="14" t="n">
+      <c r="D1433" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29264,12 +29264,12 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 7 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1434" s="10" t="inlineStr">
+      <c r="C1434" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1434" s="14" t="n">
+      <c r="D1434" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29284,12 +29284,12 @@
           <t>А. Г. Мерзляк, В. М. Поляков - Алгебра. 9 класс. Углублённый уровень, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1435" s="10" t="inlineStr">
+      <c r="C1435" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1435" s="14" t="n">
+      <c r="D1435" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1436" s="14" t="n">
+      <c r="D1436" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29324,7 +29324,7 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Математика. 6 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1437" s="9" t="inlineStr">
+      <c r="C1437" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -29344,7 +29344,7 @@
           <t>А. Г. Мордкович, И. М. Смирнова - Математика. 11 класс. Учебник для учащихся общеобразовательных учреждений (базовый уровень), 2013, Мнемозина</t>
         </is>
       </c>
-      <c r="C1438" s="8" t="inlineStr">
+      <c r="C1438" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29424,7 +29424,7 @@
           <t>Г. В. Дорофеев, Л. Г. Петерсон - Математика. 5 класс. Учебник. Часть 1, 2019, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1442" s="9" t="inlineStr">
+      <c r="C1442" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -29449,7 +29449,7 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D1443" s="14" t="n">
+      <c r="D1443" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29469,7 +29469,7 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D1444" s="14" t="n">
+      <c r="D1444" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -29484,7 +29484,7 @@
           <t>В. В. Зайцев, В. В. Рыжков, М. И. Сканави - Математика. Большой справочник, 2018, Издательство АСТ : Мир и Образование</t>
         </is>
       </c>
-      <c r="C1445" s="8" t="inlineStr">
+      <c r="C1445" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29504,7 +29504,7 @@
           <t>КНИЖКА-ШПАРГАЛКА МАТЕМАТИКА в кармане</t>
         </is>
       </c>
-      <c r="C1446" s="10" t="inlineStr">
+      <c r="C1446" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -29524,7 +29524,7 @@
           <t>Коноплева О. А., Соболева С. А., Левина Э. М., Гусева И. Ю., Жеребцова Е. Л. - Весь курс школьной программы в схемах и таблицах: математика, физика, химия, информатика, биология, 2007, Тригон</t>
         </is>
       </c>
-      <c r="C1447" s="8" t="inlineStr">
+      <c r="C1447" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29589,8 +29589,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1450" s="14" t="n">
-        <v>2</v>
+      <c r="D1450" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1451">
@@ -29629,8 +29629,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1452" s="14" t="n">
-        <v>2</v>
+      <c r="D1452" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1453">
@@ -29744,7 +29744,7 @@
           <t>А.П. Ершова, Е.П. Нелин - Самостоятельные и контрольные работы по алгебре и началам математического анализа для 10 класса, 2013, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1458" s="10" t="inlineStr">
+      <c r="C1458" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -29764,7 +29764,7 @@
           <t>Е.П. Нелин, В.А. Лазарев - Алгебра и начала математического анализа. 11 класс, 2012, Илекса</t>
         </is>
       </c>
-      <c r="C1459" s="8" t="inlineStr">
+      <c r="C1459" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29784,7 +29784,7 @@
           <t>А.П. Ершова, Е.П. Нелин - Самостоятельные и контрольные работы по алгебре и началам математического анализа для 11 класса, 2012, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1460" s="10" t="inlineStr">
+      <c r="C1460" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -29804,7 +29804,7 @@
           <t>А.Г. Рубин, П.В. Чулков - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 10 класс. Базовый и углублённый уровни, 2016, Баласс</t>
         </is>
       </c>
-      <c r="C1461" s="8" t="inlineStr">
+      <c r="C1461" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29824,7 +29824,7 @@
           <t>А.Г. Рубин, П.В. Чулков - МАТЕМАТИКА: АЛГЕБРА И НАЧАЛА МАТЕМАТИЧЕСКОГО АНАЛИЗА, ГЕОМЕТРИЯ. АЛГЕБРА И НАЧАЛА МАТЕМАТИЧЕСКОГО АНАЛИЗА. 11 класс, 2016, БАЛАСС</t>
         </is>
       </c>
-      <c r="C1462" s="8" t="inlineStr">
+      <c r="C1462" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29864,7 +29864,7 @@
           <t>Н. Д. Золотарёва, Ю. А. Попов, Н. Л. Семендяева, М. В. Федотов - Алгебра. Базовый курс с решениями и указаниями, 2015, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1464" s="10" t="inlineStr">
+      <c r="C1464" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -29884,7 +29884,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Математика. Дидактические материалы. 5 класс, 2017, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1465" s="9" t="inlineStr">
+      <c r="C1465" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -29904,7 +29904,7 @@
           <t>Л.Э. Генденштейн, А.П. Ершова, А.С. Ершова - Наглядный справочник по математике с примерами, 2009, Илекса</t>
         </is>
       </c>
-      <c r="C1466" s="8" t="inlineStr">
+      <c r="C1466" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29924,7 +29924,7 @@
           <t>А. Б. Василевский - ОБУЧЕНИЕ РЕШЕНИЮ ЗАДАЧ ПО МАТЕМАТИКЕ, 1988, Вышэйшая школа</t>
         </is>
       </c>
-      <c r="C1467" s="8" t="inlineStr">
+      <c r="C1467" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -29944,7 +29944,7 @@
           <t>Т. М. Королёва, Е. Г. Маркарян, Ю. М. Нейман - ПОСОБИЕ ПО МАТЕМАТИКЕ ДЛЯ ПОСТУПАЮЩИХ В ВУЗЫ, 2008, Изд.МИИГАиК</t>
         </is>
       </c>
-      <c r="C1468" s="10" t="inlineStr">
+      <c r="C1468" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -29996,7 +29996,7 @@
           <t>И.Е. Малова, С.К. Горохова, Н.А. Малинникова, Г.А. Яцковская - Теория и методика обучения математике в средней школе, 2009, ВЛАДОС</t>
         </is>
       </c>
-      <c r="C1471" s="12" t="inlineStr">
+      <c r="C1471" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -30021,8 +30021,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1472" s="14" t="n">
-        <v>2</v>
+      <c r="D1472" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1473">
@@ -30096,7 +30096,7 @@
           <t>Лебединцева Е.А., Беленкова Е.Ю. - Математика. 5 класс. Тетрадь 1. Задания для обучения и развития учащихся, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1476" s="9" t="inlineStr">
+      <c r="C1476" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30116,7 +30116,7 @@
           <t>М.А. Попов - Контрольные и самостоятельные работы по математике, 2012, Экзамен</t>
         </is>
       </c>
-      <c r="C1477" s="10" t="inlineStr">
+      <c r="C1477" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30136,7 +30136,7 @@
           <t>М.А. Попов - Дидактические материалы по математике: 5 класс: к учебнику Н.Я. Виленкина и др. «Математика. 5 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1478" s="10" t="inlineStr">
+      <c r="C1478" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30176,7 +30176,7 @@
           <t>В.Н. Рудницкая - Дидактические материалы по математике: 5 класс: к учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 5 класс», 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1480" s="10" t="inlineStr">
+      <c r="C1480" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30196,7 +30196,7 @@
           <t>В.Н. Рудницкая - Тесты по математике: 5 класс: к учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 5 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1481" s="10" t="inlineStr">
+      <c r="C1481" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30216,7 +30216,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Промежуточное тестирование. Математика. 5 класс, 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1482" s="10" t="inlineStr">
+      <c r="C1482" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30236,7 +30236,7 @@
           <t>Мартышова Л.И. - Контрольно-измерительные материалы. Алгебра. 9 класс, 2016, ВАКО</t>
         </is>
       </c>
-      <c r="C1483" s="10" t="inlineStr">
+      <c r="C1483" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30356,7 +30356,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. 9 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1489" s="10" t="inlineStr">
+      <c r="C1489" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -30376,12 +30376,12 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Алгебра. 9 класс, 2017, Просвещение</t>
         </is>
       </c>
-      <c r="C1490" s="10" t="inlineStr">
+      <c r="C1490" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1490" s="14" t="n">
+      <c r="D1490" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30396,7 +30396,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Алгебра. Дидактические материалы. 9 класс, 2017, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1491" s="10" t="inlineStr">
+      <c r="C1491" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -30496,7 +30496,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Математика. Алгебра. 7 класс. Базовый уровень, 2024, Просвещение</t>
         </is>
       </c>
-      <c r="C1496" s="10" t="inlineStr">
+      <c r="C1496" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -30516,7 +30516,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Математика. 6 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1497" s="9" t="inlineStr">
+      <c r="C1497" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30536,7 +30536,7 @@
           <t>Н. Я. Виленкин, В. И. Жохов, А. С. Чесноков, Л. А. Александрова, С. И. Шварцбурд - Математика. 6 класс. Базовый уровень. Учебник. В двух частях. Часть 1, 2024, Просвещение</t>
         </is>
       </c>
-      <c r="C1498" s="9" t="inlineStr">
+      <c r="C1498" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30556,7 +30556,7 @@
           <t>Л. Г. Петерсон, А. А. Невретдинова, Т. Ю. Поникарова - МАТЕМАТИКА 3/1. САМОСТОЯТЕЛЬНЫЕ И КОНТРОЛЬНЫЕ РАБОТЫ ДЛЯ НАЧАЛЬНОЙ ШКОЛЫ. ВЫПУСК 3/1, ЮВЕНТА</t>
         </is>
       </c>
-      <c r="C1499" s="8" t="inlineStr">
+      <c r="C1499" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -30641,8 +30641,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1503" s="14" t="n">
-        <v>2</v>
+      <c r="D1503" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1504">
@@ -30716,7 +30716,7 @@
           <t>Е.В. Буцко, А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Алгебра. 9 класс. Методическое пособие, 2018, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1507" s="10" t="inlineStr">
+      <c r="C1507" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -30736,12 +30736,12 @@
           <t>Е. В. Буцко, А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 9 класс. Методическое пособие, 2020, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1508" s="10" t="inlineStr">
+      <c r="C1508" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1508" s="14" t="n">
+      <c r="D1508" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30756,7 +30756,7 @@
           <t>Я. П. Понарин - Алгебра комплексных чисел в геометрических задачах, 2004, Издательство Московского центра непрерывного математического образования</t>
         </is>
       </c>
-      <c r="C1509" s="10" t="inlineStr">
+      <c r="C1509" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -30781,7 +30781,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1510" s="14" t="n">
+      <c r="D1510" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30796,7 +30796,7 @@
           <t>А.Х. Шахмейстер - Геометрические задачи на экзаменах. Часть 1. Планиметрия, 2015, Петроглиф, Виктория плюс, МЦНМО</t>
         </is>
       </c>
-      <c r="C1511" s="10" t="inlineStr">
+      <c r="C1511" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -30876,7 +30876,7 @@
           <t>С. М. Никольский, М. К. Потапов, Н. Н. Решетников, А. В. Шевкин - Математика. 5 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1515" s="9" t="inlineStr">
+      <c r="C1515" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30896,7 +30896,7 @@
           <t>Н. Я. Виленкин, В. И. Жохов, А. С. Чесноков, С. И. Шварцбурд - Математика. 5 класс: учебник для общеобразовательных организаций. Ч. 2, 2019, Мнемозина</t>
         </is>
       </c>
-      <c r="C1516" s="9" t="inlineStr">
+      <c r="C1516" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30916,7 +30916,7 @@
           <t>Е. А. Бунимович, Г. В. Дорофеев, С. Б. Суворова, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Математика. Арифметика. Геометрия. 5 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1517" s="9" t="inlineStr">
+      <c r="C1517" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30936,7 +30936,7 @@
           <t>В.В. Козлов, А.А. Никитин, В.С. Белоносов, А.А. Мальцев, А.С. Марковичев, Ю.В. Михеев, М.В. Фокин - Математика. Учебник для 6 класса общеобразовательных организаций, 2019, Русское слово</t>
         </is>
       </c>
-      <c r="C1518" s="9" t="inlineStr">
+      <c r="C1518" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -30996,7 +30996,7 @@
           <t>Смирнов В. А. - Геометрия. Стереометрия: Пособие для подготовки к ЕГЭ, 2009, МЦНМО</t>
         </is>
       </c>
-      <c r="C1521" s="10" t="inlineStr">
+      <c r="C1521" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -31041,8 +31041,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1523" s="14" t="n">
-        <v>2</v>
+      <c r="D1523" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1524">
@@ -31101,8 +31101,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1526" s="14" t="n">
-        <v>2</v>
+      <c r="D1526" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1527">
@@ -31196,12 +31196,12 @@
           <t>А.Х. Шахмейстер - Дробно-рациональные неравенства, 2008, Издательство МЦНМО : Петроглиф : Виктория плюс</t>
         </is>
       </c>
-      <c r="C1531" s="10" t="inlineStr">
+      <c r="C1531" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1531" s="14" t="n">
+      <c r="D1531" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31216,12 +31216,12 @@
           <t>А.Х. Шахмейстер - Дробно-рациональные неравенства, 2008, Издательство МЦНМО, Петроглиф, Виктория плюс</t>
         </is>
       </c>
-      <c r="C1532" s="10" t="inlineStr">
+      <c r="C1532" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1532" s="14" t="n">
+      <c r="D1532" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31236,13 +31236,13 @@
           <t>А. Г. Мерзляк, В. Б. Полонский, М. С. Якир - Алгебра. 8 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1533" s="10" t="inlineStr">
+      <c r="C1533" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1533" s="14" t="n">
-        <v>4</v>
+      <c r="D1533" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1534">
@@ -31281,7 +31281,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1535" s="14" t="n">
+      <c r="D1535" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -31296,7 +31296,7 @@
           <t>А. Г. Мордкович, П. В. Семенов, Л. А. Александрова, Е. Л. Мардахаева - Алгебра. 9 класс, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1536" s="10" t="inlineStr">
+      <c r="C1536" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31416,7 +31416,7 @@
           <t>Л. Г. Петерсон, Д. Л. Абраров, Е. В. Чуткова - Алгебра. 7 класс. Учебник. Часть 1, 2019, БИНОМ. Лаборатория знаний</t>
         </is>
       </c>
-      <c r="C1542" s="10" t="inlineStr">
+      <c r="C1542" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31476,7 +31476,7 @@
           <t>В.Е. Гмурман - Руководство к решению задач по теории вероятностей и математической статистике, 2004, Высшая школа</t>
         </is>
       </c>
-      <c r="C1545" s="13" t="inlineStr">
+      <c r="C1545" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -31496,13 +31496,13 @@
           <t>А. Р. Рязановский, Д. Г. Мухин - Математика. Всероссийская проверочная работа. 7 класс. Практикум по выполнению типовых заданий, 2016, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1546" s="10" t="inlineStr">
+      <c r="C1546" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
       </c>
-      <c r="D1546" s="14" t="n">
-        <v>2</v>
+      <c r="D1546" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1547">
@@ -31516,7 +31516,7 @@
           <t>Ю.П. Дудницын, В.Л. Кронгауз - Контрольные работы по алгебре. 7 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1547" s="10" t="inlineStr">
+      <c r="C1547" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31536,7 +31536,7 @@
           <t>С. Г. Журавлёв, С. А. Изотова, С. В. Киреева - Контрольные и самостоятельные работы по алгебре и геометрии, 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1548" s="12" t="inlineStr">
+      <c r="C1548" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -31556,7 +31556,7 @@
           <t>Б.Г. Зив, В.А. Гольдич - Дидактические материалы по алгебре для 7 класса, 2013, Петроглиф</t>
         </is>
       </c>
-      <c r="C1549" s="10" t="inlineStr">
+      <c r="C1549" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31576,7 +31576,7 @@
           <t>Л. П. Донец - Готовимся к ГИА. Алгебра. 7 класс. Итоговое тестирование в формате экзамена, 2011, Академия развития</t>
         </is>
       </c>
-      <c r="C1550" s="10" t="inlineStr">
+      <c r="C1550" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -31596,7 +31596,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухов - Алгебра. 7 класс. Тематические тесты. Промежуточная аттестация, 2011, Легион-М</t>
         </is>
       </c>
-      <c r="C1551" s="10" t="inlineStr">
+      <c r="C1551" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -31616,7 +31616,7 @@
           <t>С.С. Минаева - 30 тестов по математике: 5–7 классы, 2011, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1552" s="10" t="inlineStr">
+      <c r="C1552" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -31636,7 +31636,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Алгебра. 8 класс: учебник для общеобразовательных организаций с приложением на электронном носителе, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1553" s="10" t="inlineStr">
+      <c r="C1553" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31656,7 +31656,7 @@
           <t>Функциональная грамотность</t>
         </is>
       </c>
-      <c r="C1554" s="8" t="inlineStr">
+      <c r="C1554" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -31696,7 +31696,7 @@
           <t>МАТЕМАТИКА УЧЕБНИК 10</t>
         </is>
       </c>
-      <c r="C1556" s="8" t="inlineStr">
+      <c r="C1556" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -31716,7 +31716,7 @@
           <t>МАТЕМАТИКА УЧЕБНИК 11</t>
         </is>
       </c>
-      <c r="C1557" s="8" t="inlineStr">
+      <c r="C1557" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -31736,7 +31736,7 @@
           <t>И. Г. Арефьева, О. Н. Пирютко - Алгебра : учебное пособие для 10 класса учреждений общего среднего образования с русским языком обучения, 2019, Народная асвета</t>
         </is>
       </c>
-      <c r="C1558" s="10" t="inlineStr">
+      <c r="C1558" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -31756,7 +31756,7 @@
           <t>Мирзаахмедов М. А., Исмаилов Ш.Н., Аманов А.К., Хайдаров Б.К. - МАТЕМАТИКА: АЛГЕБРА И НАЧАЛА АНАЛИЗА. ГЕОМЕТРИЯ. ЧАСТЬ I. 10 класс, 2017, ООО "EXTREMUM PRESS"</t>
         </is>
       </c>
-      <c r="C1559" s="8" t="inlineStr">
+      <c r="C1559" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -31776,13 +31776,13 @@
           <t>Мирзаахмедов М. А., Исмаилов Ш.Н., Аманов А.К., Хайдаров Б.К. - МАТЕМАТИКА 10. АЛГЕБРА И НАЧАЛА АНАЛИЗА. ГЕОМЕТРИЯ. ЧАСТЬ I, 2017, ООО "EXTREMUM PRESS"</t>
         </is>
       </c>
-      <c r="C1560" s="8" t="inlineStr">
+      <c r="C1560" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D1560" s="14" t="n">
-        <v>2</v>
+      <c r="D1560" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1561">
@@ -31796,13 +31796,13 @@
           <t>Мирзаахмедов М. А., Исмаилов Ш.Н., Аманов А.К., Хайдаров Б.К. - МАТЕМАТИКА: АЛГЕБРА И НАЧАЛА АНАЛИЗА, ГЕОМЕТРИЯ. ЧАСТЬ I. 10 класс, 2017, EXTREMUM PRESS</t>
         </is>
       </c>
-      <c r="C1561" s="8" t="inlineStr">
+      <c r="C1561" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
       </c>
-      <c r="D1561" s="14" t="n">
-        <v>3</v>
+      <c r="D1561" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1562">
@@ -31841,7 +31841,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1563" s="14" t="n">
+      <c r="D1563" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31856,7 +31856,7 @@
           <t>Володин Б. Г., Ганин М. П., Динер И. Я., Комаров Л. Б., Свешников А. А., Старовин К. Б. - Сборник задач по теории вероятностей, математической статистике и теории случайных функций, 2013, Лань</t>
         </is>
       </c>
-      <c r="C1564" s="13" t="inlineStr">
+      <c r="C1564" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -31896,7 +31896,7 @@
           <t>А. М. Попов, В. Н. Сотников - Теория вероятностей, 2019, Юрайт</t>
         </is>
       </c>
-      <c r="C1566" s="13" t="inlineStr">
+      <c r="C1566" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -31916,7 +31916,7 @@
           <t>Р.Ш. Хуснутдинов - ТЕОРИЯ ВЕРОЯТНОСТЕЙ, 2013, ИНФРА-М</t>
         </is>
       </c>
-      <c r="C1567" s="13" t="inlineStr">
+      <c r="C1567" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -31936,7 +31936,7 @@
           <t>В.Е. Гмурман - Теория вероятностей и математическая статистика, 2003, Высшая школа</t>
         </is>
       </c>
-      <c r="C1568" s="13" t="inlineStr">
+      <c r="C1568" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -31981,7 +31981,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1570" s="14" t="n">
+      <c r="D1570" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31996,7 +31996,7 @@
           <t>А.С. Чесноков, К.И. Нешков - Дидактические материалы по математике для 6 класса, 2014, Академкнига/Учебник</t>
         </is>
       </c>
-      <c r="C1571" s="9" t="inlineStr">
+      <c r="C1571" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -32016,7 +32016,7 @@
           <t>Н. А. Тарасенкова, И. Н. Богатырёва, О. Н. Коломиец, З. А. Сердюк - МАТЕМАТИКА. Учебник для 6 класса общеобразовательных учебных заведений с обучением на русском языке, 2014, Издательский дом «ОСВИТА»</t>
         </is>
       </c>
-      <c r="C1572" s="9" t="inlineStr">
+      <c r="C1572" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -32036,7 +32036,7 @@
           <t>М.К. Потапов, А.В. Шевкин - МАТЕМАТИКА. Методические рекомендации. 6 класс. Пособие для учителей общеобразовательных учреждений, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1573" s="12" t="inlineStr">
+      <c r="C1573" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -32056,7 +32056,7 @@
           <t>П. В. Чулков, Е. Ф. Шершнев, О. Ф. Зарапина - Математика. Тематические тесты. 6 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1574" s="9" t="inlineStr">
+      <c r="C1574" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -32081,7 +32081,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1575" s="14" t="n">
+      <c r="D1575" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -32096,7 +32096,7 @@
           <t>А. Г. Мерзляк, Д. А. Номировский, В. Б. Полонский, М. С. Якир - АЛГЕБРА. 11 класс, 2011, Гимназия</t>
         </is>
       </c>
-      <c r="C1576" s="10" t="inlineStr">
+      <c r="C1576" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32136,7 +32136,7 @@
           <t>John Bird - Engineering Mathematics Pocket Book, Newnes</t>
         </is>
       </c>
-      <c r="C1578" s="8" t="inlineStr">
+      <c r="C1578" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -32181,8 +32181,8 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D1580" s="14" t="n">
-        <v>2</v>
+      <c r="D1580" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1581">
@@ -32216,7 +32216,7 @@
           <t>В.П. Чистяков - Курс теории вероятностей, 2000, Агар</t>
         </is>
       </c>
-      <c r="C1582" s="13" t="inlineStr">
+      <c r="C1582" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -32261,7 +32261,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1584" s="14" t="n">
+      <c r="D1584" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -32276,7 +32276,7 @@
           <t>Власова А.П., Евсеева Н.В., Латанова Н.И.</t>
         </is>
       </c>
-      <c r="C1585" s="8" t="inlineStr">
+      <c r="C1585" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -32316,7 +32316,7 @@
           <t>Е.А. Бунимович, Л.В. Кузнецова, С.С. Минаева, Л.О. Рослова, С.В. Суворова - Алгебра. 8 класс. Учебник, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1587" s="10" t="inlineStr">
+      <c r="C1587" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32336,7 +32336,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Математика. Алгебра : 8-й класс : базовый уровень : учебник, 2024, Просвещение</t>
         </is>
       </c>
-      <c r="C1588" s="10" t="inlineStr">
+      <c r="C1588" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32356,7 +32356,7 @@
           <t>А. Г. Мордкович, П. В. Семенов, Л. А. Александрова, Е. Л. Мардахаева - Алгебра. 8 класс. Учебник, 2022, Просвещение</t>
         </is>
       </c>
-      <c r="C1589" s="10" t="inlineStr">
+      <c r="C1589" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32396,7 +32396,7 @@
           <t>А.А. Дадаян - Математика, 2004, ФОРУМ — ИНФРА-М</t>
         </is>
       </c>
-      <c r="C1591" s="8" t="inlineStr">
+      <c r="C1591" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -32416,7 +32416,7 @@
           <t>В. Т. Лисичкин, И. Л. Соловейчик - Математика в задачах с решениями, 2014, Лань</t>
         </is>
       </c>
-      <c r="C1592" s="8" t="inlineStr">
+      <c r="C1592" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -32536,7 +32536,7 @@
           <t>&lt;авторы&gt; - &lt;название&gt;, &lt;год&gt;, &lt;издательство&gt;</t>
         </is>
       </c>
-      <c r="C1598" s="13" t="inlineStr">
+      <c r="C1598" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -32556,7 +32556,7 @@
           <t>Ю. Я. Кацман - ТЕОРИЯ ВЕРОЯТНОСТЕЙ И МАТЕМАТИЧЕСКАЯ СТАТИСТИКА. ПРИМЕРЫ С РЕШЕНИЯМИ, 2019, Юрайт</t>
         </is>
       </c>
-      <c r="C1599" s="13" t="inlineStr">
+      <c r="C1599" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -32576,7 +32576,7 @@
           <t>А. Н. Бородин - Элементарный курс теории вероятностей и математической статистики, 2011, Лань</t>
         </is>
       </c>
-      <c r="C1600" s="13" t="inlineStr">
+      <c r="C1600" s="14" t="inlineStr">
         <is>
           <t>Probability &amp; Statistics</t>
         </is>
@@ -32596,7 +32596,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по математике. 6 класс: к учебнику С.М. Никольского и др. «Математика. 6 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1601" s="10" t="inlineStr">
+      <c r="C1601" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -32616,7 +32616,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Математика. Рабочая тетрадь. 6 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1602" s="9" t="inlineStr">
+      <c r="C1602" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -32636,12 +32636,12 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, М.С. Якир - Математика. 6 класс, 2014, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1603" s="9" t="inlineStr">
+      <c r="C1603" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1603" s="14" t="n">
+      <c r="D1603" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -32656,7 +32656,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 6 класса учреждений общего среднего образования с русским языком обучения, 2014, Народная асвета</t>
         </is>
       </c>
-      <c r="C1604" s="9" t="inlineStr">
+      <c r="C1604" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -32701,8 +32701,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1606" s="14" t="n">
-        <v>2</v>
+      <c r="D1606" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1607">
@@ -32756,7 +32756,7 @@
           <t>Г. В. Дорофеев, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. 8 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C1609" s="10" t="inlineStr">
+      <c r="C1609" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32776,7 +32776,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. 8 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1610" s="10" t="inlineStr">
+      <c r="C1610" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32796,7 +32796,7 @@
           <t>Ю. Н. Макарычев, Н. Г. Миндюк, К. И. Нешков, С. Б. Суворова - Алгебра. 8 класс: учебник для общеобразовательных организаций с приложением на электронном носителе, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1611" s="10" t="inlineStr">
+      <c r="C1611" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32816,7 +32816,7 @@
           <t>Ш. А. Алимов, Ю. М. Колягин, Ю. В. Сидоров, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. 9 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1612" s="10" t="inlineStr">
+      <c r="C1612" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32836,13 +32836,13 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. 9 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1613" s="10" t="inlineStr">
+      <c r="C1613" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1613" s="14" t="n">
-        <v>3</v>
+      <c r="D1613" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1614">
@@ -32856,7 +32856,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра. Учебное пособие для 9 класса учреждений общего среднего образования с русским языком обучения, 2014, Народная асвета</t>
         </is>
       </c>
-      <c r="C1614" s="10" t="inlineStr">
+      <c r="C1614" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32876,7 +32876,7 @@
           <t>С. А. Шестаков, И. Р. Высоцкий, Л. И. Звавич - Сборник задач для подготовки и проведения письменного экзамена по алгебре за курс основной школы : 9 класс, 2008, АСТ: Астрель</t>
         </is>
       </c>
-      <c r="C1615" s="10" t="inlineStr">
+      <c r="C1615" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -32896,7 +32896,7 @@
           <t>Ю. П. Дудницын, В. Л. Кронгауз - Алгебра. Тематические тесты. 8 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1616" s="10" t="inlineStr">
+      <c r="C1616" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -32916,7 +32916,7 @@
           <t>И. Л. Гусева, С. А. Пушкин, Н. В. Рыбакова - Тестовые материалы для оценки качества обучения. Алгебра. 8 класс, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1617" s="10" t="inlineStr">
+      <c r="C1617" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -32936,7 +32936,7 @@
           <t>Лебединцева Е.А., Беленкова Е.Ю. - Алгебра. 8 класс. Задания для обучения и развития учащихся, 2013, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1618" s="10" t="inlineStr">
+      <c r="C1618" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32956,7 +32956,7 @@
           <t>Тематическое планирование к учебнику Ю.Н. Макарычева, Н.Г. Миндюк, К.И. Нешкова, С.Б. Суворовой</t>
         </is>
       </c>
-      <c r="C1619" s="10" t="inlineStr">
+      <c r="C1619" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32976,7 +32976,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Методические рекомендации. 8 класс, 2016, Просвещение</t>
         </is>
       </c>
-      <c r="C1620" s="10" t="inlineStr">
+      <c r="C1620" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -32996,7 +32996,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили, В. И. Ахременкова - Алгебра. 8 класс. Контрольные измерительные материалы, 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C1621" s="10" t="inlineStr">
+      <c r="C1621" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -33016,7 +33016,7 @@
           <t>В. И. Жохов, Ю. Н. Макарычев, Н. Г. Миндюк - Алгебра. Дидактические материалы. 8 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1622" s="10" t="inlineStr">
+      <c r="C1622" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33041,7 +33041,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1623" s="14" t="n">
+      <c r="D1623" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33101,8 +33101,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1626" s="14" t="n">
-        <v>2</v>
+      <c r="D1626" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1627">
@@ -33161,7 +33161,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1629" s="14" t="n">
+      <c r="D1629" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33176,7 +33176,7 @@
           <t>М.А. Попов - Контрольные и самостоятельные работы по математике: 5 класс: к учебнику Н.Я. Виленкина и др. «Математика. 5 класс», 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1630" s="9" t="inlineStr">
+      <c r="C1630" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33196,12 +33196,12 @@
           <t>В.Л. Александрова - Математика. 5 класс. Контрольные работы в НОВОМ формате, 2011, Интеллект-Центр</t>
         </is>
       </c>
-      <c r="C1631" s="9" t="inlineStr">
+      <c r="C1631" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1631" s="14" t="n">
+      <c r="D1631" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33216,12 +33216,12 @@
           <t>И. И. Зубарева, М. С. Мильштейн, М. Н. Шанцева - Математика. 5 класс. Самостоятельные работы, 2007, Мнемозина</t>
         </is>
       </c>
-      <c r="C1632" s="9" t="inlineStr">
+      <c r="C1632" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1632" s="14" t="n">
+      <c r="D1632" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33236,7 +33236,7 @@
           <t>И. Л. Гусева, С. А. Пушкин, Н. В. Рыбакова - Тестовые материалы для оценки качества обучения. Математика. 5 класс, 2011, «Интеллект-Центр»</t>
         </is>
       </c>
-      <c r="C1633" s="9" t="inlineStr">
+      <c r="C1633" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33256,12 +33256,12 @@
           <t>И. И. Зубарева, А. Г. Мордкович - Математика. 5 класс, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C1634" s="9" t="inlineStr">
+      <c r="C1634" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1634" s="14" t="n">
+      <c r="D1634" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
           <t>Г. В. Дорофеев, Л. В. Кузнецова, С. С. Минаева, С. Б. Суворова - Математика. Дидактические материалы. 5 класс, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C1635" s="9" t="inlineStr">
+      <c r="C1635" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33296,7 +33296,7 @@
           <t>А.П. Ершова, В.В. Голобородько - Самостоятельные и контрольные работы по математике для 5 класса, 2010, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1636" s="9" t="inlineStr">
+      <c r="C1636" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33316,7 +33316,7 @@
           <t>Смирнова Е.С. - САМОСТОЯТЕЛЬНЫЕ И КОНТРОЛЬНЫЕ РАБОТЫ ПО МАТЕМАТИКЕ для 5 класса, 2004, УЦ «Перспектива»</t>
         </is>
       </c>
-      <c r="C1637" s="9" t="inlineStr">
+      <c r="C1637" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33336,7 +33336,7 @@
           <t>С.А. Козлова, А.Г. Рубин - Контрольные работы к учебнику «Математика», 5 класс, 2012, Баласс</t>
         </is>
       </c>
-      <c r="C1638" s="9" t="inlineStr">
+      <c r="C1638" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33356,7 +33356,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по математике. 5 класс, 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1639" s="9" t="inlineStr">
+      <c r="C1639" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33376,7 +33376,7 @@
           <t>С. С. Минаева - Проверь себя. Тесты по математике. 5 класс, 2016, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1640" s="9" t="inlineStr">
+      <c r="C1640" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33416,7 +33416,7 @@
           <t>В.А. Гусев - Математика. Сборник геометрических задач: 5-6 классы, 2011, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1642" s="9" t="inlineStr">
+      <c r="C1642" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33436,7 +33436,7 @@
           <t>Л.А. Иляшенко - Математика: входные тесты за курс начальной школы: 5 класс, 2011, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1643" s="9" t="inlineStr">
+      <c r="C1643" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33456,12 +33456,12 @@
           <t>В.А. Гусев - Математика. Сборник геометрических задач: 5-6 классы, 2011, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1644" s="9" t="inlineStr">
+      <c r="C1644" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1644" s="14" t="n">
+      <c r="D1644" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33476,7 +33476,7 @@
           <t>Г.А. Захарова, Е.И. Полушкина, О.В. Тетенкова - Математика. 5 класс. Экспресс-диагностика, 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C1645" s="9" t="inlineStr">
+      <c r="C1645" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33496,7 +33496,7 @@
           <t>Т.М. Ерина - Рабочая тетрадь по математике. Часть 2. 5 класс: к учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 5 класс», 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1646" s="9" t="inlineStr">
+      <c r="C1646" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33516,7 +33516,7 @@
           <t>С. А. Бокарева, Т. В. Смирнова - Математика. Поурочные разработки для 5 класса, 2009, Просвещение</t>
         </is>
       </c>
-      <c r="C1647" s="12" t="inlineStr">
+      <c r="C1647" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -33536,7 +33536,7 @@
           <t>С.Б. Суворова, Л.В. Кузнецова, С.С. Минаева, Л.О. Рослова - Математика. Методические рекомендации. 5 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1648" s="12" t="inlineStr">
+      <c r="C1648" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -33556,7 +33556,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. Б. Суворова - Математика. Дидактические материалы. 5 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1649" s="9" t="inlineStr">
+      <c r="C1649" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33576,7 +33576,7 @@
           <t>Е. А. Бунимович, Л. В. Кузнецова, Л. О. Рослова, С. С. Минаева, С. Б. Суворова - Математика. Рабочая тетрадь. 5 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1650" s="9" t="inlineStr">
+      <c r="C1650" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33596,7 +33596,7 @@
           <t>Г. В. Дорофеев, И. Ф. Шарыгин, С. Б. Суворова, Е. А. Бунимович, К. А. Краснянская, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Математика. 5 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1651" s="9" t="inlineStr">
+      <c r="C1651" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33616,7 +33616,7 @@
           <t>Н. А. Тарасенкова, И. Н. Богатырёва, О. П. Бочко, О. Н. Коломиец, З. А. Сердюк - МАТЕМАТИКА. 5 класс, 2013, Видавничий дім «ОСВІТА»</t>
         </is>
       </c>
-      <c r="C1652" s="9" t="inlineStr">
+      <c r="C1652" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33636,7 +33636,7 @@
           <t>П. В. Чулков, Е. Ф. Шершнев, О. Ф. Зарапина - Математика. Тематические тесты. 5 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1653" s="9" t="inlineStr">
+      <c r="C1653" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -33656,7 +33656,7 @@
           <t>С. А. ТЕЛЯКОВСКОГО - АЛГЕБРА 7 КЛАСС УЧЕБНИК ДЛЯ ОБЩЕОБРАЗОВАТЕЛЬНЫХ УЧРЕЖДЕНИЙ, 2009, «Просвещение»</t>
         </is>
       </c>
-      <c r="C1654" s="10" t="inlineStr">
+      <c r="C1654" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33672,7 +33672,7 @@
         </is>
       </c>
       <c r="B1655" s="3" t="inlineStr"/>
-      <c r="C1655" s="8" t="inlineStr">
+      <c r="C1655" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -33692,12 +33692,12 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 7 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1656" s="10" t="inlineStr">
+      <c r="C1656" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1656" s="14" t="n">
+      <c r="D1656" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33712,7 +33712,7 @@
           <t>Л. П. Евстафьева, А. П. Карп - Алгебра. Дидактические материалы. 7 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1657" s="10" t="inlineStr">
+      <c r="C1657" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33732,7 +33732,7 @@
           <t>Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова, С. В. Суворова, Н. С. Масленникова - Алгебра. Тематические тесты. 7 класс, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1658" s="10" t="inlineStr">
+      <c r="C1658" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33752,7 +33752,7 @@
           <t>С. С. Минаева, Л. О. Рослова - Алгебра. Рабочая тетрадь. 7 класс, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1659" s="10" t="inlineStr">
+      <c r="C1659" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33772,12 +33772,12 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 7 класс. Часть 1, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1660" s="10" t="inlineStr">
+      <c r="C1660" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1660" s="14" t="n">
+      <c r="D1660" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -33792,7 +33792,7 @@
           <t>А. Ю. Кузнецов, Т. В. Межина, О. В. Сененко - Русский язык. Подготовка к ОГЭ в 2017 году. Диагностические работы, 2017, МЦНМО</t>
         </is>
       </c>
-      <c r="C1661" s="10" t="inlineStr">
+      <c r="C1661" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -33812,7 +33812,7 @@
           <t>М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Дидактические материалы. 7 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1662" s="10" t="inlineStr">
+      <c r="C1662" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -33837,8 +33837,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1663" s="14" t="n">
-        <v>2</v>
+      <c r="D1663" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1664">
@@ -33857,8 +33857,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1664" s="14" t="n">
-        <v>3</v>
+      <c r="D1664" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1665">
@@ -33877,8 +33877,8 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1665" s="14" t="n">
-        <v>4</v>
+      <c r="D1665" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1666">
@@ -33892,7 +33892,7 @@
           <t>О.В. Узорова, Е.А. Нефёдова - Быстро решаем задачи по математике. 1-й класс, 2017, Издательство АСТ</t>
         </is>
       </c>
-      <c r="C1666" s="11" t="inlineStr">
+      <c r="C1666" s="12" t="inlineStr">
         <is>
           <t>Popular Math &amp; Puzzles</t>
         </is>
@@ -33932,7 +33932,7 @@
           <t>Г. В. Дорофеев, С. Б. Суворова, Е. А. Бунимович, Л. В. Кузнецова, С. С. Минаева, Л. О. Рослова - Алгебра. 9 класс: учебник для общеобразовательных организаций, 2019, Просвещение</t>
         </is>
       </c>
-      <c r="C1668" s="10" t="inlineStr">
+      <c r="C1668" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34117,8 +34117,8 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1677" s="14" t="n">
-        <v>2</v>
+      <c r="D1677" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1678">
@@ -34512,7 +34512,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин, Ю. К. Войтова - Сборник задач по математике, 2010, Национальный институт образования</t>
         </is>
       </c>
-      <c r="C1697" s="9" t="inlineStr">
+      <c r="C1697" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34532,7 +34532,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин, Ю. К. Войтова - Математика. Учебное пособие для 6 класса учреждений общего среднего образования с русским языком обучения, 2014, Национальный институт образования</t>
         </is>
       </c>
-      <c r="C1698" s="9" t="inlineStr">
+      <c r="C1698" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34552,7 +34552,7 @@
           <t>С.А. Козлова, А.Г. Рубин - Контрольно-измерительные материалы. Контрольные работы к учебнику «Математика». 6 класс, 2014, Баласс</t>
         </is>
       </c>
-      <c r="C1699" s="9" t="inlineStr">
+      <c r="C1699" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34572,7 +34572,7 @@
           <t>В.Н. Рудницкая - Тесты по математике: 6 класс: к учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 6 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1700" s="9" t="inlineStr">
+      <c r="C1700" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34592,7 +34592,7 @@
           <t>В.Н. Рудницкая - Дидактические материалы по математике. 6 класс: к учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 6 класс», 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1701" s="9" t="inlineStr">
+      <c r="C1701" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34612,7 +34612,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Промежуточное тестирование. Математика. 6 класс, 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1702" s="9" t="inlineStr">
+      <c r="C1702" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34632,12 +34632,12 @@
           <t>С.А. Козлова, А.Г. Рубин - МАТЕМАТИКА. УЧЕБНИК. 6 класс. Часть 1, 2013, БАЛАСС</t>
         </is>
       </c>
-      <c r="C1703" s="9" t="inlineStr">
+      <c r="C1703" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1703" s="14" t="n">
+      <c r="D1703" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34712,12 +34712,12 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра : учебное пособие для 10 класса учреждений общего среднего образования с русским языком обучения, 2013, Народная асвета</t>
         </is>
       </c>
-      <c r="C1707" s="10" t="inlineStr">
+      <c r="C1707" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1707" s="14" t="n">
+      <c r="D1707" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34732,7 +34732,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин - Алгебра. Учебное пособие для 11 класса учреждений общего среднего образования с русским языком обучения, 2013, Народная асвета</t>
         </is>
       </c>
-      <c r="C1708" s="10" t="inlineStr">
+      <c r="C1708" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34752,7 +34752,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 10 класса учреждений общего среднего образования с русским языком обучения, 2013, Адукацыя і выхаванне</t>
         </is>
       </c>
-      <c r="C1709" s="8" t="inlineStr">
+      <c r="C1709" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -34772,7 +34772,7 @@
           <t>Л. А. Латотин, Б. Д. Чеботаревский - МАТЕМАТИКА. Учебное пособие для 11 класса учреждений общего среднего образования с русским языком обучения, 2013, Народная асвета</t>
         </is>
       </c>
-      <c r="C1710" s="8" t="inlineStr">
+      <c r="C1710" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -34812,12 +34812,12 @@
           <t>Т.М. Ерина - Рабочая тетрадь по алгебре: 8 класс: к учебнику Ю.Н. Макарычева и др. «Алгебра. 8 класс», 2013, Экзамен</t>
         </is>
       </c>
-      <c r="C1712" s="10" t="inlineStr">
+      <c r="C1712" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1712" s="14" t="n">
+      <c r="D1712" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34832,7 +34832,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Рабочая тетрадь. 8 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1713" s="10" t="inlineStr">
+      <c r="C1713" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34852,7 +34852,7 @@
           <t>М. А. Попов - Контрольные и самостоятельные работы по алгебре: 8 класс: к учебнику А. Г. Мордковича «Алгебра. 8 класс», 2016, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1714" s="10" t="inlineStr">
+      <c r="C1714" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34872,7 +34872,7 @@
           <t>М.А. Попов - Дидактические материалы по алгебре: 8 класс: к учебнику А.Г. Мордковича «Алгебра. 8 класс», 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C1715" s="10" t="inlineStr">
+      <c r="C1715" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34892,7 +34892,7 @@
           <t>Маслакова Г.И. - Рабочая программа по алгебре. 8 класс, 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C1716" s="10" t="inlineStr">
+      <c r="C1716" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34912,7 +34912,7 @@
           <t>Е. М. Ключникова, И. В. Комиссарова - Промежуточное тестирование. Алгебра. 8 класс, 2015, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1717" s="10" t="inlineStr">
+      <c r="C1717" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -34932,7 +34932,7 @@
           <t>А.Н. Рурукин, С.В. Сочилова, Ю.М. Зеленский - Поурочные разработки по алгебре: 8 класс, 2010, ВАКО</t>
         </is>
       </c>
-      <c r="C1718" s="10" t="inlineStr">
+      <c r="C1718" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -34952,7 +34952,7 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Тесты по алгебре: 8 класс: к учебнику А.Г. Мордковича «Алгебра. 8 класс», 2011, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1719" s="10" t="inlineStr">
+      <c r="C1719" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -34972,7 +34972,7 @@
           <t>М.А. Попов - Контрольные и самостоятельные работы по математике: К учебнику Н.Я. Виленкина и др. «Математика. 6 класс», 2011, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1720" s="9" t="inlineStr">
+      <c r="C1720" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -34992,7 +34992,7 @@
           <t>В. Г. Гамбарин, И. И. Зубарева - Сборник задач и упражнений по математике. 6 класс, 2011, Мнемозина</t>
         </is>
       </c>
-      <c r="C1721" s="9" t="inlineStr">
+      <c r="C1721" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35012,7 +35012,7 @@
           <t>И. И. Зубарева, И. П. Лепешонкова, М. С. Мильштейн - Математика. 6 класс. Самостоятельные работы, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C1722" s="9" t="inlineStr">
+      <c r="C1722" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35032,7 +35032,7 @@
           <t>Н. Я. Виленкин, В. И. Жохов, А. С. Чесноков, С. И. Шварцбурд - Математика. 6 класс, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C1723" s="9" t="inlineStr">
+      <c r="C1723" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35052,7 +35052,7 @@
           <t>И. И. Зубарева, А. Г. Мордкович - Математика. 6 класс, 2009, Мнемозина</t>
         </is>
       </c>
-      <c r="C1724" s="9" t="inlineStr">
+      <c r="C1724" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35072,7 +35072,7 @@
           <t>А.П. Ершова, В.В. Голобородько - Самостоятельные и контрольные работы по математике для 6 класса, 2010, ИЛЕКСА</t>
         </is>
       </c>
-      <c r="C1725" s="9" t="inlineStr">
+      <c r="C1725" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35092,7 +35092,7 @@
           <t>Брагин В.Г., Уединов А.Б., Чулков П.В. - Математика. Дидактические материалы. 6 класс, 2005, Школа XXI век</t>
         </is>
       </c>
-      <c r="C1726" s="9" t="inlineStr">
+      <c r="C1726" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35112,7 +35112,7 @@
           <t>Смирнова Е.С. - Самостоятельные и контрольные работы по математике для 6 класса, 2006, УЦ «Перспектива»</t>
         </is>
       </c>
-      <c r="C1727" s="9" t="inlineStr">
+      <c r="C1727" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35132,7 +35132,7 @@
           <t>М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Дидактические материалы. 8 класс, 2013, Просвещение</t>
         </is>
       </c>
-      <c r="C1728" s="10" t="inlineStr">
+      <c r="C1728" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35152,7 +35152,7 @@
           <t>Ю. М. Колягин, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 8 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1729" s="10" t="inlineStr">
+      <c r="C1729" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35172,7 +35172,7 @@
           <t>А.С. Истер - Алгебра : учеб. для 8-го кл. общеобразоват. учеб. завед., 2016, Генеза</t>
         </is>
       </c>
-      <c r="C1730" s="10" t="inlineStr">
+      <c r="C1730" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35192,7 +35192,7 @@
           <t>Ю. М. Колягин, Ю. В. Сидоров, М. В. Ткачёва, Н. Е. Фёдорова, М. И. Шабунин - Алгебра. Рабочая тетрадь. 8 класс, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C1731" s="10" t="inlineStr">
+      <c r="C1731" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35212,7 +35212,7 @@
           <t>В.И. Жохов, Г.Д. Карташева - Уроки алгебры в 8 классе: книга для учителя, 2011, Просвещение</t>
         </is>
       </c>
-      <c r="C1732" s="10" t="inlineStr">
+      <c r="C1732" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35232,7 +35232,7 @@
           <t>Ю.А. Глазков, М.Я. Гаиашвили - Тесты по алгебре. 8 класс : к учебнику Ю.Н. Макарычева и др. «Алгебра. 8 класс», 2013, Экзамен</t>
         </is>
       </c>
-      <c r="C1733" s="10" t="inlineStr">
+      <c r="C1733" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -35252,7 +35252,7 @@
           <t>Ю.А. Глазков, М.Я. Гаиашвили - Самостоятельные и контрольные работы по алгебре, 2012, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1734" s="10" t="inlineStr">
+      <c r="C1734" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35272,7 +35272,7 @@
           <t>Л. И. Звавич, Н. В. Дьяконова - Дидактические материалы по алгебре: 8 класс: к учебнику Ю. Н. Макарычева и др. «Алгебра. 8 класс», 2014, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1735" s="10" t="inlineStr">
+      <c r="C1735" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35357,7 +35357,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1739" s="14" t="n">
+      <c r="D1739" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -35377,7 +35377,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1740" s="14" t="n">
+      <c r="D1740" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -35517,7 +35517,7 @@
           <t>Primary School Olympiads</t>
         </is>
       </c>
-      <c r="D1747" s="14" t="n">
+      <c r="D1747" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -35592,7 +35592,7 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухов - Математика. 5 класс. Тренажер. Тематические тесты и итоговые работы, 2013, Легион</t>
         </is>
       </c>
-      <c r="C1751" s="9" t="inlineStr">
+      <c r="C1751" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35612,13 +35612,13 @@
           <t>Ф.Ф. Лысенко, С.Ю. Кулабухов - Математика. 5 класс. Тематические тесты. Промежуточная аттестация, 2012, Легион</t>
         </is>
       </c>
-      <c r="C1752" s="9" t="inlineStr">
+      <c r="C1752" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1752" s="14" t="n">
-        <v>2</v>
+      <c r="D1752" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1753">
@@ -35632,7 +35632,7 @@
           <t>С. Г. Журавлев, В. А. Свентковский - Контрольные и самостоятельные работы по математике, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1753" s="9" t="inlineStr">
+      <c r="C1753" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35652,7 +35652,7 @@
           <t>М. Я. Гаиашвили, В. И. Ахременкова - Математика. Итоговая аттестация. Типовые тестовые задания. 5 класс, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1754" s="10" t="inlineStr">
+      <c r="C1754" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -35672,7 +35672,7 @@
           <t>Радаева Е.А. - Математика. 5 класс. 180 диагностических вариантов, 2013, Издательство «Национальное образование»</t>
         </is>
       </c>
-      <c r="C1755" s="9" t="inlineStr">
+      <c r="C1755" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35692,7 +35692,7 @@
           <t>Ю.П. Дудницын, В.Л. Кронгауз - Контрольные работы по математике, 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C1756" s="9" t="inlineStr">
+      <c r="C1756" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35712,7 +35712,7 @@
           <t>С.С. Минаева - Вычисляем без ошибок. Работы с самопроверкой для учащихся 5–6 классов, 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1757" s="9" t="inlineStr">
+      <c r="C1757" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35732,7 +35732,7 @@
           <t>С.С. Минаева - 20 тестов по математике: 5–6 классы, 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C1758" s="9" t="inlineStr">
+      <c r="C1758" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35752,7 +35752,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Математика. 5 класс. Методические рекомендации, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1759" s="12" t="inlineStr">
+      <c r="C1759" s="13" t="inlineStr">
         <is>
           <t>Teaching Methodology</t>
         </is>
@@ -35772,7 +35772,7 @@
           <t>М. К. Потапов, А. В. Шевкин - Математика. Дидактические материалы. 5 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1760" s="9" t="inlineStr">
+      <c r="C1760" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35792,7 +35792,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по математике. 5 класс: к учебнику С.М. Никольского и др. «Математика. 5 класс», 2013, Экзамен</t>
         </is>
       </c>
-      <c r="C1761" s="9" t="inlineStr">
+      <c r="C1761" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35812,7 +35812,7 @@
           <t>М.К. Потапов, А.В. Шевкин - Математика. 5 класс. Рабочая тетрадь. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1762" s="9" t="inlineStr">
+      <c r="C1762" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35832,7 +35832,7 @@
           <t>М. А. МИРЗААХМЕДОВ, А. А. РАХИМКАРИЕВ - МАТЕМАТИКА. 5, 2007, Государственное научное издательство «O‘zbekiston milliy ensiklopediyasi»</t>
         </is>
       </c>
-      <c r="C1763" s="9" t="inlineStr">
+      <c r="C1763" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35852,7 +35852,7 @@
           <t>Е. П. Кузнецова, Г. Л. Муравьева, Л. Б. Шнеперман, Б. Ю. Ящин, Ю. К. Войтова - Математика, 2013, Национальный институт образования</t>
         </is>
       </c>
-      <c r="C1764" s="9" t="inlineStr">
+      <c r="C1764" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35872,7 +35872,7 @@
           <t>С.А. Козлова, В.Н. Гераськин, А.Г. Рубин - Дидактический материал к учебнику «Математика» для 5-го класса, 2014, Баласс</t>
         </is>
       </c>
-      <c r="C1765" s="9" t="inlineStr">
+      <c r="C1765" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35892,7 +35892,7 @@
           <t>С.А. Козлова, А.Г. Рубин, В.Н. Гераськин - Тесты и самостоятельные работы к учебнику «Математика». 5 класс, 2014, Баласс</t>
         </is>
       </c>
-      <c r="C1766" s="9" t="inlineStr">
+      <c r="C1766" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -35912,7 +35912,7 @@
           <t>Ю.Н. Макарычев, Н.Г. Миндюк, К.И. Нешков, С.Б. Суворова - Алгебра. 7 класс, Просвещение</t>
         </is>
       </c>
-      <c r="C1767" s="10" t="inlineStr">
+      <c r="C1767" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35932,7 +35932,7 @@
           <t>Т.М. Ерина - Поурочное планирование по алгебре. 7 класс: к учебнику Ю.Н. Макарычева и др. «Алгебра: 7 класс», 2011, Экзамен</t>
         </is>
       </c>
-      <c r="C1768" s="10" t="inlineStr">
+      <c r="C1768" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35952,13 +35952,13 @@
           <t>А.Н. Рурукин - Поурочные разработки по алгебре. 7 класс: к учебнику Ю.Н. Макарычева и др., 2014, ВАКО</t>
         </is>
       </c>
-      <c r="C1769" s="10" t="inlineStr">
+      <c r="C1769" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1769" s="14" t="n">
-        <v>2</v>
+      <c r="D1769" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1770">
@@ -35972,7 +35972,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили - Алгебра. 7 класс. Контрольные измерительные материалы, 2014, Экзамен</t>
         </is>
       </c>
-      <c r="C1770" s="10" t="inlineStr">
+      <c r="C1770" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -35992,7 +35992,7 @@
           <t>Ю. А. Глазков, М. Я. Гаиашвили - Самостоятельные и контрольные работы по алгебре, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1771" s="10" t="inlineStr">
+      <c r="C1771" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -36012,7 +36012,7 @@
           <t>Т. М. Ерина - Рабочая тетрадь по алгебре. Часть 1. 7 класс, 2015, Экзамен</t>
         </is>
       </c>
-      <c r="C1772" s="8" t="inlineStr">
+      <c r="C1772" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -36032,7 +36032,7 @@
           <t>Н. Г. Миндюк, И. С. Шлыкова - Алгебра. Рабочая тетрадь. 7 класс. Часть 1, 2014, Просвещение</t>
         </is>
       </c>
-      <c r="C1773" s="10" t="inlineStr">
+      <c r="C1773" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -36052,7 +36052,7 @@
           <t>Ю.П. Дудницын, В.Л. Кронгауз - Контрольные работы по геометрии. 10 класс, 2009, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1774" s="8" t="inlineStr">
+      <c r="C1774" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -36112,7 +36112,7 @@
           <t>Н.Б. Мельникова - Контрольные работы по геометрии. 7 класс, 2009, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1777" s="8" t="inlineStr">
+      <c r="C1777" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -36157,7 +36157,7 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="D1779" s="14" t="n">
+      <c r="D1779" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36172,7 +36172,7 @@
           <t>В. Г. Гамбарин, И. И. Зубарева - Сборник задач и упражнений по математике. 5 класс, 2011, Мнемозина</t>
         </is>
       </c>
-      <c r="C1780" s="9" t="inlineStr">
+      <c r="C1780" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36192,7 +36192,7 @@
           <t>А.С.ЧЕСНОКОВ, К.И.НЕШКОВ - ДИДАКТИЧЕСКИЕ МАТЕРИАЛЫ ПО МАТЕМАТИКЕ ДЛЯ 5 КЛАССА СРЕДНЕЙ ШКОЛЫ, 1990, ПРОСВЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C1781" s="9" t="inlineStr">
+      <c r="C1781" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36212,7 +36212,7 @@
           <t>Под редакцией Ф.Ф. Лысенко - Алгебра. 9 класс. Подготовка к государственной итоговой аттестации-2010: учебно-методическое пособие, 2009, Легион-М</t>
         </is>
       </c>
-      <c r="C1782" s="10" t="inlineStr">
+      <c r="C1782" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -36492,7 +36492,7 @@
           <t>С.А. Козлова, А.Г. Рубин - МАТЕМАТИКА. 6 класс. Часть 1, 2013, БАЛАСС</t>
         </is>
       </c>
-      <c r="C1796" s="9" t="inlineStr">
+      <c r="C1796" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36512,12 +36512,12 @@
           <t>Т.М. Ерина - Рабочая тетрадь по математике. Часть 1. 6 класс. К учебнику И.И. Зубаревой, А.Г. Мордковича «Математика. 6 класс», 2014, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1797" s="9" t="inlineStr">
+      <c r="C1797" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
       </c>
-      <c r="D1797" s="14" t="n">
+      <c r="D1797" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36532,7 +36532,7 @@
           <t>С. С. Минаева - Проверь себя. Тесты по математике. 6 класс, 2016, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1798" s="9" t="inlineStr">
+      <c r="C1798" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36552,7 +36552,7 @@
           <t>Под редакцией Ф.Ф. Лысенко, С.Ю. Кулабухова - Математика. 6 класс. Тренажер. Тематические тесты и итоговые работы, 2014, Легион</t>
         </is>
       </c>
-      <c r="C1799" s="9" t="inlineStr">
+      <c r="C1799" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36572,7 +36572,7 @@
           <t>Под редакцией Ф.Ф. Лысенко, С.Ю. Кулабухова - Математика. 6 класс. Тематические тесты. Промежуточная аттестация, 2012, Легион</t>
         </is>
       </c>
-      <c r="C1800" s="9" t="inlineStr">
+      <c r="C1800" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36592,7 +36592,7 @@
           <t>М. Я. Гаиашвили, В. И. Ахременкова - МАТЕМАТИКА. ИТОГОВАЯ АТТЕСТАЦИЯ. ТИПОВЫЕ ТЕСТОВЫЕ ЗАДАНИЯ. 6 класс, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1801" s="10" t="inlineStr">
+      <c r="C1801" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -36612,7 +36612,7 @@
           <t>Ф.Ф. Лысенко, Л.С. Ольховой, С.Ю. Кулабухова - Математика. 5-6 класс. Тесты для промежуточной аттестации, 2010, Легион, Легион-М</t>
         </is>
       </c>
-      <c r="C1802" s="10" t="inlineStr">
+      <c r="C1802" s="11" t="inlineStr">
         <is>
           <t>Exam Prep</t>
         </is>
@@ -36632,7 +36632,7 @@
           <t>С. Г. Журавлев, С. А. Изотова, С. В. Киреева - Контрольные и самостоятельные работы по математике, 2015, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1803" s="9" t="inlineStr">
+      <c r="C1803" s="10" t="inlineStr">
         <is>
           <t>Middle School Math</t>
         </is>
@@ -36832,7 +36832,7 @@
           <t>Г. К. Муравин, О. В. Муравина - Математика: алгебра и начала математического анализа, геометрия. Алгебра и начала математического анализа. 11 класс. Углубленный уровень, 2014, Дрофа</t>
         </is>
       </c>
-      <c r="C1813" s="8" t="inlineStr">
+      <c r="C1813" s="9" t="inlineStr">
         <is>
           <t>General Math</t>
         </is>
@@ -36857,7 +36857,7 @@
           <t>Calculus</t>
         </is>
       </c>
-      <c r="D1814" s="14" t="n">
+      <c r="D1814" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36877,7 +36877,7 @@
           <t>Primary School</t>
         </is>
       </c>
-      <c r="D1815" s="14" t="n">
+      <c r="D1815" s="8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -36924,12 +36924,12 @@
           <t>Е.М. Ключникова, И.В. Комиссарова - Рабочая тетрадь по алгебре: часть 1: 8 класс: к учебнику А.Г. Мордковича «Алгебра. 8 класс», 2013, Издательство «Экзамен»</t>
         </is>
       </c>
-      <c r="C1818" s="10" t="inlineStr">
+      <c r="C1818" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D1818" s="14" t="n">
+      <c r="D1818" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36944,7 +36944,7 @@
           <t>А.Г. Мерзляк, В.Б. Полонский, Е.М. Рабинович, М.С. Якир - Алгебра. Дидактические материалы. 8 класс, 2015, Вентана-Граф</t>
         </is>
       </c>
-      <c r="C1819" s="10" t="inlineStr">
+      <c r="C1819" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -36964,7 +36964,7 @@
           <t>Макарычев Ю. Н., Миндюк Н. Г. - Алгебра. Дидактические материалы. 8 класс: пособие для шк. с углубл. изучением математики, 2010, Просвещение</t>
         </is>
       </c>
-      <c r="C1820" s="10" t="inlineStr">
+      <c r="C1820" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -36984,7 +36984,7 @@
           <t>А.Г. Рубин, П.В. Чулков - Алгебра. 8 класс, 2015, БАЛАСС</t>
         </is>
       </c>
-      <c r="C1821" s="10" t="inlineStr">
+      <c r="C1821" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -37004,7 +37004,7 @@
           <t>С.Г. Журавлев, В.В. Ермаков, Ю.В. Перепелкина, В.А. Свентковский - Тесты по алгебре. 8 класс: к учебнику С.М. Никольского и др. «Алгебра. 8 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1822" s="10" t="inlineStr">
+      <c r="C1822" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -37024,7 +37024,7 @@
           <t>П. В. Чулков, Т. С. Струков - Алгебра. Тематические тесты. 8 класс, 2012, Просвещение</t>
         </is>
       </c>
-      <c r="C1823" s="10" t="inlineStr">
+      <c r="C1823" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -37044,7 +37044,7 @@
           <t>С.Г. Журавлев, Ю.В. Перепелкина - Рабочая тетрадь по алгебре: 8 класс: к учебнику С.М. Никольского и др. «Алгебра. 8 класс», 2013, Издательство «ЭКЗАМЕН»</t>
         </is>
       </c>
-      <c r="C1824" s="10" t="inlineStr">
+      <c r="C1824" s="11" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
@@ -37088,7 +37088,7 @@
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>1686</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="3">
@@ -37098,7 +37098,7 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
